--- a/Results/Hydrogen/hydrogen human toxicity non-carcinogenic results.xlsx
+++ b/Results/Hydrogen/hydrogen human toxicity non-carcinogenic results.xlsx
@@ -515,37 +515,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.208774686984318e-07</v>
+        <v>5.208774686984519e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>2.895706867005804e-07</v>
+        <v>2.895706867005796e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>6.460381455771431e-07</v>
+        <v>6.460381455771412e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>2.895706867005804e-07</v>
+        <v>2.895706867005796e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>2.895706867005804e-07</v>
+        <v>2.895706867005796e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>4.782335421662066e-07</v>
+        <v>4.782335421662009e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.388575731042446e-06</v>
+        <v>1.388575731042435e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>2.895706867005804e-07</v>
+        <v>2.895706867005796e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>3.915720700217566e-07</v>
+        <v>3.915720700217504e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>3.391835828110524e-07</v>
+        <v>3.391835828110436e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.719332397625913e-06</v>
+        <v>2.413312780881303e-07</v>
       </c>
     </row>
     <row r="3">
@@ -558,25 +558,25 @@
         <v>1.048586797748796e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>9.823604571966532e-09</v>
+        <v>9.823604571966583e-09</v>
       </c>
       <c r="D3" t="n">
         <v>1.048586797748796e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>9.97178107577203e-09</v>
+        <v>9.971781075772172e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>9.971781075772022e-09</v>
+        <v>9.971781075772138e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>1.042727558756831e-08</v>
+        <v>1.042727558756841e-08</v>
       </c>
       <c r="H3" t="n">
         <v>1.048586797748796e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.018386544921388e-08</v>
+        <v>1.018386544921409e-08</v>
       </c>
       <c r="J3" t="n">
         <v>1.048586797748796e-08</v>
@@ -595,31 +595,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.492000275045253e-08</v>
+        <v>2.734344911612073e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>2.673854634041321e-08</v>
+        <v>2.673854634041299e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>2.784762507338719e-08</v>
+        <v>2.784781367627673e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>2.548491360674043e-08</v>
+        <v>2.548491360674053e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>2.705652080202814e-08</v>
+        <v>2.705652080202825e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>4.48614103605329e-08</v>
+        <v>4.486141036053311e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>4.576358509163172e-08</v>
+        <v>4.576358509163153e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>4.461800022217851e-08</v>
+        <v>2.704144658784685e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>2.837711143408391e-08</v>
+        <v>2.837711143408444e-08</v>
       </c>
       <c r="K4" t="n">
         <v>2.723826078474672e-08</v>
@@ -635,37 +635,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.203454469630304e-08</v>
+        <v>5.203454469630301e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>5.173254216802921e-08</v>
+        <v>5.173254216802925e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>5.203181954952327e-08</v>
+        <v>5.203181954952342e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>5.172579108225326e-08</v>
+        <v>5.172579108225338e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>5.172579108225326e-08</v>
+        <v>5.172579108225338e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>5.197595230638354e-08</v>
+        <v>5.197595230638356e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>5.203454469630304e-08</v>
+        <v>5.203454469630301e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>5.173254216802921e-08</v>
+        <v>5.173254216802925e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>5.203454469630304e-08</v>
+        <v>5.203454469630301e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>5.203454469630304e-08</v>
+        <v>5.203454469630301e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>5.203454469630304e-08</v>
+        <v>5.203454469630301e-08</v>
       </c>
     </row>
     <row r="6">
@@ -675,37 +675,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.619281433374785e-07</v>
+        <v>1.619281433374784e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>2.603099594229853e-07</v>
+        <v>2.603099594229857e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>2.810548786077113e-07</v>
+        <v>2.810548786077118e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>2.333228156862637e-07</v>
+        <v>2.333228156862638e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.647513435469373e-07</v>
+        <v>1.647513435469377e-07</v>
       </c>
       <c r="G6" t="n">
         <v>2.605369568454371e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>2.605955492353573e-07</v>
+        <v>2.605955492353581e-07</v>
       </c>
       <c r="I6" t="n">
         <v>2.602935467070828e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>2.606149402221151e-07</v>
+        <v>2.606149402221153e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.600953456156853e-07</v>
+        <v>1.600953456156854e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>3.636619051434994e-07</v>
+        <v>3.636619051434998e-07</v>
       </c>
     </row>
     <row r="7">
@@ -715,37 +715,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.377834581406583e-07</v>
+        <v>1.377834581406584e-07</v>
       </c>
       <c r="C7" t="n">
         <v>1.737494566589815e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>1.740514622792914e-07</v>
+        <v>1.740514622792913e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>2.156019178341531e-07</v>
+        <v>2.15601917834153e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>1.737494200014628e-07</v>
+        <v>1.737494200014616e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>1.739928667973356e-07</v>
+        <v>1.739928667973358e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>1.740514591872545e-07</v>
+        <v>1.740514591872552e-07</v>
       </c>
       <c r="I7" t="n">
         <v>1.737494566589815e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>1.740514591872545e-07</v>
+        <v>1.740514591872552e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>1.283835712529138e-07</v>
+        <v>1.53037638245926e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>1.740514591872545e-07</v>
+        <v>1.740514591872552e-07</v>
       </c>
     </row>
     <row r="8">
@@ -755,37 +755,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.129908477934621e-08</v>
+        <v>2.129908477934851e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>1.948022917583349e-08</v>
+        <v>1.948022917583351e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>1.883962123709908e-08</v>
+        <v>1.883962123709911e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>1.948022917583349e-08</v>
+        <v>1.948022917583351e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>1.948022917583349e-08</v>
+        <v>1.948022917583351e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.25888310291393e-08</v>
+        <v>2.258883102913952e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>6.201465405900859e-09</v>
+        <v>6.201465405900822e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.948022917583349e-08</v>
+        <v>1.948022917583351e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.466628784649331e-08</v>
+        <v>2.466628784649335e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>2.542418024326608e-08</v>
+        <v>2.542418024326627e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>2.790675859272358e-08</v>
+        <v>2.790675859272359e-08</v>
       </c>
     </row>
     <row r="9">
@@ -795,37 +795,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.654779577831026e-08</v>
+        <v>2.654779577831023e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.174979435952175e-08</v>
+        <v>2.174979435952174e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>2.554638895067353e-08</v>
+        <v>2.554638895067361e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>2.174979435952175e-08</v>
+        <v>2.174979435952174e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.174979435952175e-08</v>
+        <v>2.174979435952174e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.704137330127056e-08</v>
+        <v>2.704137330127063e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.042150359905162e-08</v>
+        <v>2.042150359905166e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.174979435952175e-08</v>
+        <v>2.174979435952174e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.792156397041601e-08</v>
+        <v>2.792156397041605e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.822820408805283e-08</v>
+        <v>2.822820408805286e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.924119555152719e-08</v>
+        <v>2.924119555152723e-08</v>
       </c>
     </row>
   </sheetData>
@@ -911,37 +911,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.311720942242096e-07</v>
+        <v>1.31172094224209e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>1.6921076239227e-07</v>
+        <v>1.692107623922691e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.798460775314919e-07</v>
+        <v>1.798460775314915e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.6921076239227e-07</v>
+        <v>1.692107623922691e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.6921076239227e-07</v>
+        <v>1.692107623922691e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.714459650966504e-07</v>
+        <v>1.71445965096644e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.916171655488518e-07</v>
+        <v>1.916171655488511e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.6921076239227e-07</v>
+        <v>1.692107623922691e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>2.182707071170224e-07</v>
+        <v>2.182707071170221e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.371884676106648e-07</v>
+        <v>1.371884676106651e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.684809560770347e-07</v>
+        <v>1.794947993647032e-07</v>
       </c>
     </row>
     <row r="3">
@@ -951,37 +951,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.383474804721396e-09</v>
+        <v>9.383474804721348e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>8.939804762932409e-09</v>
+        <v>8.939804762932303e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>9.383474804721396e-09</v>
+        <v>9.383474804721348e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>9.054048705352931e-09</v>
+        <v>9.054048705352818e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>9.054048705352931e-09</v>
+        <v>9.054048705352822e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>9.331560563048344e-09</v>
+        <v>9.331560563048271e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>9.383474804721396e-09</v>
+        <v>9.383474804721348e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>9.124121051534073e-09</v>
+        <v>9.124121051533978e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>9.383474804721396e-09</v>
+        <v>9.383474804721348e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>9.383474804721396e-09</v>
+        <v>9.383474804721348e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>9.383474804721396e-09</v>
+        <v>9.383474804721348e-09</v>
       </c>
     </row>
     <row r="4">
@@ -991,37 +991,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.699703963804622e-08</v>
+        <v>3.699703963804612e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>2.292039161302044e-08</v>
+        <v>2.29203916130201e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>2.325410534621817e-08</v>
+        <v>3.726428723108952e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>2.185133571467694e-08</v>
+        <v>2.185133571467684e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>2.29806705112601e-08</v>
+        <v>2.298067051125998e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>3.694512539637303e-08</v>
+        <v>2.31518311637862e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>3.756564040490167e-08</v>
+        <v>3.756564040490161e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>2.294439165227197e-08</v>
+        <v>2.294439165227187e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>3.713318755274432e-08</v>
+        <v>3.713318755274423e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>2.31684833793169e-08</v>
+        <v>2.316848337931688e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>2.322190109974804e-08</v>
+        <v>2.322190109974802e-08</v>
       </c>
     </row>
     <row r="5">
@@ -1031,37 +1031,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.512137265085348e-08</v>
+        <v>4.51213726508533e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>4.486201889766618e-08</v>
+        <v>4.486201889766596e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>4.51190104894248e-08</v>
+        <v>4.511901048942464e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>4.48632984255314e-08</v>
+        <v>4.486329842553122e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>4.48632984255314e-08</v>
+        <v>4.486329842553122e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>4.506945840918045e-08</v>
+        <v>4.506945840918029e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>4.512137265085348e-08</v>
+        <v>4.51213726508533e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>4.486201889766618e-08</v>
+        <v>4.486201889766596e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>4.512137265085348e-08</v>
+        <v>4.51213726508533e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>4.512137265085348e-08</v>
+        <v>4.51213726508533e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>4.512137265085348e-08</v>
+        <v>4.51213726508533e-08</v>
       </c>
     </row>
     <row r="6">
@@ -1071,37 +1071,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.400326235169465e-07</v>
+        <v>1.40032623516946e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>2.249008329619749e-07</v>
+        <v>2.24900832961974e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>2.427866320398824e-07</v>
+        <v>2.427866320398819e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>2.016220659224752e-07</v>
+        <v>2.016220659224744e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.42473190022813e-07</v>
+        <v>1.424731900228125e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>2.250873097673016e-07</v>
+        <v>2.250873097673008e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>2.251392240089746e-07</v>
+        <v>2.251392240089741e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>2.248798702557875e-07</v>
+        <v>2.248798702557868e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>2.251559499073108e-07</v>
+        <v>2.251559499073103e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.384517247178398e-07</v>
+        <v>1.384517247178394e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>3.140401847331001e-07</v>
+        <v>3.14040184733099e-07</v>
       </c>
     </row>
     <row r="7">
@@ -1111,37 +1111,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.681609756191569e-08</v>
+        <v>9.68160975619152e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.216479354593186e-07</v>
+        <v>1.216479354593183e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>1.219072985238706e-07</v>
+        <v>1.219072985238701e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>1.506026243078718e-07</v>
+        <v>1.506026243078714e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>1.216479172878722e-07</v>
+        <v>1.216479172878719e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>1.218553749708331e-07</v>
+        <v>1.218553749708325e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>1.219072892125059e-07</v>
+        <v>1.219072892125057e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>1.216479354593186e-07</v>
+        <v>1.216479354593183e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>1.219072892125059e-07</v>
+        <v>1.219072892125057e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>1.073693581457659e-07</v>
+        <v>1.073693581457653e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>1.219072892125059e-07</v>
+        <v>1.219072892125057e-07</v>
       </c>
     </row>
     <row r="8">
@@ -1151,37 +1151,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.860728578974077e-08</v>
+        <v>2.860728578974069e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.094026148447193e-08</v>
+        <v>2.094026148447188e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.743641763275462e-08</v>
+        <v>2.743641763275453e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.094026148447193e-08</v>
+        <v>2.094026148447188e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>2.094026148447193e-08</v>
+        <v>2.094026148447188e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.764582526098476e-08</v>
+        <v>2.764582526098474e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.755160981908979e-08</v>
+        <v>2.755160981908976e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.094026148447193e-08</v>
+        <v>2.094026148447188e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.662489829623674e-08</v>
+        <v>2.662489829623669e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>2.851122855112332e-08</v>
+        <v>2.851122855112327e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>2.800608061478131e-08</v>
+        <v>2.787421633221032e-08</v>
       </c>
     </row>
     <row r="9">
@@ -1191,13 +1191,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.899713965852742e-08</v>
+        <v>2.899713965852739e-08</v>
       </c>
       <c r="C9" t="n">
         <v>2.195280739279198e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>2.852031741191639e-08</v>
+        <v>2.85203174119163e-08</v>
       </c>
       <c r="E9" t="n">
         <v>2.195280739279198e-08</v>
@@ -1206,22 +1206,22 @@
         <v>2.195280739279198e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.858936100309144e-08</v>
+        <v>2.858936100309136e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.856932252562823e-08</v>
+        <v>2.856932252562822e-08</v>
       </c>
       <c r="I9" t="n">
         <v>2.195280739279198e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.819096123733181e-08</v>
+        <v>2.819096123733173e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.89580881062435e-08</v>
+        <v>2.895808810624348e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.875365955713382e-08</v>
+        <v>2.875365955713376e-08</v>
       </c>
     </row>
   </sheetData>
@@ -1307,37 +1307,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.222901508897995e-07</v>
+        <v>1.222901508897998e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>2.755615218627685e-07</v>
+        <v>2.755615218627689e-07</v>
       </c>
       <c r="D2" t="n">
         <v>4.059070558766436e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>2.161378819984958e-07</v>
+        <v>2.161378819984962e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>2.161378819984958e-07</v>
+        <v>2.161378819984962e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>3.00114719606956e-07</v>
+        <v>3.001147196069548e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>7.062243832099791e-07</v>
+        <v>7.062243832099794e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>2.161378819984958e-07</v>
+        <v>2.161378819984962e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>3.588950044872085e-07</v>
+        <v>3.588950044872087e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>2.128699494007315e-07</v>
+        <v>2.128699494007319e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>4.201541786952035e-07</v>
+        <v>4.201541786952031e-07</v>
       </c>
     </row>
     <row r="3">
@@ -1347,37 +1347,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.406723322978603e-09</v>
+        <v>9.406723322978585e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>8.550951276110707e-09</v>
+        <v>8.550951276110697e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>9.406723322978603e-09</v>
+        <v>9.406723322978587e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>8.950838397286646e-09</v>
+        <v>8.950838397286356e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>8.950838397286647e-09</v>
+        <v>8.950838397286361e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>9.350530755373928e-09</v>
+        <v>9.350530755373849e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>9.406723322978603e-09</v>
+        <v>9.406723322978587e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>9.120407671234148e-09</v>
+        <v>9.120407671234034e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>9.40672332297858e-09</v>
+        <v>9.406723322978587e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>9.406723322978603e-09</v>
+        <v>9.406723322978587e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>9.406723322978603e-09</v>
+        <v>9.406723322978587e-09</v>
       </c>
     </row>
     <row r="4">
@@ -1387,34 +1387,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.972658361251507e-08</v>
+        <v>2.450685719762844e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>2.426722144188993e-08</v>
+        <v>2.426722144188986e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>2.480054858171653e-08</v>
+        <v>2.480070491325369e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>2.291539308757223e-08</v>
+        <v>2.291539308757225e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>2.424123257561741e-08</v>
+        <v>2.424123257561743e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>3.96703910449104e-08</v>
+        <v>3.967039104491034e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>4.134183078703629e-08</v>
+        <v>4.134183078703627e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>3.944026796077054e-08</v>
+        <v>3.944026796077055e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>4.0137049093426e-08</v>
+        <v>4.013704909342599e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>2.442479590670009e-08</v>
+        <v>2.442479590670002e-08</v>
       </c>
       <c r="L4" t="n">
         <v>2.457707730033249e-08</v>
@@ -1427,37 +1427,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.748873795123987e-08</v>
+        <v>4.74887379512399e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>4.733157640484133e-08</v>
+        <v>4.73315764048413e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>4.748637461450172e-08</v>
+        <v>4.748637461450173e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>4.720396177739959e-08</v>
+        <v>4.720396177739957e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>4.720396177739959e-08</v>
+        <v>4.720396177739957e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>4.74325453836352e-08</v>
+        <v>4.743254538363519e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>4.748873795123987e-08</v>
+        <v>4.74887379512399e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>4.720242229949538e-08</v>
+        <v>4.720242229949534e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>4.748873795123987e-08</v>
+        <v>4.74887379512399e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>4.748873795123987e-08</v>
+        <v>4.74887379512399e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>4.748873795123987e-08</v>
+        <v>4.74887379512399e-08</v>
       </c>
     </row>
     <row r="6">
@@ -1467,13 +1467,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.487011848653514e-07</v>
+        <v>1.487011848653513e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>2.393930258416951e-07</v>
+        <v>2.393930258419777e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>2.583613559180394e-07</v>
+        <v>2.583613559180391e-07</v>
       </c>
       <c r="E6" t="n">
         <v>2.144205764458487e-07</v>
@@ -1485,19 +1485,19 @@
         <v>2.394716617563459e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>2.395278543240017e-07</v>
+        <v>2.395278543240015e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>2.392415386722062e-07</v>
+        <v>2.392415386722059e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>2.395457043801115e-07</v>
+        <v>2.395457043801114e-07</v>
       </c>
       <c r="K6" t="n">
         <v>1.470140328483933e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>3.344039053887181e-07</v>
+        <v>3.34403905388718e-07</v>
       </c>
     </row>
     <row r="7">
@@ -1507,37 +1507,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.14991630810808e-07</v>
+        <v>1.149916308108079e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>1.45044544221993e-07</v>
+        <v>1.450445442219928e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>1.452017134817319e-07</v>
+        <v>1.452017134817318e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>1.797771515842614e-07</v>
+        <v>1.797771515842615e-07</v>
       </c>
       <c r="F7" t="n">
         <v>1.449153649573845e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>1.451455132007868e-07</v>
+        <v>1.451455132007866e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>1.452017057683915e-07</v>
+        <v>1.452017057683913e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>1.44915390116647e-07</v>
+        <v>1.449153901166469e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>1.452017057683915e-07</v>
+        <v>1.452017057683913e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>1.07161826918357e-07</v>
+        <v>1.276978729380507e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>1.452017057683915e-07</v>
+        <v>1.452017057683913e-07</v>
       </c>
     </row>
     <row r="8">
@@ -1547,31 +1547,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.032693913022162e-08</v>
+        <v>2.032693913022161e-08</v>
       </c>
       <c r="C8" t="n">
         <v>1.377093251256591e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.090837916199042e-08</v>
+        <v>2.09083791619904e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>1.90688063649389e-08</v>
+        <v>1.906880636493892e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>1.90688063649389e-08</v>
+        <v>1.906880636493892e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.716615608516456e-08</v>
+        <v>2.716615608516458e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>1.577757305085088e-08</v>
+        <v>1.577757305085087e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>1.90688063649389e-08</v>
+        <v>1.906880636493892e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>1.883099531241732e-08</v>
+        <v>1.88309953124173e-08</v>
       </c>
       <c r="K8" t="n">
         <v>2.925695603717982e-08</v>
@@ -1587,34 +1587,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.149687504071195e-08</v>
+        <v>2.149687504071194e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>1.618056749287089e-08</v>
+        <v>1.618056749287086e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>2.50312246774921e-08</v>
+        <v>2.503122467749211e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>2.066748785757405e-08</v>
+        <v>2.066748785757403e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.066748785757405e-08</v>
+        <v>2.066748785757403e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.969497440912718e-08</v>
+        <v>2.969497440912717e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.295307082965019e-08</v>
+        <v>2.295307082965021e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.066748785757405e-08</v>
+        <v>2.066748785757403e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.214863460682896e-08</v>
+        <v>2.214863460682897e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>3.066524464652453e-08</v>
+        <v>3.066524464652454e-08</v>
       </c>
       <c r="L9" t="n">
         <v>2.486182674665131e-08</v>
@@ -1703,37 +1703,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.703254427529156e-08</v>
+        <v>7.703254427529121e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>2.190933287899248e-07</v>
+        <v>2.190933287899243e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>3.119500972891452e-07</v>
+        <v>3.119500972891449e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.71366571997465e-07</v>
+        <v>1.713665719974643e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.71366571997465e-07</v>
+        <v>1.713665719974643e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>2.228928323817706e-07</v>
+        <v>2.228928323817647e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>4.307435792107092e-07</v>
+        <v>4.307435792107089e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.71366571997465e-07</v>
+        <v>1.713665719974643e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>2.547552759642675e-07</v>
+        <v>2.54755275964267e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.486394690679902e-07</v>
+        <v>1.4863946906799e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>2.153619997938591e-07</v>
+        <v>2.153619997938588e-07</v>
       </c>
     </row>
     <row r="3">
@@ -1743,37 +1743,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.256616975581652e-09</v>
+        <v>9.256616975581432e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>8.427059156811159e-09</v>
+        <v>8.427059156811109e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>9.256616975581652e-09</v>
+        <v>9.256616975581432e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>8.916583658806835e-09</v>
+        <v>8.916583658806719e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>8.916583658806833e-09</v>
+        <v>8.916583658806777e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>9.201654131900145e-09</v>
+        <v>9.201654131900001e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>9.256616975581652e-09</v>
+        <v>9.256616975581432e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>8.978136939799587e-09</v>
+        <v>8.978136939799519e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>9.256616975581652e-09</v>
+        <v>9.256616975581432e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>9.256616975581652e-09</v>
+        <v>9.256616975581432e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>9.256616975581652e-09</v>
+        <v>9.256616975581432e-09</v>
       </c>
     </row>
     <row r="4">
@@ -1783,37 +1783,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.749362977541473e-08</v>
+        <v>3.749362977541449e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>2.29981572384322e-08</v>
+        <v>2.299815723843158e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>2.34480521474615e-08</v>
+        <v>3.805797531118256e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>2.17558243144357e-08</v>
+        <v>2.175582431443562e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>2.296590684718887e-08</v>
+        <v>2.296590684718869e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>2.315898045577807e-08</v>
+        <v>2.315898045577788e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>3.919082193006742e-08</v>
+        <v>3.919082193006713e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>2.293546326367737e-08</v>
+        <v>2.293546326367736e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>2.408724713636786e-08</v>
+        <v>2.408724713636754e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>2.313047760120066e-08</v>
+        <v>2.313047760120057e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>2.323724867710543e-08</v>
+        <v>2.323724867710523e-08</v>
       </c>
     </row>
     <row r="5">
@@ -1823,37 +1823,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.558450085685633e-08</v>
+        <v>4.55845008568563e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>4.542865786007816e-08</v>
+        <v>4.542865786007814e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>4.558226725971216e-08</v>
+        <v>4.558226725971213e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>4.533208886723325e-08</v>
+        <v>4.533208886723321e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>4.533208886723325e-08</v>
+        <v>4.533208886723321e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>4.552953801317485e-08</v>
+        <v>4.552953801317483e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>4.558450085685633e-08</v>
+        <v>4.55845008568563e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>4.530602082107433e-08</v>
+        <v>4.530602082107429e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>4.558450085685633e-08</v>
+        <v>4.55845008568563e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>4.558450085685633e-08</v>
+        <v>4.55845008568563e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>4.558450085685633e-08</v>
+        <v>4.55845008568563e-08</v>
       </c>
     </row>
     <row r="6">
@@ -1863,37 +1863,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.414896505722482e-07</v>
+        <v>1.41489650572248e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>2.276972892629027e-07</v>
+        <v>2.276972892632013e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>2.457071634913697e-07</v>
+        <v>2.457071634913693e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>2.039619008728247e-07</v>
+        <v>2.039619008728245e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.439642251275302e-07</v>
+        <v>1.4396422512753e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>2.277534441817215e-07</v>
+        <v>2.277534441817213e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>2.278084070255335e-07</v>
+        <v>2.278084070255332e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>2.27529926989621e-07</v>
+        <v>2.275299269896209e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>2.278253711464202e-07</v>
+        <v>2.2782537114642e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.398862353537944e-07</v>
+        <v>1.398862353537941e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>3.179755660096027e-07</v>
+        <v>3.179755660096022e-07</v>
       </c>
     </row>
     <row r="7">
@@ -1903,37 +1903,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.023885158749697e-07</v>
+        <v>1.023885158749694e-07</v>
       </c>
       <c r="C7" t="n">
         <v>1.289895925441024e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>1.29145444375996e-07</v>
+        <v>1.291454443759957e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>1.597438554764728e-07</v>
+        <v>1.597438554764727e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>1.288669347278917e-07</v>
+        <v>1.288669347278915e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>1.290904726971992e-07</v>
+        <v>1.29090472697199e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>1.291454355408807e-07</v>
+        <v>1.291454355408804e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>1.288669555050985e-07</v>
+        <v>1.288669555050984e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>1.291454355408807e-07</v>
+        <v>1.291454355408804e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>1.136423749199365e-07</v>
+        <v>1.136423749199363e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>1.291454355408807e-07</v>
+        <v>1.291454355408804e-07</v>
       </c>
     </row>
     <row r="8">
@@ -1943,37 +1943,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.115533345593641e-08</v>
+        <v>2.115533345593645e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>1.46689398208535e-08</v>
+        <v>1.466893982085351e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.262501154870929e-08</v>
+        <v>2.262501154870926e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>1.991022127182269e-08</v>
+        <v>1.991022127182272e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>1.991022127182269e-08</v>
+        <v>1.991022127182272e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.854559223670911e-08</v>
+        <v>2.854559223670908e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.084939963775215e-08</v>
+        <v>2.084939963775207e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>1.991022127182269e-08</v>
+        <v>1.991022127182272e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.088599863775264e-08</v>
+        <v>2.088599863775256e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>3.041404849023887e-08</v>
+        <v>3.041404849023879e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>2.512072196223369e-08</v>
+        <v>2.512072196223363e-08</v>
       </c>
     </row>
     <row r="9">
@@ -1983,37 +1983,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.178033089110131e-08</v>
+        <v>2.178033089110125e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>1.648813265574646e-08</v>
+        <v>1.648813265574647e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>2.569742821251103e-08</v>
+        <v>2.569742821251102e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>2.102866699668432e-08</v>
+        <v>2.102866699668435e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.102866699668432e-08</v>
+        <v>2.102866699668435e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>3.021147365024112e-08</v>
+        <v>3.021147365024102e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.498109170041748e-08</v>
+        <v>2.498109170041735e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.102866699668432e-08</v>
+        <v>2.102866699668435e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.302967959758938e-08</v>
+        <v>2.302967959758933e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>3.105875758221388e-08</v>
+        <v>3.105875758221382e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.646003424125765e-08</v>
+        <v>2.646003424125762e-08</v>
       </c>
     </row>
   </sheetData>
@@ -2099,31 +2099,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.533321102686824e-08</v>
+        <v>5.533321102686825e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.806259566777204e-07</v>
+        <v>1.806259566777207e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>2.546993268080724e-07</v>
+        <v>2.546993268080718e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.389545253771441e-07</v>
+        <v>1.389545253771424e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.389545253771441e-07</v>
+        <v>1.389545253771424e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.80575423737096e-07</v>
+        <v>1.805754237370901e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>2.998964285339349e-07</v>
+        <v>2.998964285339338e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.389545253771441e-07</v>
+        <v>1.389545253771424e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>1.733946140574756e-07</v>
+        <v>1.733946140574753e-07</v>
       </c>
       <c r="K2" t="n">
         <v>1.260629689860199e-07</v>
@@ -2139,37 +2139,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.306899834860853e-09</v>
+        <v>9.306899834860908e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>8.450956953818508e-09</v>
+        <v>8.450956953818538e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>9.306899834860853e-09</v>
+        <v>9.306899834860906e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>8.99188502838661e-09</v>
+        <v>8.991885028386572e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>8.99188502838661e-09</v>
+        <v>8.991885028386574e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>9.252317019504877e-09</v>
+        <v>9.252317019504933e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>9.306899834860853e-09</v>
+        <v>9.306899834860906e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>9.030901602257702e-09</v>
+        <v>9.030901602257786e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>9.306899834860853e-09</v>
+        <v>9.306899834860908e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>9.306899834860853e-09</v>
+        <v>9.306899834860906e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>9.306899834860853e-09</v>
+        <v>9.306899834860906e-09</v>
       </c>
     </row>
     <row r="4">
@@ -2179,37 +2179,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.726366936060252e-08</v>
+        <v>2.303760155240823e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>2.281055276578226e-08</v>
+        <v>2.281055276576164e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>2.322842792548753e-08</v>
+        <v>2.322842792548337e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>2.15967978894739e-08</v>
+        <v>2.159679788947399e-08</v>
       </c>
       <c r="F4" t="n">
         <v>2.279120054444306e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>2.298301873705229e-08</v>
+        <v>3.720908654524654e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>3.915128060441242e-08</v>
+        <v>3.915128060441244e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>2.276160331980511e-08</v>
+        <v>3.698767112799937e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>2.388423600218413e-08</v>
+        <v>3.770331554147413e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>2.297671335839987e-08</v>
+        <v>2.297671335839985e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>2.305146289392897e-08</v>
+        <v>2.305146289392925e-08</v>
       </c>
     </row>
     <row r="5">
@@ -2219,37 +2219,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.573783728017281e-08</v>
+        <v>4.573783728017276e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>4.558231657185837e-08</v>
+        <v>4.558231657185832e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>4.573560857808976e-08</v>
+        <v>4.573560857808972e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>4.549534744030528e-08</v>
+        <v>4.549534744030524e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>4.549534744030528e-08</v>
+        <v>4.549534744030524e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>4.568325446481691e-08</v>
+        <v>4.568325446481678e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>4.573783728017281e-08</v>
+        <v>4.573783728017276e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>4.546183904756981e-08</v>
+        <v>4.54618390475697e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>4.573783728017281e-08</v>
+        <v>4.573783728017276e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>4.573783728017281e-08</v>
+        <v>4.573783728017276e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>4.573783728017281e-08</v>
+        <v>4.573783728017276e-08</v>
       </c>
     </row>
     <row r="6">
@@ -2259,13 +2259,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.416985056632645e-07</v>
+        <v>1.416985056632643e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>2.2806436419584e-07</v>
+        <v>2.280643641954678e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>2.460980324162157e-07</v>
+        <v>2.460980324162158e-07</v>
       </c>
       <c r="E6" t="n">
         <v>2.042891440713848e-07</v>
@@ -2274,22 +2274,22 @@
         <v>1.441847762988218e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>2.281134333093037e-07</v>
+        <v>2.281134333093034e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>2.281680161248677e-07</v>
+        <v>2.281680161248676e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>2.278920178920565e-07</v>
+        <v>2.278920178920564e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>2.281850098727921e-07</v>
+        <v>2.28185009872792e-07</v>
       </c>
       <c r="K6" t="n">
         <v>1.400922901116483e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>3.184926502762923e-07</v>
+        <v>3.184926502762924e-07</v>
       </c>
     </row>
     <row r="7">
@@ -2299,37 +2299,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.721600898699056e-08</v>
+        <v>9.721600898699039e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.223947805556848e-07</v>
+        <v>1.223947805556847e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2255031073143e-07</v>
+        <v>1.225503107314298e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>1.51509523666284e-07</v>
+        <v>1.515095236662838e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>1.222742838014963e-07</v>
+        <v>1.222742838014962e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>1.224957184486434e-07</v>
+        <v>1.224957184486432e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>1.225503012639992e-07</v>
+        <v>1.22550301263999e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>1.222743030313962e-07</v>
+        <v>1.22274303031396e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>1.225503012639992e-07</v>
+        <v>1.22550301263999e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>1.072759795935433e-07</v>
+        <v>9.064990267831616e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.225503012639992e-07</v>
+        <v>1.22550301263999e-07</v>
       </c>
     </row>
     <row r="8">
@@ -2339,37 +2339,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.158937556148091e-08</v>
+        <v>2.158937556148096e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>1.543687939126942e-08</v>
+        <v>1.543687939126944e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.389198091538583e-08</v>
+        <v>2.389198091538589e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.060286533428621e-08</v>
+        <v>2.060286533428635e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>2.060286533428621e-08</v>
+        <v>2.060286533428635e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.94395214468293e-08</v>
+        <v>2.943952144682943e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.353514756821365e-08</v>
+        <v>2.353514756821376e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.060286533428621e-08</v>
+        <v>2.060286533428635e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.273929686508656e-08</v>
+        <v>2.273929686508668e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>3.080763979198799e-08</v>
+        <v>3.080763979198806e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>2.621492037660918e-08</v>
+        <v>2.621492037660921e-08</v>
       </c>
     </row>
     <row r="9">
@@ -2379,37 +2379,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.191159989865004e-08</v>
+        <v>2.191159989865005e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>1.671735875220063e-08</v>
+        <v>1.671735875220065e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>2.613870283681148e-08</v>
+        <v>2.613870283681156e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>2.125896390847602e-08</v>
+        <v>2.125896390847609e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.125896390847602e-08</v>
+        <v>2.125896390847609e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>3.051311818990378e-08</v>
+        <v>3.051311818990388e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.599763897575066e-08</v>
+        <v>2.599763897575071e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.125896390847602e-08</v>
+        <v>2.125896390847609e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.376590366584351e-08</v>
+        <v>2.376590366584357e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>3.112986629909064e-08</v>
+        <v>3.112986629909075e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.689358214727725e-08</v>
+        <v>2.689358214727726e-08</v>
       </c>
     </row>
   </sheetData>
@@ -2495,37 +2495,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.568434661975125e-08</v>
+        <v>5.568434661975119e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.23159025831373e-07</v>
+        <v>1.231590258313731e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>2.884712142985514e-07</v>
+        <v>2.884712142985515e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.549909921922568e-07</v>
+        <v>1.549909921922569e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.549909921922568e-07</v>
+        <v>1.549909921922569e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>2.350830719629512e-07</v>
+        <v>2.350830719629478e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>5.849268824354488e-07</v>
+        <v>5.849268824354491e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.549909921922568e-07</v>
+        <v>1.549909921922569e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>3.442199200409554e-07</v>
+        <v>3.442199200409544e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.769459599961466e-07</v>
+        <v>1.769459599961463e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>4.10667087922975e-07</v>
+        <v>4.106670879229748e-07</v>
       </c>
     </row>
     <row r="3">
@@ -2535,37 +2535,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.013130338153806e-09</v>
+        <v>9.013130338153803e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>8.081716409742766e-09</v>
+        <v>8.08171640974278e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>9.013130338153806e-09</v>
+        <v>9.013130338153803e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>8.698211915683034e-09</v>
+        <v>8.698211915682962e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>8.698211915683e-09</v>
+        <v>8.698211915682966e-09</v>
       </c>
       <c r="G3" t="n">
         <v>8.957248085565348e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>9.013130338153806e-09</v>
+        <v>9.013130338153803e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>8.728655077954023e-09</v>
+        <v>8.728655077954001e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>9.013130338153806e-09</v>
+        <v>9.013130338153803e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>9.013130338153806e-09</v>
+        <v>9.013130338153803e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>9.013130338153806e-09</v>
+        <v>9.013130338153803e-09</v>
       </c>
     </row>
     <row r="4">
@@ -2575,37 +2575,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.859316530283484e-08</v>
+        <v>2.368956564862891e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>2.327378672870793e-08</v>
+        <v>2.327378672870766e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>2.386929017417068e-08</v>
+        <v>2.386929017417021e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>2.214264097251462e-08</v>
+        <v>2.214264097251469e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>2.343597621196696e-08</v>
+        <v>2.343597621196692e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>2.363368339604046e-08</v>
+        <v>2.363368339604041e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>4.014354416296132e-08</v>
+        <v>4.014354416296125e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>3.830869004263502e-08</v>
+        <v>2.34050903884291e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>3.898877692734873e-08</v>
+        <v>3.89887769273487e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>2.365614794937039e-08</v>
+        <v>2.365614794937035e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>2.37783150768674e-08</v>
+        <v>2.377831507686739e-08</v>
       </c>
     </row>
     <row r="5">
@@ -2615,37 +2615,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.700301859810207e-08</v>
+        <v>4.700301859810201e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>4.684418293868201e-08</v>
+        <v>4.684418293868196e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>4.70006638650663e-08</v>
+        <v>4.700066386506623e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>4.675876626807619e-08</v>
+        <v>4.675876626807611e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>4.675876626807619e-08</v>
+        <v>4.675876626807611e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>4.694713634551359e-08</v>
+        <v>4.694713634551353e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>4.700301859810207e-08</v>
+        <v>4.700301859810201e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>4.671854333790223e-08</v>
+        <v>4.671854333790221e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>4.700301859810207e-08</v>
+        <v>4.700301859810201e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>4.700301859810207e-08</v>
+        <v>4.700301859810201e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>4.700301859810207e-08</v>
+        <v>4.700301859810201e-08</v>
       </c>
     </row>
     <row r="6">
@@ -2655,37 +2655,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.480499285168226e-07</v>
+        <v>1.480499285168223e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>2.386100706038749e-07</v>
+        <v>2.386100706038744e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>2.575085386167901e-07</v>
+        <v>2.575085386167894e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>2.136829030882836e-07</v>
+        <v>2.136829030882833e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.506646261997599e-07</v>
+        <v>1.506646261997596e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>2.386537717006543e-07</v>
+        <v>2.386537717006542e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>2.387096539532849e-07</v>
+        <v>2.387096539532845e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>2.384251786930429e-07</v>
+        <v>2.384251786930427e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>2.387274712001819e-07</v>
+        <v>2.387274712001818e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.463658775707851e-07</v>
+        <v>1.463658775707848e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>3.334113180272556e-07</v>
+        <v>3.334113180272546e-07</v>
       </c>
     </row>
     <row r="7">
@@ -2695,10 +2695,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.127873739168898e-07</v>
+        <v>1.127873739168899e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>1.423364596617638e-07</v>
+        <v>1.423364596617637e-07</v>
       </c>
       <c r="D7" t="n">
         <v>1.424953034233192e-07</v>
@@ -2713,19 +2713,19 @@
         <v>1.424394130685953e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>1.424952953211838e-07</v>
+        <v>1.424952953211837e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>1.42210820060984e-07</v>
+        <v>1.422108200609838e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>1.424952953211838e-07</v>
+        <v>1.424952953211837e-07</v>
       </c>
       <c r="K7" t="n">
         <v>1.05087717328066e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>1.424952953211838e-07</v>
+        <v>1.424952953211837e-07</v>
       </c>
     </row>
     <row r="8">
@@ -2738,10 +2738,10 @@
         <v>2.261066709133016e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>1.664195484885713e-08</v>
+        <v>1.664195484885712e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.315579825795743e-08</v>
+        <v>2.315579825795741e-08</v>
       </c>
       <c r="E8" t="n">
         <v>2.014171752483635e-08</v>
@@ -2750,22 +2750,22 @@
         <v>2.014171752483635e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.842863748024338e-08</v>
+        <v>2.842863748024333e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>1.778433528838874e-08</v>
+        <v>1.778433528838871e-08</v>
       </c>
       <c r="I8" t="n">
         <v>2.014171752483635e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>1.894704909631122e-08</v>
+        <v>1.894704909631124e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>2.985628521828299e-08</v>
+        <v>2.985628521828279e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>2.121774874418493e-08</v>
+        <v>2.121774874418491e-08</v>
       </c>
     </row>
     <row r="9">
@@ -2775,37 +2775,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.28886478406087e-08</v>
+        <v>2.288864784060868e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>1.703400709846604e-08</v>
+        <v>1.703400709846602e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>2.568228674305408e-08</v>
+        <v>2.568228674305407e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>2.092130405786419e-08</v>
+        <v>2.092130405786422e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.092130405786419e-08</v>
+        <v>2.092130405786422e-08</v>
       </c>
       <c r="G9" t="n">
         <v>3.010043370650627e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.350388648246187e-08</v>
+        <v>2.350388648246188e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.092130405786419e-08</v>
+        <v>2.092130405786422e-08</v>
       </c>
       <c r="J9" t="n">
         <v>2.208166840290695e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>3.078306427567998e-08</v>
+        <v>3.07830642756798e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.47405780022175e-08</v>
+        <v>2.474057800221747e-08</v>
       </c>
     </row>
   </sheetData>
@@ -2891,37 +2891,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.789617177504078e-08</v>
+        <v>5.789617177504079e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.267368563915145e-07</v>
+        <v>1.267368563915147e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.586140420965708e-07</v>
+        <v>1.58614042096571e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.483856296805617e-07</v>
+        <v>1.483856296805631e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.483856296805617e-07</v>
+        <v>1.483856296805631e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.460459815975508e-07</v>
+        <v>1.460459815975532e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.81863491790448e-07</v>
+        <v>1.818634917904482e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.483856296805617e-07</v>
+        <v>1.483856296805631e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>2.026539955857038e-07</v>
+        <v>2.026539955857039e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.252605877348063e-07</v>
+        <v>1.252605877348062e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.789737172727348e-07</v>
+        <v>1.789737172727349e-07</v>
       </c>
     </row>
     <row r="3">
@@ -2931,37 +2931,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.994051808659019e-09</v>
+        <v>8.994051808659057e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>8.159448110272261e-09</v>
+        <v>8.159448110272272e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>8.994051808659019e-09</v>
+        <v>8.994051808659057e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>8.792010769437856e-09</v>
+        <v>8.792010769437869e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>8.792010769437879e-09</v>
+        <v>8.792010769437869e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>8.941214494305605e-09</v>
+        <v>8.941214494305614e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>8.994051808659019e-09</v>
+        <v>8.994051808659057e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>8.729033447270947e-09</v>
+        <v>8.729033447270969e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>8.994051808659019e-09</v>
+        <v>8.994051808659057e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>8.994051808659019e-09</v>
+        <v>8.994051808659057e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>8.994051808659019e-09</v>
+        <v>8.994051808659057e-09</v>
       </c>
     </row>
     <row r="4">
@@ -2971,37 +2971,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.259383261907467e-08</v>
+        <v>2.25938326190747e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>2.231910516448856e-08</v>
+        <v>2.231910516448889e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>3.704493367207364e-08</v>
+        <v>2.262668579918808e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>2.12519975261732e-08</v>
+        <v>2.125199752617319e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>2.237125063794668e-08</v>
+        <v>2.237125063794667e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>2.254099530472127e-08</v>
+        <v>3.647706486822266e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>3.812528958922419e-08</v>
+        <v>3.812528958922428e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>2.232881425768664e-08</v>
+        <v>3.626488382118799e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>2.343456893834264e-08</v>
+        <v>2.343456893834268e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>2.256959396915635e-08</v>
+        <v>2.256959396915638e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>2.261245099405167e-08</v>
+        <v>2.261245099405164e-08</v>
       </c>
     </row>
     <row r="5">
@@ -3011,37 +3011,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.518617543446472e-08</v>
+        <v>4.518617543446479e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>4.503121424802522e-08</v>
+        <v>4.50312142480253e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>4.518394461757151e-08</v>
+        <v>4.518394461757159e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>4.497357167865479e-08</v>
+        <v>4.497357167865496e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>4.497357167865479e-08</v>
+        <v>4.497357167865496e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>4.513333812011129e-08</v>
+        <v>4.513333812011137e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>4.518617543446472e-08</v>
+        <v>4.518617543446479e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>4.492115707307656e-08</v>
+        <v>4.49211570730767e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>4.518617543446472e-08</v>
+        <v>4.518617543446479e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>4.518617543446472e-08</v>
+        <v>4.518617543446479e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>4.518617543446472e-08</v>
+        <v>4.518617543446479e-08</v>
       </c>
     </row>
     <row r="6">
@@ -3051,37 +3051,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.408540978176051e-07</v>
+        <v>1.408540978176053e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>2.268365117375776e-07</v>
+        <v>2.268365117375775e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>2.447682833306106e-07</v>
+        <v>2.447682833306104e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>2.031797608065282e-07</v>
+        <v>2.03179760806528e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.433498857023222e-07</v>
+        <v>1.43349885702322e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>2.268687842819688e-07</v>
+        <v>2.268687842819687e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>2.269216215964443e-07</v>
+        <v>2.269216215964439e-07</v>
       </c>
       <c r="I6" t="n">
         <v>2.26656603234934e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>2.269385363430786e-07</v>
+        <v>2.269385363430783e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.39255349375055e-07</v>
+        <v>1.392553493750551e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>3.168263470444907e-07</v>
+        <v>3.168263470444903e-07</v>
       </c>
     </row>
     <row r="7">
@@ -3091,37 +3091,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.004161055217239e-07</v>
+        <v>1.00416105521724e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>1.26538998140596e-07</v>
+        <v>1.265389981405962e-07</v>
       </c>
       <c r="D7" t="n">
         <v>1.266939693517613e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>1.56753014401871e-07</v>
+        <v>1.567530144018712e-07</v>
       </c>
       <c r="F7" t="n">
         <v>1.264289235762501e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>1.26641122012682e-07</v>
+        <v>1.266411220126821e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>1.266939593270354e-07</v>
+        <v>1.266939593270355e-07</v>
       </c>
       <c r="I7" t="n">
         <v>1.264289409656474e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>1.266939593270354e-07</v>
+        <v>1.266939593270355e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>1.114684718475047e-07</v>
+        <v>9.360544820764327e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.266939593270354e-07</v>
+        <v>1.266939593270355e-07</v>
       </c>
     </row>
     <row r="8">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.290197221119507e-08</v>
+        <v>2.290197221119512e-08</v>
       </c>
       <c r="C8" t="n">
         <v>1.644873169808629e-08</v>
@@ -3140,28 +3140,28 @@
         <v>2.603986584655465e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.022857521620284e-08</v>
+        <v>2.022857521620285e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>2.022857521620284e-08</v>
+        <v>2.022857521620285e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>3.021943691883728e-08</v>
+        <v>3.021943691883734e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.587912052676841e-08</v>
+        <v>2.587912052676843e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.022857521620284e-08</v>
+        <v>2.022857521620285e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.177260180295053e-08</v>
+        <v>2.177260180295052e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>3.079147215966456e-08</v>
+        <v>3.079147215966484e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>2.566288942727327e-08</v>
+        <v>2.566288942727328e-08</v>
       </c>
     </row>
     <row r="9">
@@ -3171,37 +3171,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.324088509012204e-08</v>
+        <v>2.324088509012205e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>1.697802482746271e-08</v>
+        <v>1.697802482746272e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>2.690309097365055e-08</v>
+        <v>2.690309097365059e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>2.102523065312197e-08</v>
+        <v>2.102523065312199e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.102523065312197e-08</v>
+        <v>2.102523065312199e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>3.081178661747511e-08</v>
+        <v>3.081178661747512e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.683958915205968e-08</v>
+        <v>2.683958915205972e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.102523065312197e-08</v>
+        <v>2.102523065312199e-08</v>
       </c>
       <c r="J9" t="n">
         <v>2.320857212561469e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>3.110571819925574e-08</v>
+        <v>3.110571819925611e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.655295179992501e-08</v>
+        <v>2.655295179992504e-08</v>
       </c>
     </row>
   </sheetData>
@@ -3287,37 +3287,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.069204458324922e-08</v>
+        <v>6.069204458324923e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.334090384506792e-07</v>
+        <v>1.334090384506791e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.589665275263018e-07</v>
+        <v>1.589665275263016e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.439869145618814e-07</v>
+        <v>1.439869145618799e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.439869145618814e-07</v>
+        <v>1.439869145618799e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.432637007950108e-07</v>
+        <v>1.432637007950096e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.671591230527353e-07</v>
+        <v>1.671591230527352e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.439869145618814e-07</v>
+        <v>1.439869145618799e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>1.693613954624686e-07</v>
+        <v>1.693613954624687e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.254793386931371e-07</v>
+        <v>1.254793386931369e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.571612068175301e-07</v>
+        <v>1.571612068175299e-07</v>
       </c>
     </row>
     <row r="3">
@@ -3327,37 +3327,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.497418079192043e-09</v>
+        <v>9.497418079192038e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>8.653137007384477e-09</v>
+        <v>8.653137007384475e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>9.497418079192043e-09</v>
+        <v>9.497418079192038e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>9.290519439811919e-09</v>
+        <v>9.290519439811851e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>9.290519439811904e-09</v>
+        <v>9.290519439811845e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>9.444449049762872e-09</v>
+        <v>9.444449049764758e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>9.497418079192043e-09</v>
+        <v>9.497418079192038e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>9.231718040933639e-09</v>
+        <v>9.231718040937217e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>9.497418079192043e-09</v>
+        <v>9.497418079192038e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>9.497418079192043e-09</v>
+        <v>9.497418079192038e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>9.497418079192043e-09</v>
+        <v>9.497418079192038e-09</v>
       </c>
     </row>
     <row r="4">
@@ -3367,37 +3367,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.732969641790004e-08</v>
+        <v>3.732969641790005e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>2.282329883655431e-08</v>
+        <v>2.282329883655417e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>2.311626560772086e-08</v>
+        <v>2.311626560772087e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>2.171859819323e-08</v>
+        <v>2.171859819323013e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>2.286328888984107e-08</v>
+        <v>2.286328888984104e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>3.727672738847088e-08</v>
+        <v>3.727672738847082e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>3.920868544049044e-08</v>
+        <v>3.920868544049036e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>2.282314659099204e-08</v>
+        <v>2.282314659099195e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>3.777048041669808e-08</v>
+        <v>3.777048041669804e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>2.306819439215691e-08</v>
+        <v>2.306819439215674e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>2.310060406840376e-08</v>
+        <v>2.310060406840377e-08</v>
       </c>
     </row>
     <row r="5">
@@ -3410,25 +3410,25 @@
         <v>4.609885196558803e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>4.594374277471426e-08</v>
+        <v>4.59437427747142e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>4.609661777722316e-08</v>
+        <v>4.609661777722309e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>4.588770997006114e-08</v>
+        <v>4.588770997006104e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>4.588770997006114e-08</v>
+        <v>4.588770997006104e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>4.604588293615887e-08</v>
+        <v>4.604588293615884e-08</v>
       </c>
       <c r="H5" t="n">
         <v>4.609885196558803e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>4.583315192732964e-08</v>
+        <v>4.583315192732956e-08</v>
       </c>
       <c r="J5" t="n">
         <v>4.609885196558803e-08</v>
@@ -3447,37 +3447,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.420528585110759e-07</v>
+        <v>1.420528585110762e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>2.286573136670217e-07</v>
+        <v>2.286573136670218e-07</v>
       </c>
       <c r="D6" t="n">
         <v>2.467156036127836e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>2.048302186395895e-07</v>
+        <v>2.048302186395894e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.445688984001636e-07</v>
+        <v>1.445688984001635e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>2.286874120593963e-07</v>
+        <v>2.286874120593964e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>2.287403810890292e-07</v>
+        <v>2.287403810890293e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>2.284746810505668e-07</v>
+        <v>2.284746810505669e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>2.287574176810309e-07</v>
+        <v>2.28757417681031e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.404425932726324e-07</v>
+        <v>1.404425932726326e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>3.192927471244164e-07</v>
+        <v>3.192927471244169e-07</v>
       </c>
     </row>
     <row r="7">
@@ -3487,7 +3487,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.68071102519318e-08</v>
+        <v>9.680711025193178e-08</v>
       </c>
       <c r="C7" t="n">
         <v>1.218701019940346e-07</v>
@@ -3499,10 +3499,10 @@
         <v>1.508606526332239e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>1.217594939025193e-07</v>
+        <v>1.217594939025194e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>1.219722421554794e-07</v>
+        <v>1.219722421554793e-07</v>
       </c>
       <c r="H7" t="n">
         <v>1.220252111849084e-07</v>
@@ -3514,7 +3514,7 @@
         <v>1.220252111849084e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>1.074137487807054e-07</v>
+        <v>1.06820942877648e-07</v>
       </c>
       <c r="L7" t="n">
         <v>1.220252111849084e-07</v>
@@ -3527,37 +3527,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.372613791644335e-08</v>
+        <v>2.372613791644332e-08</v>
       </c>
       <c r="C8" t="n">
         <v>1.649508664794364e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.63434157813624e-08</v>
+        <v>2.634341578136238e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.064472868031311e-08</v>
+        <v>2.06447286803131e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>2.064472868031311e-08</v>
+        <v>2.06447286803131e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>3.058814775445413e-08</v>
+        <v>3.058814775445411e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.650699592877283e-08</v>
+        <v>2.650699592877281e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.064472868031311e-08</v>
+        <v>2.06447286803131e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.302025911146009e-08</v>
+        <v>2.302025911146006e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>3.104091476214876e-08</v>
+        <v>3.104091476214868e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>2.640508706035525e-08</v>
+        <v>2.640508706035524e-08</v>
       </c>
     </row>
     <row r="9">
@@ -3567,37 +3567,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.408805657127598e-08</v>
+        <v>2.408805657127596e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>1.711264045684281e-08</v>
+        <v>1.711264045684282e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>2.720434557969301e-08</v>
+        <v>2.720434557969297e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>2.137106009057112e-08</v>
+        <v>2.137106009057111e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.137106009057112e-08</v>
+        <v>2.137106009057111e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>3.113427316238885e-08</v>
+        <v>3.113427316238884e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.72726398061668e-08</v>
+        <v>2.727263980616678e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.137106009057112e-08</v>
+        <v>2.137106009057111e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.398903814788252e-08</v>
+        <v>2.39890381478825e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>3.135183042448965e-08</v>
+        <v>3.135183042448958e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.701562034533598e-08</v>
+        <v>2.701562034533597e-08</v>
       </c>
     </row>
   </sheetData>
@@ -3683,37 +3683,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.738631250499759e-08</v>
+        <v>5.738631250499752e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.261642562957886e-07</v>
+        <v>1.261642562957887e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.786042160176894e-07</v>
+        <v>1.786042160176886e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.558915780655651e-07</v>
+        <v>1.558915780655653e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.558915780655651e-07</v>
+        <v>1.558915780655653e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.72495654921208e-07</v>
+        <v>1.724956549212001e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>5.106528671015375e-07</v>
+        <v>5.106528671015374e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.558915780655651e-07</v>
+        <v>1.558915780655653e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>1.639730118116256e-07</v>
+        <v>1.639730118116251e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.325242181666209e-07</v>
+        <v>1.325242181666201e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>3.587730042488144e-07</v>
+        <v>3.587730042488136e-07</v>
       </c>
     </row>
     <row r="3">
@@ -3723,37 +3723,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.977292411894813e-09</v>
+        <v>8.977292411894232e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>8.093550481976666e-09</v>
+        <v>8.093550481976658e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>8.977292411894813e-09</v>
+        <v>8.977292411894232e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>8.743228978306563e-09</v>
+        <v>8.743228978306607e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>8.743228978306563e-09</v>
+        <v>8.743228978306606e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>8.923655271241988e-09</v>
+        <v>8.923655271241615e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>8.977292411894813e-09</v>
+        <v>8.977292411894232e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>8.707092167157687e-09</v>
+        <v>8.707092167158065e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>8.977292411894813e-09</v>
+        <v>8.977292411894232e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>8.977292411894813e-09</v>
+        <v>8.977292411894232e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>8.977292411894813e-09</v>
+        <v>8.977292411894232e-09</v>
       </c>
     </row>
     <row r="4">
@@ -3763,37 +3763,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.813015304740475e-08</v>
+        <v>2.341804155671857e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>2.310128307357701e-08</v>
+        <v>2.31012830735772e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>2.345902220297694e-08</v>
+        <v>2.345902220297546e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>2.199121912616134e-08</v>
+        <v>2.19912191261614e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>2.318943770001748e-08</v>
+        <v>2.318943770001751e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>3.807651590675155e-08</v>
+        <v>3.807651590675091e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>3.965976638268904e-08</v>
+        <v>3.965976638268825e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>2.314784131198241e-08</v>
+        <v>3.7859952802668e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>3.850966127211861e-08</v>
+        <v>3.850966127211743e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>2.33755973501193e-08</v>
+        <v>2.337559735011878e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>2.349055948221916e-08</v>
+        <v>2.349055948221897e-08</v>
       </c>
     </row>
     <row r="5">
@@ -3803,37 +3803,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.688711736702643e-08</v>
+        <v>4.688711736702597e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>4.673124642832891e-08</v>
+        <v>4.673124642832887e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>4.688476276604585e-08</v>
+        <v>4.688476276604538e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>4.666550926152752e-08</v>
+        <v>4.666550926152756e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>4.666550926152752e-08</v>
+        <v>4.666550926152756e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>4.683348022637329e-08</v>
+        <v>4.683348022637279e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>4.688711736702643e-08</v>
+        <v>4.688711736702597e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>4.661691712228967e-08</v>
+        <v>4.661691712228968e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>4.688711736702643e-08</v>
+        <v>4.688711736702597e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>4.688711736702643e-08</v>
+        <v>4.688711736702597e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>4.688711736702643e-08</v>
+        <v>4.688711736702597e-08</v>
       </c>
     </row>
     <row r="6">
@@ -3843,37 +3843,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.477595739278933e-07</v>
+        <v>1.477595739278919e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>2.381696425212965e-07</v>
+        <v>2.38169642521296e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>2.570237934152178e-07</v>
+        <v>2.57023793415217e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>2.132969771822796e-07</v>
+        <v>2.132969771822798e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.503884355723883e-07</v>
+        <v>1.503884355723886e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>2.382046570770214e-07</v>
+        <v>2.382046570770212e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>2.382582942177156e-07</v>
+        <v>2.38258294217716e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>2.379880939729376e-07</v>
+        <v>2.379880939729378e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>2.382760798225355e-07</v>
+        <v>2.38276079822535e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.460785137351096e-07</v>
+        <v>1.460785137351098e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>3.327917749530331e-07</v>
+        <v>3.327917749530343e-07</v>
       </c>
     </row>
     <row r="7">
@@ -3883,37 +3883,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.113902188815746e-07</v>
+        <v>1.113902188815742e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>1.405661012288734e-07</v>
+        <v>1.405661012288737e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>1.407219790428298e-07</v>
+        <v>1.407219790428296e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>1.742999712056438e-07</v>
+        <v>1.742999712056441e-07</v>
       </c>
       <c r="F7" t="n">
         <v>1.404517492902817e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>1.406683350269179e-07</v>
+        <v>1.406683350269177e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>1.40721972167571e-07</v>
+        <v>1.407219721675708e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>1.404517719228342e-07</v>
+        <v>1.404517719228346e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>1.40721972167571e-07</v>
+        <v>1.407219721675708e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>1.230375359474749e-07</v>
+        <v>1.237270420106893e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>1.40721972167571e-07</v>
+        <v>1.407219721675709e-07</v>
       </c>
     </row>
     <row r="8">
@@ -3923,37 +3923,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.287112654032403e-08</v>
+        <v>2.287112654032366e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>1.664758663958909e-08</v>
+        <v>1.66475866395891e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.563199562472075e-08</v>
+        <v>2.563199562472052e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.006893610044932e-08</v>
+        <v>2.006893610044935e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>2.006893610044932e-08</v>
+        <v>2.006893610044935e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.973065588545586e-08</v>
+        <v>2.973065588545567e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>1.923544636616546e-08</v>
+        <v>1.923544636616526e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.006893610044932e-08</v>
+        <v>2.006893610044935e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.262957446913053e-08</v>
+        <v>2.262957446913073e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>3.067405552453598e-08</v>
+        <v>3.06740555245357e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>2.217318614766829e-08</v>
+        <v>2.217318614766807e-08</v>
       </c>
     </row>
     <row r="9">
@@ -3963,37 +3963,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.316677956213482e-08</v>
+        <v>2.316677956213431e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>1.707897708546274e-08</v>
+        <v>1.707897708546276e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>2.665503773239663e-08</v>
+        <v>2.665503773239602e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>2.086241549133841e-08</v>
+        <v>2.086241549133844e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.086241549133841e-08</v>
+        <v>2.086241549133844e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>3.057226657792535e-08</v>
+        <v>3.057226657792522e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.405777955393774e-08</v>
+        <v>2.40577795539371e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.086241549133841e-08</v>
+        <v>2.086241549133844e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.342343731337357e-08</v>
+        <v>2.342343731337327e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>3.099861568366512e-08</v>
+        <v>3.099861568366497e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.5082414092016e-08</v>
+        <v>2.508241409201582e-08</v>
       </c>
     </row>
   </sheetData>
@@ -4079,37 +4079,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.033331019700235e-08</v>
+        <v>6.033331019700192e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.291604636419105e-07</v>
+        <v>1.291604636419104e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.578151131609175e-07</v>
+        <v>1.578151131609173e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.482055430951923e-07</v>
+        <v>1.482055430951907e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.482055430951923e-07</v>
+        <v>1.482055430951907e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.419827576831431e-07</v>
+        <v>1.419827576831403e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.666587211162601e-07</v>
+        <v>1.666587211162593e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.482055430951923e-07</v>
+        <v>1.482055430951907e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>1.706503336172447e-07</v>
+        <v>1.706503336172444e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.274476829623211e-07</v>
+        <v>1.274476829623193e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.538927469835256e-07</v>
+        <v>1.53892746983525e-07</v>
       </c>
     </row>
     <row r="3">
@@ -4119,37 +4119,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.037677108281776e-09</v>
+        <v>9.037677108281328e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>8.207045655983602e-09</v>
+        <v>8.207045655983609e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>9.037677108281776e-09</v>
+        <v>9.037677108281328e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>8.887319301276846e-09</v>
+        <v>8.887319301276842e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>8.887319301276851e-09</v>
+        <v>8.887319301276844e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>8.984865587071714e-09</v>
+        <v>8.984865587071385e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>9.037677108281776e-09</v>
+        <v>9.037677108281328e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>8.772742536853528e-09</v>
+        <v>8.772742536853415e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>9.037677108281776e-09</v>
+        <v>9.037677108281328e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>9.037677108281776e-09</v>
+        <v>9.037677108281328e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>9.037677108281776e-09</v>
+        <v>9.037677108281328e-09</v>
       </c>
     </row>
     <row r="4">
@@ -4159,37 +4159,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.655298821689435e-08</v>
+        <v>2.258265765919125e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>2.23166586423007e-08</v>
+        <v>2.231665864230117e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>2.261807546420141e-08</v>
+        <v>2.261822041684664e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>2.125229382559151e-08</v>
+        <v>2.125229382559146e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>2.236288611142956e-08</v>
+        <v>2.236288611142954e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>2.252984613798125e-08</v>
+        <v>2.252984613798119e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>3.813338342295997e-08</v>
+        <v>3.813338342295985e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>2.231772308776324e-08</v>
+        <v>3.628805364546617e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>2.341168290311638e-08</v>
+        <v>3.693121661874563e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>2.256935095675754e-08</v>
+        <v>2.256935095675748e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>2.259314767481488e-08</v>
+        <v>2.25931476748148e-08</v>
       </c>
     </row>
     <row r="5">
@@ -4199,37 +4199,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.532271005381602e-08</v>
+        <v>4.53227100538159e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>4.516806821674411e-08</v>
+        <v>4.516806821674414e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>4.53204803970811e-08</v>
+        <v>4.532048039708097e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>4.512429015255757e-08</v>
+        <v>4.512429015255766e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>4.512429015255757e-08</v>
+        <v>4.512429015255766e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>4.526989853260601e-08</v>
+        <v>4.526989853260587e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>4.532271005381602e-08</v>
+        <v>4.53227100538159e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>4.50577754823879e-08</v>
+        <v>4.505777548238799e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>4.532271005381602e-08</v>
+        <v>4.53227100538159e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>4.532271005381602e-08</v>
+        <v>4.53227100538159e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>4.532271005381602e-08</v>
+        <v>4.53227100538159e-08</v>
       </c>
     </row>
     <row r="6">
@@ -4239,37 +4239,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.409389165611386e-07</v>
+        <v>1.409389165611378e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>2.269913005625041e-07</v>
+        <v>2.269913005625036e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>2.449209138913154e-07</v>
+        <v>2.449209138913149e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>2.033175293774789e-07</v>
+        <v>2.03317529377479e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.434449792771519e-07</v>
+        <v>1.434449792771512e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>2.27009794347513e-07</v>
+        <v>2.270097943475111e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>2.270626058688431e-07</v>
+        <v>2.270626058688428e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>2.267976712972948e-07</v>
+        <v>2.267976712972939e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>2.270795316536873e-07</v>
+        <v>2.270795316536867e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.393391248150453e-07</v>
+        <v>1.393391248150445e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>3.170260009083462e-07</v>
+        <v>3.170260009083445e-07</v>
       </c>
     </row>
     <row r="7">
@@ -4279,37 +4279,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.003951023793662e-07</v>
+        <v>1.00395102379366e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>1.265134949651136e-07</v>
+        <v>1.265134949651132e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>1.266681468758779e-07</v>
+        <v>1.266681468758775e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>1.567217145354635e-07</v>
+        <v>1.567217145354631e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>1.26403185072901e-07</v>
+        <v>1.264031850729008e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>1.266153252809752e-07</v>
+        <v>1.266153252809748e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>1.266681368021854e-07</v>
+        <v>1.266681368021849e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>1.26403202230757e-07</v>
+        <v>1.264032022307569e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>1.266681368021854e-07</v>
+        <v>1.266681368021849e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>9.358569413291641e-08</v>
+        <v>1.114454417123927e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>1.266681368021854e-07</v>
+        <v>1.266681368021849e-07</v>
       </c>
     </row>
     <row r="8">
@@ -4319,34 +4319,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.654847493938218e-08</v>
+        <v>2.654847493938213e-08</v>
       </c>
       <c r="C8" t="n">
         <v>1.665370195708175e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.606525858817166e-08</v>
+        <v>2.606525858817164e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.033729599802989e-08</v>
+        <v>2.03372959980299e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>2.033729599802989e-08</v>
+        <v>2.03372959980299e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>3.070625352187144e-08</v>
+        <v>3.070625352187141e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.621222898572616e-08</v>
+        <v>2.621222898572614e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.033729599802989e-08</v>
+        <v>2.03372959980299e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.24977657545115e-08</v>
+        <v>2.249776575451139e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>3.102012155249061e-08</v>
+        <v>3.102012155249082e-08</v>
       </c>
       <c r="L8" t="n">
         <v>2.621250746000013e-08</v>
@@ -4359,37 +4359,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.686388348431079e-08</v>
+        <v>2.68638834843107e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>1.721331068907124e-08</v>
+        <v>1.721331068907125e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>2.691737180767785e-08</v>
+        <v>2.691737180767784e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>2.11303115145252e-08</v>
+        <v>2.113031151452518e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.11303115145252e-08</v>
+        <v>2.113031151452518e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>3.12359666942609e-08</v>
+        <v>3.123596669426085e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.697889695087583e-08</v>
+        <v>2.697889695087581e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.11303115145252e-08</v>
+        <v>2.113031151452518e-08</v>
       </c>
       <c r="J9" t="n">
         <v>2.349483096576666e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>3.136198925272504e-08</v>
+        <v>3.136198925272503e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.67887932123844e-08</v>
+        <v>2.678879321238432e-08</v>
       </c>
     </row>
   </sheetData>
@@ -4475,31 +4475,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.111903997314091e-08</v>
+        <v>6.111903997314107e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.328120934059802e-07</v>
+        <v>1.3281209340598e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.563187940029604e-07</v>
+        <v>1.563187940029605e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.442901161717175e-07</v>
+        <v>1.442901161717174e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.442901161717175e-07</v>
+        <v>1.442901161717174e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.427152915242514e-07</v>
+        <v>1.427152915242505e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.667322031765972e-07</v>
+        <v>1.667322031765974e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.442901161717175e-07</v>
+        <v>1.442901161717174e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>1.728738076666115e-07</v>
+        <v>1.728738076666116e-07</v>
       </c>
       <c r="K2" t="n">
         <v>1.274596436900415e-07</v>
@@ -4515,37 +4515,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.461285196389923e-09</v>
+        <v>9.461285196390039e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>8.619841160666468e-09</v>
+        <v>8.619841160666423e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>9.461285196389923e-09</v>
+        <v>9.461285196390039e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>9.310240514965673e-09</v>
+        <v>9.310240514965779e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>9.310240514965621e-09</v>
+        <v>9.310240514965789e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>9.40771301712454e-09</v>
+        <v>9.407713017124708e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>9.461285196389923e-09</v>
+        <v>9.461285196390039e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>9.191479615234677e-09</v>
+        <v>9.191479615234814e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>9.461285196389923e-09</v>
+        <v>9.461285196390051e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>9.461285196389923e-09</v>
+        <v>9.461285196390039e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>9.461285196389923e-09</v>
+        <v>9.461285196390039e-09</v>
       </c>
     </row>
     <row r="4">
@@ -4555,37 +4555,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.720533210593093e-08</v>
+        <v>2.297638961903812e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>2.271033342177335e-08</v>
+        <v>2.271033342177411e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>2.300095169421829e-08</v>
+        <v>2.300095169421832e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>2.161903234254622e-08</v>
+        <v>2.16190323425463e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>2.275052394132247e-08</v>
+        <v>2.275052394132241e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>3.715175992666551e-08</v>
+        <v>3.715175992666559e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>3.903877344542253e-08</v>
+        <v>3.903877344542261e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>2.270658403788289e-08</v>
+        <v>3.693552652477584e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>3.763724380268096e-08</v>
+        <v>2.381336226462527e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>2.295971217182309e-08</v>
+        <v>2.29597121718231e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>2.299142276543783e-08</v>
+        <v>2.299142276543762e-08</v>
       </c>
     </row>
     <row r="5">
@@ -4595,37 +4595,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.612863248835893e-08</v>
+        <v>4.612863248835899e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>4.597362658890317e-08</v>
+        <v>4.597362658890315e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>4.612639897726407e-08</v>
+        <v>4.612639897726415e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>4.593058664229185e-08</v>
+        <v>4.593058664229198e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>4.593058664229185e-08</v>
+        <v>4.593058664229198e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>4.607506030909356e-08</v>
+        <v>4.607506030909353e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>4.612863248835893e-08</v>
+        <v>4.612863248835899e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>4.585882690720368e-08</v>
+        <v>4.58588269072037e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>4.612863248835893e-08</v>
+        <v>4.612863248835899e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>4.612863248835893e-08</v>
+        <v>4.612863248835899e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>4.612863248835893e-08</v>
+        <v>4.612863248835899e-08</v>
       </c>
     </row>
     <row r="6">
@@ -4635,37 +4635,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.419948290111217e-07</v>
+        <v>1.41994829011122e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>2.285977087205138e-07</v>
+        <v>2.285977087205141e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>2.466357006830261e-07</v>
+        <v>2.466357006830266e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>2.04769621397673e-07</v>
+        <v>2.047696213976735e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.445164503228201e-07</v>
+        <v>1.445164503228202e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>2.286106626150996e-07</v>
+        <v>2.286106626150997e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>2.286642347945655e-07</v>
+        <v>2.286642347945656e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>2.283944292132096e-07</v>
+        <v>2.283944292132095e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>2.286812678269321e-07</v>
+        <v>2.286812678269325e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.403849003013545e-07</v>
+        <v>1.403849003013546e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>3.191976763239827e-07</v>
+        <v>3.191976763239832e-07</v>
       </c>
     </row>
     <row r="7">
@@ -4675,34 +4675,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.67456643343057e-08</v>
+        <v>9.674566433430578e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.217999292053361e-07</v>
+        <v>1.217999292053362e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>1.219549453008708e-07</v>
+        <v>1.219549453008707e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>1.507760812151516e-07</v>
+        <v>1.507760812151515e-07</v>
       </c>
       <c r="F7" t="n">
         <v>1.216851123462067e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>1.219013629255266e-07</v>
+        <v>1.219013629255264e-07</v>
       </c>
       <c r="H7" t="n">
         <v>1.219549351047919e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>1.216851295236367e-07</v>
+        <v>1.216851295236369e-07</v>
       </c>
       <c r="J7" t="n">
         <v>1.219549351047919e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>1.06755990574761e-07</v>
+        <v>1.067559905747611e-07</v>
       </c>
       <c r="L7" t="n">
         <v>1.219549351047919e-07</v>
@@ -4715,37 +4715,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.684815421686174e-08</v>
+        <v>3.684815421686165e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>1.681873717910692e-08</v>
+        <v>1.681873717910693e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.634205235837126e-08</v>
+        <v>2.634205235837123e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.062068181074966e-08</v>
+        <v>2.062068181074977e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>2.062068181074966e-08</v>
+        <v>2.062068181074977e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>3.177208053096561e-08</v>
+        <v>3.177208053096557e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.645033083915087e-08</v>
+        <v>2.645033083915091e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.062068181074966e-08</v>
+        <v>2.062068181074977e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.282830608994452e-08</v>
+        <v>2.282830608994456e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>3.111450015427359e-08</v>
+        <v>3.111450015427325e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>2.639010104952511e-08</v>
+        <v>2.639010104952504e-08</v>
       </c>
     </row>
     <row r="9">
@@ -4758,34 +4758,34 @@
         <v>3.701112117825852e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>1.742363964092624e-08</v>
+        <v>1.742363964092621e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>2.716649483939527e-08</v>
+        <v>2.716649483939526e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>2.135245855419477e-08</v>
+        <v>2.13524585541948e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.135245855419477e-08</v>
+        <v>2.135245855419479e-08</v>
       </c>
       <c r="G9" t="n">
         <v>3.229293896020993e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.721225902431235e-08</v>
+        <v>2.721225902431243e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.135245855419477e-08</v>
+        <v>2.13524585541948e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.384781582623171e-08</v>
+        <v>2.384781582623174e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>3.145280109549726e-08</v>
+        <v>3.145280109549704e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.699499844888738e-08</v>
+        <v>2.699499844888733e-08</v>
       </c>
     </row>
   </sheetData>
@@ -4871,13 +4871,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.234229349537081e-07</v>
+        <v>4.234229349537073e-07</v>
       </c>
       <c r="C2" t="n">
         <v>2.134811764927823e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>5.892763430680225e-07</v>
+        <v>5.89276343068023e-07</v>
       </c>
       <c r="E2" t="n">
         <v>2.134811764927823e-07</v>
@@ -4886,22 +4886,22 @@
         <v>2.134811764927823e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>4.435196110098142e-07</v>
+        <v>4.435196110098139e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.217273930828024e-06</v>
+        <v>1.217273930828027e-06</v>
       </c>
       <c r="I2" t="n">
         <v>2.134811764927823e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>3.200750541785523e-07</v>
+        <v>3.200750541785516e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>2.838941568459395e-07</v>
+        <v>2.838941568459404e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>2.965736302165971e-07</v>
+        <v>2.965736302165965e-07</v>
       </c>
     </row>
     <row r="3">
@@ -4911,37 +4911,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.006222992302534e-08</v>
+        <v>1.006222992302514e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>9.353377117392848e-09</v>
+        <v>9.353377117392571e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>1.006222992302534e-08</v>
+        <v>1.006222992302514e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>9.497341697890632e-09</v>
+        <v>9.497341697890422e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>9.49734169789063e-09</v>
+        <v>9.49734169789042e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>1.000166908947269e-08</v>
+        <v>1.000166908947243e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.006222992302534e-08</v>
+        <v>1.006222992302514e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>9.74769386525523e-09</v>
+        <v>9.747693865255138e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>1.006222992302534e-08</v>
+        <v>1.006222992302514e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.006222992302534e-08</v>
+        <v>1.006222992302514e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.006222992302534e-08</v>
+        <v>1.006222992302514e-08</v>
       </c>
     </row>
     <row r="4">
@@ -4951,37 +4951,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.208948321227886e-08</v>
+        <v>4.208948321227869e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>2.494232793746507e-08</v>
+        <v>2.49423279374647e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>2.612958154645951e-08</v>
+        <v>2.612958154645923e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>2.377891105092318e-08</v>
+        <v>2.377891105092296e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>2.531739660952816e-08</v>
+        <v>2.53173966095279e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>2.558193245982661e-08</v>
+        <v>4.202892237872593e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>2.595867526938397e-08</v>
+        <v>4.288751831035014e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>4.177494715450892e-08</v>
+        <v>4.177494715450864e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>4.22238038016004e-08</v>
+        <v>4.222380380160029e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>2.550777789690263e-08</v>
+        <v>2.550777789690239e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>2.604747631641994e-08</v>
+        <v>2.604747631641972e-08</v>
       </c>
     </row>
     <row r="5">
@@ -4991,37 +4991,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.898922576786795e-08</v>
+        <v>4.898922576786779e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>4.867468971009812e-08</v>
+        <v>4.867468971009783e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>4.898669201163749e-08</v>
+        <v>4.89866920116373e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>4.866550490827714e-08</v>
+        <v>4.86655049082768e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>4.866550490827714e-08</v>
+        <v>4.86655049082768e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>4.892866493431528e-08</v>
+        <v>4.892866493431511e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>4.898922576786795e-08</v>
+        <v>4.898922576786779e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>4.867468971009812e-08</v>
+        <v>4.867468971009783e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>4.898922576786795e-08</v>
+        <v>4.898922576786779e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>4.898922576786795e-08</v>
+        <v>4.898922576786779e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>4.898922576786795e-08</v>
+        <v>4.898922576786779e-08</v>
       </c>
     </row>
     <row r="6">
@@ -5031,34 +5031,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.518287846286138e-07</v>
+        <v>1.518287846286136e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>2.439234363061538e-07</v>
+        <v>2.439234363061542e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>2.633843964645995e-07</v>
+        <v>2.633843964645997e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>2.186517643805863e-07</v>
+        <v>2.186517643805865e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.544391097829537e-07</v>
+        <v>1.544391097829538e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>2.441648030200188e-07</v>
+        <v>2.441648030200184e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>2.442253638535719e-07</v>
+        <v>2.442253638535724e-07</v>
       </c>
       <c r="I6" t="n">
         <v>2.43910827795801e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>2.442435224421886e-07</v>
+        <v>2.442435224421889e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.50112470731812e-07</v>
+        <v>1.501124707318119e-07</v>
       </c>
       <c r="L6" t="n">
         <v>3.407413169428965e-07</v>
@@ -5071,37 +5071,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.203808919688885e-07</v>
+        <v>1.203808919688882e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>1.515852170297746e-07</v>
+        <v>1.515852170297743e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>1.518997573907557e-07</v>
+        <v>1.518997573907555e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>1.879572764225727e-07</v>
+        <v>1.879572764225724e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>1.515851834935035e-07</v>
+        <v>1.515851834935032e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>1.518391922539919e-07</v>
+        <v>1.518391922539916e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>1.518997530875445e-07</v>
+        <v>1.518997530875444e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>1.515852170297746e-07</v>
+        <v>1.515852170297743e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>1.518997530875445e-07</v>
+        <v>1.518997530875444e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>1.336376029811916e-07</v>
+        <v>1.336376029811915e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>1.518997530875445e-07</v>
+        <v>1.518997530875444e-07</v>
       </c>
     </row>
     <row r="8">
@@ -5111,37 +5111,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.268894242352146e-08</v>
+        <v>2.268894242352145e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.065423255746459e-08</v>
+        <v>2.065423255746462e-08</v>
       </c>
       <c r="D8" t="n">
         <v>1.901969431467376e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.065423255746459e-08</v>
+        <v>2.065423255746462e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>2.065423255746459e-08</v>
+        <v>2.065423255746462e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.253436118665522e-08</v>
+        <v>2.253436118665525e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>7.668146522624793e-09</v>
+        <v>7.668146522624764e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>2.065423255746459e-08</v>
+        <v>2.065423255746462e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.558619503508233e-08</v>
+        <v>2.558619503508232e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>2.608893109993474e-08</v>
+        <v>2.608893109993471e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>1.715521181338229e-09</v>
+        <v>2.636615787979193e-08</v>
       </c>
     </row>
     <row r="9">
@@ -5151,37 +5151,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.706223378239061e-08</v>
+        <v>2.706223378239063e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.211076040049775e-08</v>
+        <v>2.211076040049776e-08</v>
       </c>
       <c r="D9" t="n">
         <v>2.556808225260651e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>2.211076040049775e-08</v>
+        <v>2.211076040049776e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.211076040049775e-08</v>
+        <v>2.211076040049776e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.696170138998857e-08</v>
+        <v>2.696170138998855e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.096578313950795e-08</v>
+        <v>2.096578313950791e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.211076040049775e-08</v>
+        <v>2.211076040049776e-08</v>
       </c>
       <c r="J9" t="n">
         <v>2.824420928029907e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.844727083522514e-08</v>
+        <v>2.844727083522512e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>1.854182937365876e-08</v>
+        <v>2.85631601366121e-08</v>
       </c>
     </row>
   </sheetData>
@@ -5267,37 +5267,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.456017696048272e-07</v>
+        <v>3.45601769604827e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>2.377283877311911e-07</v>
+        <v>2.377283877311913e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>5.180537247560527e-07</v>
+        <v>5.180537247560496e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>2.377283877311911e-07</v>
+        <v>2.377283877311913e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>2.377283877311911e-07</v>
+        <v>2.377283877311913e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>4.046502396950909e-07</v>
+        <v>4.046502396950956e-07</v>
       </c>
       <c r="H2" t="n">
         <v>1.007982990251427e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>2.377283877311911e-07</v>
+        <v>2.377283877311913e-07</v>
       </c>
       <c r="J2" t="n">
         <v>2.567243069469364e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>2.635844236448979e-07</v>
+        <v>2.635844236448981e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.371299550376148e-06</v>
+        <v>3.118203593316165e-07</v>
       </c>
     </row>
     <row r="3">
@@ -5307,37 +5307,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.0100319587762e-08</v>
+        <v>1.010031958776196e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>9.482350927300369e-09</v>
+        <v>9.482350927300354e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>1.0100319587762e-08</v>
+        <v>1.010031958776197e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>9.613220854838692e-09</v>
+        <v>9.613220854838644e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>9.613220854838705e-09</v>
+        <v>9.613220854838646e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>1.004174299978067e-08</v>
+        <v>1.004174299978071e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.0100319587762e-08</v>
+        <v>1.010031958776197e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>9.798471367483559e-09</v>
+        <v>9.798471367483389e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>1.0100319587762e-08</v>
+        <v>1.010031958776197e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.0100319587762e-08</v>
+        <v>1.010031958776197e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.0100319587762e-08</v>
+        <v>1.010031958776197e-08</v>
       </c>
     </row>
     <row r="4">
@@ -5347,37 +5347,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.45635142730091e-08</v>
+        <v>3.993794114929232e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>2.39958022315446e-08</v>
+        <v>2.399580223154468e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>2.496357482429919e-08</v>
+        <v>2.496357482429851e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>2.29055906696714e-08</v>
+        <v>2.290559066967146e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>2.427714832756178e-08</v>
+        <v>2.427714832756174e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>2.450493768502788e-08</v>
+        <v>3.987936456131107e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>4.065013416896973e-08</v>
+        <v>4.065013416896954e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>2.426166605273051e-08</v>
+        <v>3.963609292901383e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>2.544187802584869e-08</v>
+        <v>4.007454195010343e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>2.444616244805357e-08</v>
+        <v>2.444616244805347e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>2.491526898142629e-08</v>
+        <v>2.491526898142635e-08</v>
       </c>
     </row>
     <row r="5">
@@ -5387,37 +5387,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.666352554911315e-08</v>
+        <v>4.666352554911311e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>4.636167732883456e-08</v>
+        <v>4.636167732883454e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>4.666115599700561e-08</v>
+        <v>4.666115599700551e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>4.635728855126728e-08</v>
+        <v>4.635728855126732e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>4.635728855126728e-08</v>
+        <v>4.635728855126732e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>4.660494896113191e-08</v>
+        <v>4.660494896113185e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>4.666352554911315e-08</v>
+        <v>4.666352554911313e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>4.636167732883456e-08</v>
+        <v>4.636167732883454e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>4.666352554911315e-08</v>
+        <v>4.666352554911313e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>4.666352554911315e-08</v>
+        <v>4.666352554911313e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>4.666352554911315e-08</v>
+        <v>4.666352554911313e-08</v>
       </c>
     </row>
     <row r="6">
@@ -5427,37 +5427,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.424979748110164e-07</v>
+        <v>1.42497974811016e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>2.285827347776294e-07</v>
+        <v>2.285827347778428e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>2.467783346201624e-07</v>
+        <v>2.467783346201622e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>2.04958765747052e-07</v>
+        <v>2.049587657470519e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.44932743321127e-07</v>
+        <v>1.449327433211268e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>2.288102079755725e-07</v>
+        <v>2.288102079755723e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>2.288687845635557e-07</v>
+        <v>2.288687845635552e-07</v>
       </c>
       <c r="I6" t="n">
         <v>2.285669363432748e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>2.288857589147854e-07</v>
+        <v>2.288857589147852e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.408935926758924e-07</v>
+        <v>1.408935926758919e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>3.190903175713331e-07</v>
+        <v>3.190903175713323e-07</v>
       </c>
     </row>
     <row r="7">
@@ -5470,34 +5470,34 @@
         <v>1.071177603570351e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>1.346245311617745e-07</v>
+        <v>1.346245311617741e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>1.349263846251033e-07</v>
+        <v>1.349263846251032e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>1.667150560839709e-07</v>
+        <v>1.667150560839704e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>1.346245019343208e-07</v>
+        <v>1.346245019343203e-07</v>
       </c>
       <c r="G7" t="n">
         <v>1.348678027940715e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>1.34926379382053e-07</v>
+        <v>1.349263793820526e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>1.346245311617745e-07</v>
+        <v>1.346245311617741e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>1.34926379382053e-07</v>
+        <v>1.349263793820526e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>9.991036284973223e-08</v>
+        <v>9.991036284973201e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.34926379382053e-07</v>
+        <v>1.349263793820526e-07</v>
       </c>
     </row>
     <row r="8">
@@ -5507,37 +5507,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.418689427310595e-08</v>
+        <v>2.418689427310598e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>1.993205436201283e-08</v>
+        <v>1.993205436201284e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>1.983235157702755e-08</v>
+        <v>1.983235157702767e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>1.993205436201283e-08</v>
+        <v>1.993205436201284e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>1.993205436201283e-08</v>
+        <v>1.993205436201284e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.285620174243459e-08</v>
+        <v>2.285620174243456e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>1.064135007491073e-08</v>
+        <v>1.064135007491075e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>1.993205436201283e-08</v>
+        <v>1.993205436201284e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.672637788467302e-08</v>
+        <v>2.6726377884673e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>2.613380618544358e-08</v>
+        <v>2.61338061854436e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>3.868076387858822e-09</v>
+        <v>2.573669095934903e-08</v>
       </c>
     </row>
     <row r="9">
@@ -5547,37 +5547,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.776560888946643e-08</v>
+        <v>2.776560888946646e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.198869349536516e-08</v>
+        <v>2.198869349536514e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>2.599232391993435e-08</v>
+        <v>2.599232391993443e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>2.198869349536516e-08</v>
+        <v>2.198869349536514e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.198869349536516e-08</v>
+        <v>2.198869349536514e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.719122102214327e-08</v>
+        <v>2.719122102214323e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.226740013852802e-08</v>
+        <v>2.2267400138528e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.198869349536516e-08</v>
+        <v>2.198869349536514e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.880149352381827e-08</v>
+        <v>2.880149352381825e-08</v>
       </c>
       <c r="K9" t="n">
         <v>2.855882312109768e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.84006406658589e-08</v>
+        <v>2.840064066585888e-08</v>
       </c>
     </row>
   </sheetData>
@@ -5663,37 +5663,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.06747216862516e-07</v>
+        <v>3.06747216862514e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>3.170870479399732e-07</v>
+        <v>3.170870479399714e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>4.588644812360019e-07</v>
+        <v>4.588644812360013e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>3.170870479399732e-07</v>
+        <v>3.170870479399714e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>3.170870479399732e-07</v>
+        <v>3.170870479399714e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>3.719392482129716e-07</v>
+        <v>3.719392482129678e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>8.351228759751864e-07</v>
+        <v>8.351228759751896e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>3.170870479399732e-07</v>
+        <v>3.170870479399714e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>2.57078331315603e-07</v>
+        <v>2.570783313156013e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>2.495593001563743e-07</v>
+        <v>2.495593001563708e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.237315721863126e-06</v>
+        <v>1.237315721863134e-06</v>
       </c>
     </row>
     <row r="3">
@@ -5703,37 +5703,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.04861439095491e-08</v>
+        <v>1.048614390954907e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.00120313853665e-08</v>
+        <v>1.001203138536636e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.04861439095491e-08</v>
+        <v>1.048614390954907e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.013686987167405e-08</v>
+        <v>1.013686987167401e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.013686987167407e-08</v>
+        <v>1.013686987167396e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.043208629549212e-08</v>
+        <v>1.043208629549209e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.04861439095491e-08</v>
+        <v>1.048614390954907e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.021317715086939e-08</v>
+        <v>1.021317715086926e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.04861439095491e-08</v>
+        <v>1.048614390954907e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.04861439095491e-08</v>
+        <v>1.048614390954907e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.04861439095491e-08</v>
+        <v>1.048614390954907e-08</v>
       </c>
     </row>
     <row r="4">
@@ -5743,37 +5743,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.499673678565843e-08</v>
+        <v>2.499673678565834e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>2.4676405232502e-08</v>
+        <v>2.467640523250181e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>4.057605792118826e-08</v>
+        <v>4.057605792118795e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>2.357405212222783e-08</v>
+        <v>2.357405212222762e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>2.479589740876511e-08</v>
+        <v>2.479589740876502e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>2.494267917160147e-08</v>
+        <v>2.494267917160141e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>4.098367794987949e-08</v>
+        <v>4.098367794987918e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>4.002090022782005e-08</v>
+        <v>4.002090022781989e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>4.04222517343429e-08</v>
+        <v>2.588837276243773e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>2.487684012524068e-08</v>
+        <v>2.487684012524054e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>2.532053577537344e-08</v>
+        <v>2.532053577537345e-08</v>
       </c>
     </row>
     <row r="5">
@@ -5783,37 +5783,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.722460243562764e-08</v>
+        <v>4.722460243562762e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>4.695163567694795e-08</v>
+        <v>4.695163567694772e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>4.722221981113096e-08</v>
+        <v>4.72222198111309e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>4.695706305545504e-08</v>
+        <v>4.695706305545498e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>4.695706305545504e-08</v>
+        <v>4.695706305545498e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>4.71705448215707e-08</v>
+        <v>4.717054482157059e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>4.722460243562764e-08</v>
+        <v>4.722460243562758e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>4.695163567694795e-08</v>
+        <v>4.695163567694772e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>4.722460243562764e-08</v>
+        <v>4.722460243562758e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>4.722460243562764e-08</v>
+        <v>4.722460243562758e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>4.722460243562764e-08</v>
+        <v>4.722460243562758e-08</v>
       </c>
     </row>
     <row r="6">
@@ -5823,37 +5823,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.429873586583608e-07</v>
+        <v>1.429873586583606e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>2.292198429524627e-07</v>
+        <v>2.292198429524624e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>2.473998249239602e-07</v>
+        <v>2.473998249239595e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>2.055649452005497e-07</v>
+        <v>2.055649452005493e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.454603406215719e-07</v>
+        <v>1.454603406215714e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>2.294135287317147e-07</v>
+        <v>2.294135287317142e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>2.294675863457758e-07</v>
+        <v>2.294675863457751e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>2.291946195870919e-07</v>
+        <v>2.291946195870914e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>2.294845822006904e-07</v>
+        <v>2.294845822006901e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.413809440289256e-07</v>
+        <v>1.413809440289253e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>3.198034155358429e-07</v>
+        <v>3.198034155358419e-07</v>
       </c>
     </row>
     <row r="7">
@@ -5866,31 +5866,31 @@
         <v>1.027989715912187e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>1.290525234764253e-07</v>
+        <v>1.290525234764251e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>1.29325495858743e-07</v>
+        <v>1.293254958587429e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>1.596635351479055e-07</v>
+        <v>1.596635351479052e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>1.290524966970891e-07</v>
+        <v>1.290524966970888e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>1.29271432621048e-07</v>
+        <v>1.292714326210482e-07</v>
       </c>
       <c r="H7" t="n">
         <v>1.29325490235105e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>1.290525234764253e-07</v>
+        <v>1.290525234764251e-07</v>
       </c>
       <c r="J7" t="n">
         <v>1.29325490235105e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>1.13955923520442e-07</v>
+        <v>1.139559235204419e-07</v>
       </c>
       <c r="L7" t="n">
         <v>1.29325490235105e-07</v>
@@ -5903,37 +5903,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.517954666095075e-08</v>
+        <v>2.517954666095077e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>1.820283585250842e-08</v>
+        <v>1.820283585250849e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.122413629126479e-08</v>
+        <v>2.122413629126477e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>1.820283585250842e-08</v>
+        <v>1.820283585250849e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>1.820283585250842e-08</v>
+        <v>1.820283585250849e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.369424205580739e-08</v>
+        <v>2.369424205580726e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>1.392137234666944e-08</v>
+        <v>1.392137234666947e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>1.820283585250842e-08</v>
+        <v>1.820283585250849e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.684632627417927e-08</v>
+        <v>2.684632627417928e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>2.650400361204822e-08</v>
+        <v>2.650400361204833e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>6.45760996076103e-09</v>
+        <v>6.457609960761267e-09</v>
       </c>
     </row>
     <row r="9">
@@ -5943,37 +5943,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.823968238971346e-08</v>
+        <v>2.823968238971357e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.152458857106483e-08</v>
+        <v>2.152458857106478e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>2.662892773504505e-08</v>
+        <v>2.662892773504507e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>2.152458857106483e-08</v>
+        <v>2.152458857106478e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.152458857106483e-08</v>
+        <v>2.152458857106478e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.761464540439517e-08</v>
+        <v>2.761464540439515e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.367016295746037e-08</v>
+        <v>2.367016295746038e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.152458857106483e-08</v>
+        <v>2.152458857106478e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.892012029571951e-08</v>
+        <v>2.892012029571952e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.877936143931111e-08</v>
+        <v>2.877936143931115e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.063291368637643e-08</v>
+        <v>2.063291368637647e-08</v>
       </c>
     </row>
   </sheetData>
@@ -6059,37 +6059,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.622309433000335e-07</v>
+        <v>1.622309433000337e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>1.536353610965954e-07</v>
+        <v>1.536353610965953e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>2.514686582432599e-07</v>
+        <v>2.514686582432598e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.536353610965954e-07</v>
+        <v>1.536353610965953e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.536353610965954e-07</v>
+        <v>1.536353610965953e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>2.159674091740492e-07</v>
+        <v>2.159674091740489e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>4.497776642160714e-07</v>
+        <v>4.497776642160709e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.536353610965954e-07</v>
+        <v>1.536353610965953e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>2.486190790463588e-07</v>
+        <v>2.486190790463584e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.827648360721787e-07</v>
+        <v>1.827648360721783e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.760728972455774e-07</v>
+        <v>4.517454878828083e-07</v>
       </c>
     </row>
     <row r="3">
@@ -6099,37 +6099,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.323466214755499e-09</v>
+        <v>9.323466214755464e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>8.788476675583894e-09</v>
+        <v>8.7884766755839e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>9.323466214755499e-09</v>
+        <v>9.323466214755464e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>8.917732938237395e-09</v>
+        <v>8.917732938237377e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>8.917732938237397e-09</v>
+        <v>8.917732938237373e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>9.269001194073447e-09</v>
+        <v>9.269001194073417e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>9.323466214755499e-09</v>
+        <v>9.323466214755464e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>9.047780680622142e-09</v>
+        <v>9.047780680622094e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>9.323466214755499e-09</v>
+        <v>9.323466214755464e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>9.323466214755499e-09</v>
+        <v>9.323466214755464e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>9.323466214755499e-09</v>
+        <v>9.323466214755464e-09</v>
       </c>
     </row>
     <row r="4">
@@ -6139,37 +6139,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.436120721189234e-08</v>
+        <v>2.436120721189232e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>2.394313086241253e-08</v>
+        <v>2.394313086241262e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>2.45020205630326e-08</v>
+        <v>3.951818021103787e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>2.280141012952266e-08</v>
+        <v>2.280141012952248e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>2.410114409701234e-08</v>
+        <v>2.410114409701226e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>3.919102418103403e-08</v>
+        <v>2.430674219121024e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>3.990280502428302e-08</v>
+        <v>3.990280502428282e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>3.896980366758279e-08</v>
+        <v>2.408552167775899e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>3.936821151556476e-08</v>
+        <v>3.936821151556464e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>2.436028705801506e-08</v>
+        <v>2.436028705801507e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>2.445902709854774e-08</v>
+        <v>2.445902709854763e-08</v>
       </c>
     </row>
     <row r="5">
@@ -6179,37 +6179,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.716406049616565e-08</v>
+        <v>4.716406049616561e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>4.688837496203232e-08</v>
+        <v>4.688837496203233e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>4.716153262893041e-08</v>
+        <v>4.716153262893037e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>4.688660348781483e-08</v>
+        <v>4.688660348781487e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>4.688660348781483e-08</v>
+        <v>4.688660348781487e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>4.710959547548362e-08</v>
+        <v>4.710959547548361e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>4.716406049616565e-08</v>
+        <v>4.716406049616561e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>4.688837496203232e-08</v>
+        <v>4.688837496203233e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>4.716406049616565e-08</v>
+        <v>4.716406049616561e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>4.716406049616565e-08</v>
+        <v>4.716406049616561e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>4.716406049616565e-08</v>
+        <v>4.716406049616561e-08</v>
       </c>
     </row>
     <row r="6">
@@ -6219,37 +6219,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.490579415195516e-07</v>
+        <v>1.490579415195518e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>2.396942334204752e-07</v>
+        <v>2.396942334202538e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>2.587976907017567e-07</v>
+        <v>2.58797690701757e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>2.148331702972676e-07</v>
+        <v>2.148331702972681e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.516638616568857e-07</v>
+        <v>1.516638616568858e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>2.398960570025329e-07</v>
+        <v>2.398960570025333e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>2.399505220232154e-07</v>
+        <v>2.399505220232159e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>2.396748364890816e-07</v>
+        <v>2.39674836489082e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>2.39968385033296e-07</v>
+        <v>2.399683850332962e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.473695651711225e-07</v>
+        <v>1.473695651711227e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>3.348954226861064e-07</v>
+        <v>3.348954226861066e-07</v>
       </c>
     </row>
     <row r="7">
@@ -6259,19 +6259,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.138017051867592e-07</v>
+        <v>1.138017051867589e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>1.43337039892332e-07</v>
+        <v>1.433370398923316e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>1.436127330383927e-07</v>
+        <v>1.436127330383926e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>1.777383027674697e-07</v>
+        <v>1.777383027674695e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>1.433370164789114e-07</v>
+        <v>1.433370164789112e-07</v>
       </c>
       <c r="G7" t="n">
         <v>1.435582604057832e-07</v>
@@ -6280,13 +6280,13 @@
         <v>1.436127254264653e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>1.43337039892332e-07</v>
+        <v>1.433370398923316e-07</v>
       </c>
       <c r="J7" t="n">
         <v>1.436127254264653e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>1.060753277235379e-07</v>
+        <v>1.263401064242174e-07</v>
       </c>
       <c r="L7" t="n">
         <v>1.436127254264653e-07</v>
@@ -6299,37 +6299,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.793271916698295e-08</v>
+        <v>2.793271916698292e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.128326367153278e-08</v>
+        <v>2.128326367153279e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.581372232632237e-08</v>
+        <v>2.581372232632234e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.128326367153278e-08</v>
+        <v>2.128326367153279e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>2.128326367153278e-08</v>
+        <v>2.128326367153279e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.672106451209047e-08</v>
+        <v>2.672106451209043e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.186115018664582e-08</v>
+        <v>2.186115018664579e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.128326367153278e-08</v>
+        <v>2.128326367153279e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.615242397762133e-08</v>
+        <v>2.615242397762131e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>2.744498047267639e-08</v>
+        <v>2.744498047267637e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>2.240083565929804e-08</v>
+        <v>2.788701709263709e-08</v>
       </c>
     </row>
     <row r="9">
@@ -6339,37 +6339,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.863453308779765e-08</v>
+        <v>2.863453308779762e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.18940555382536e-08</v>
+        <v>2.189405553825356e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>2.777158309275596e-08</v>
+        <v>2.777158309275593e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>2.18940555382536e-08</v>
+        <v>2.189405553825357e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.18940555382536e-08</v>
+        <v>2.189405553825357e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.811859671054046e-08</v>
+        <v>2.811859671054045e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.61689314113708e-08</v>
+        <v>2.616893141137078e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.18940555382536e-08</v>
+        <v>2.189405553825357e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.791078803376506e-08</v>
+        <v>2.791078803376503e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.843600056457219e-08</v>
+        <v>2.843600056457214e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.861728164521829e-08</v>
+        <v>2.638696711453949e-08</v>
       </c>
     </row>
   </sheetData>
@@ -6455,34 +6455,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.451768665279842e-07</v>
+        <v>1.451768665279843e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>1.632680223391609e-07</v>
+        <v>1.632680223391607e-07</v>
       </c>
       <c r="D2" t="n">
         <v>1.69531386763264e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.632680223391609e-07</v>
+        <v>1.632680223391607e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.632680223391609e-07</v>
+        <v>1.632680223391607e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.696305220799488e-07</v>
+        <v>1.69630522079946e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.723853286358808e-07</v>
+        <v>1.723853286358809e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.632680223391609e-07</v>
+        <v>1.632680223391607e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>2.061874046739625e-07</v>
+        <v>2.061874046739622e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.688227760595996e-07</v>
+        <v>1.688227760595999e-07</v>
       </c>
       <c r="L2" t="n">
         <v>1.553872987118481e-07</v>
@@ -6495,37 +6495,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.225216720982294e-09</v>
+        <v>9.225216720982309e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>8.773509890047532e-09</v>
+        <v>8.773509890047499e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>9.225216720982294e-09</v>
+        <v>9.225216720982309e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>8.88710912659724e-09</v>
+        <v>8.887109126597234e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>8.887109126597242e-09</v>
+        <v>8.887109126597273e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>9.173037567394733e-09</v>
+        <v>9.173037567394722e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>9.225216720982294e-09</v>
+        <v>9.225216720982309e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>8.96414197057062e-09</v>
+        <v>8.964141970570577e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>9.225216720982294e-09</v>
+        <v>9.225216720982309e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>9.225216720982294e-09</v>
+        <v>9.225216720982309e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>9.225216720982294e-09</v>
+        <v>9.225216720982309e-09</v>
       </c>
     </row>
     <row r="4">
@@ -6535,37 +6535,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.31194096277312e-08</v>
+        <v>3.682892452236305e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>2.280615241584704e-08</v>
+        <v>2.280615241584698e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>2.312855967920783e-08</v>
+        <v>2.312872112676434e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>2.173947619704521e-08</v>
+        <v>2.173947619704517e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>2.287835388178925e-08</v>
+        <v>2.287835388178924e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>2.306723047414359e-08</v>
+        <v>2.306723047414363e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>3.734653167277718e-08</v>
+        <v>2.312174523461985e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>2.28583348773195e-08</v>
+        <v>2.285833487731947e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>2.394252215001478e-08</v>
+        <v>3.692843670132254e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>2.314503623688295e-08</v>
+        <v>2.314503623688299e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>2.311639964309356e-08</v>
+        <v>2.311639964309361e-08</v>
       </c>
     </row>
     <row r="5">
@@ -6575,37 +6575,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.466218459315042e-08</v>
+        <v>4.466218459315044e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>4.440110984273874e-08</v>
+        <v>4.440110984273872e-08</v>
       </c>
       <c r="D5" t="n">
         <v>4.465982485520355e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>4.440122865233691e-08</v>
+        <v>4.440122865233689e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>4.440122865233691e-08</v>
+        <v>4.440122865233689e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>4.461000543956282e-08</v>
+        <v>4.461000543956286e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>4.466218459315042e-08</v>
+        <v>4.466218459315044e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>4.440110984273874e-08</v>
+        <v>4.440110984273872e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>4.466218459315042e-08</v>
+        <v>4.466218459315044e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>4.466218459315042e-08</v>
+        <v>4.466218459315044e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>4.466218459315042e-08</v>
+        <v>4.466218459315044e-08</v>
       </c>
     </row>
     <row r="6">
@@ -6615,13 +6615,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.39466348590073e-07</v>
+        <v>1.394663485900729e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>2.239980722806691e-07</v>
+        <v>2.23998072280669e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>2.41817599234125e-07</v>
+        <v>2.418175992341246e-07</v>
       </c>
       <c r="E6" t="n">
         <v>2.00810663466836e-07</v>
@@ -6630,22 +6630,22 @@
         <v>1.418939260500836e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>2.241871833912482e-07</v>
+        <v>2.241871833912479e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>2.242393625448349e-07</v>
+        <v>2.242393625448347e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>2.239782877944238e-07</v>
+        <v>2.239782877944237e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>2.242560228838311e-07</v>
+        <v>2.24256022883831e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.378916463321633e-07</v>
+        <v>1.378916463321634e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>3.127918642367061e-07</v>
+        <v>3.127918642367058e-07</v>
       </c>
     </row>
     <row r="7">
@@ -6655,37 +6655,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.006039159879084e-07</v>
+        <v>1.006039159879083e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>1.264929844524365e-07</v>
+        <v>1.264929844524364e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>1.267540688441091e-07</v>
+        <v>1.267540688441089e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>1.566696817155677e-07</v>
+        <v>1.566696817155673e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>1.264929666525901e-07</v>
+        <v>1.2649296665259e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>1.267018800492606e-07</v>
+        <v>1.267018800492605e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>1.267540592028481e-07</v>
+        <v>1.267540592028478e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>1.264929844524365e-07</v>
+        <v>1.264929844524364e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>1.267540592028481e-07</v>
+        <v>1.267540592028478e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>1.109878520341417e-07</v>
+        <v>1.109878520341415e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>1.267540592028481e-07</v>
+        <v>1.267540592028478e-07</v>
       </c>
     </row>
     <row r="8">
@@ -6695,13 +6695,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.809460113790821e-08</v>
+        <v>2.80946011379082e-08</v>
       </c>
       <c r="C8" t="n">
         <v>2.091779426882776e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.766649156185458e-08</v>
+        <v>2.76664915618546e-08</v>
       </c>
       <c r="E8" t="n">
         <v>2.091779426882776e-08</v>
@@ -6710,10 +6710,10 @@
         <v>2.091779426882776e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.759458176301113e-08</v>
+        <v>2.759458176301112e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.80326644888133e-08</v>
+        <v>2.803266448881332e-08</v>
       </c>
       <c r="I8" t="n">
         <v>2.091779426882776e-08</v>
@@ -6722,10 +6722,10 @@
         <v>2.678787404314349e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>2.750618412753006e-08</v>
+        <v>2.750618412753005e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>2.834786453689762e-08</v>
+        <v>2.834786453689764e-08</v>
       </c>
     </row>
     <row r="9">
@@ -6735,13 +6735,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.871118648768985e-08</v>
+        <v>2.871118648768983e-08</v>
       </c>
       <c r="C9" t="n">
         <v>2.181909405288182e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>2.853687546555391e-08</v>
+        <v>2.853687546555392e-08</v>
       </c>
       <c r="E9" t="n">
         <v>2.181909405288182e-08</v>
@@ -6759,13 +6759,13 @@
         <v>2.181909405288182e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.818008745412843e-08</v>
+        <v>2.818008745412842e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.847164608471441e-08</v>
+        <v>2.847164608471443e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.876105167495001e-08</v>
+        <v>2.881538349388308e-08</v>
       </c>
     </row>
   </sheetData>
@@ -6851,37 +6851,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.661080341049476e-07</v>
+        <v>1.661080341049477e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>1.72151365552354e-07</v>
+        <v>1.721513655523564e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.799343874583645e-07</v>
+        <v>1.799343874583647e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.72151365552354e-07</v>
+        <v>1.721513655523564e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.72151365552354e-07</v>
+        <v>1.721513655523564e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.704175192728251e-07</v>
+        <v>1.704175192728285e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.708281996530259e-07</v>
+        <v>1.708281996530264e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.72151365552354e-07</v>
+        <v>1.721513655523564e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>2.450915095471901e-07</v>
+        <v>2.450915095471902e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.6321104270639e-07</v>
+        <v>1.632110427063904e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.688262467705726e-07</v>
+        <v>1.677976190359099e-07</v>
       </c>
     </row>
     <row r="3">
@@ -6891,37 +6891,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.370549655624894e-09</v>
+        <v>9.370549655624939e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>8.927365236068746e-09</v>
+        <v>8.927365236068781e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>9.370549655624894e-09</v>
+        <v>9.370549655624957e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>9.040863510726947e-09</v>
+        <v>9.04086351072702e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>9.040863510726947e-09</v>
+        <v>9.040863510726992e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>9.318756114705738e-09</v>
+        <v>9.318756114706005e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>9.370549655624894e-09</v>
+        <v>9.370549655624939e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>9.11196119923347e-09</v>
+        <v>9.111961199233635e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>9.370549655624894e-09</v>
+        <v>9.370549655624939e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>9.370549655624894e-09</v>
+        <v>9.370549655624939e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>9.370549655624894e-09</v>
+        <v>9.370549655624939e-09</v>
       </c>
     </row>
     <row r="4">
@@ -6931,37 +6931,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.324892606079399e-08</v>
+        <v>2.32489260607938e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>2.294730376010138e-08</v>
+        <v>2.294730376010172e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>3.726700893066866e-08</v>
+        <v>2.327255510491895e-08</v>
       </c>
       <c r="E4" t="n">
         <v>2.187612291120385e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>2.300792372562047e-08</v>
+        <v>2.300792372562063e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>2.319713251987466e-08</v>
+        <v>3.703019928671031e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>3.755467668863528e-08</v>
+        <v>3.755467668863535e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>2.299033760440243e-08</v>
+        <v>2.299033760440254e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>2.408156828630149e-08</v>
+        <v>3.713597215975962e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>2.324735807793416e-08</v>
+        <v>2.324735807793402e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>2.324325985813565e-08</v>
+        <v>2.324325985813568e-08</v>
       </c>
     </row>
     <row r="5">
@@ -6971,37 +6971,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.504199039687507e-08</v>
+        <v>4.504199039687543e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>4.478340194048399e-08</v>
+        <v>4.478340194048412e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>4.503962988582146e-08</v>
+        <v>4.503962988582165e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>4.478336093143791e-08</v>
+        <v>4.478336093143807e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>4.478336093143791e-08</v>
+        <v>4.478336093143807e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>4.499019685595648e-08</v>
+        <v>4.499019685595644e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>4.504199039687507e-08</v>
+        <v>4.504199039687543e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>4.478340194048399e-08</v>
+        <v>4.478340194048412e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>4.504199039687507e-08</v>
+        <v>4.504199039687543e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>4.504199039687507e-08</v>
+        <v>4.504199039687543e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>4.504199039687507e-08</v>
+        <v>4.504199039687543e-08</v>
       </c>
     </row>
     <row r="6">
@@ -7014,28 +7014,28 @@
         <v>1.398895138556116e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>2.246627513472976e-07</v>
+        <v>2.246627513475061e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>2.425294830390751e-07</v>
+        <v>2.425294830390753e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>2.01409953275578e-07</v>
+        <v>2.014099532755781e-07</v>
       </c>
       <c r="F6" t="n">
         <v>1.423270628716635e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>2.248498670657515e-07</v>
+        <v>2.248498670657516e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>2.249016606066708e-07</v>
+        <v>2.24901660606671e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>2.246430721502789e-07</v>
+        <v>2.246430721502793e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>2.249183679420946e-07</v>
+        <v>2.249183679420945e-07</v>
       </c>
       <c r="K6" t="n">
         <v>1.383103695832392e-07</v>
@@ -7051,37 +7051,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.674012751397887e-08</v>
+        <v>9.674012751397901e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.215501869516084e-07</v>
+        <v>1.215501869516087e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>1.218087849501095e-07</v>
+        <v>1.218087849501097e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>1.504788614722841e-07</v>
+        <v>1.504788614722843e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2155016916465e-07</v>
+        <v>1.215501691646502e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>1.217569818670807e-07</v>
+        <v>1.217569818670809e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>1.218087754079998e-07</v>
+        <v>1.218087754080001e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>1.215501869516084e-07</v>
+        <v>1.215501869516087e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>1.218087754079998e-07</v>
+        <v>1.218087754080001e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>1.072839063794024e-07</v>
+        <v>1.066946137081196e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>1.218087754079998e-07</v>
+        <v>1.218087754080001e-07</v>
       </c>
     </row>
     <row r="8">
@@ -7091,37 +7091,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.769091839605856e-08</v>
+        <v>2.769091839605854e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.081836521563722e-08</v>
+        <v>2.081836521563724e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.743029377927292e-08</v>
+        <v>2.743029377927287e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.081836521563722e-08</v>
+        <v>2.081836521563724e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>2.081836521563722e-08</v>
+        <v>2.081836521563724e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.767259232396194e-08</v>
+        <v>2.76725923239618e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.805987506279547e-08</v>
+        <v>2.805987506279545e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.081836521563722e-08</v>
+        <v>2.081836521563724e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.595810651561829e-08</v>
+        <v>2.595810651561827e-08</v>
       </c>
       <c r="K8" t="n">
         <v>2.77827465754468e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>2.79827049499822e-08</v>
+        <v>2.798270494998217e-08</v>
       </c>
     </row>
     <row r="9">
@@ -7131,37 +7131,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.861940813272306e-08</v>
+        <v>2.861940813272313e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.188086677600314e-08</v>
+        <v>2.188086677600319e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>2.851332225613858e-08</v>
+        <v>2.851332225613849e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>2.188086677600314e-08</v>
+        <v>2.188086677600319e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.188086677600314e-08</v>
+        <v>2.188086677600319e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.859624074851872e-08</v>
+        <v>2.859624074851871e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.877135451184881e-08</v>
+        <v>2.877135451184887e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.188086677600314e-08</v>
+        <v>2.188086677600319e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.791513176355124e-08</v>
+        <v>2.791513176355129e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.86569192561891e-08</v>
+        <v>2.865691925618899e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.873964963681362e-08</v>
+        <v>2.879525237965148e-08</v>
       </c>
     </row>
   </sheetData>
@@ -7253,7 +7253,7 @@
         <v>1.913822852518366e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>5.526981784457452e-07</v>
+        <v>5.526981784457451e-07</v>
       </c>
       <c r="E2" t="n">
         <v>1.913822852518366e-07</v>
@@ -7262,22 +7262,22 @@
         <v>1.913822852518366e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>3.874859559975203e-07</v>
+        <v>3.874859559975184e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.102833075315941e-06</v>
+        <v>1.102833075315942e-06</v>
       </c>
       <c r="I2" t="n">
         <v>1.913822852518366e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>2.844679119625276e-07</v>
+        <v>2.844679119625281e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>2.489602553960682e-07</v>
+        <v>2.489602553960686e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.367731742166387e-06</v>
+        <v>1.367731742166388e-06</v>
       </c>
     </row>
     <row r="3">
@@ -7290,25 +7290,25 @@
         <v>9.84392227764221e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>9.166946966083967e-09</v>
+        <v>9.166946966084055e-09</v>
       </c>
       <c r="D3" t="n">
         <v>9.84392227764221e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>9.307668937558343e-09</v>
+        <v>9.307668937558404e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>9.307668937558343e-09</v>
+        <v>9.307668937558402e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>9.784341913559599e-09</v>
+        <v>9.784341913559619e-09</v>
       </c>
       <c r="H3" t="n">
         <v>9.84392227764221e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>9.535612156948912e-09</v>
+        <v>9.535612156949055e-09</v>
       </c>
       <c r="J3" t="n">
         <v>9.84392227764221e-09</v>
@@ -7327,37 +7327,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.528489768948396e-08</v>
+        <v>2.528489768948398e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>2.463159399406939e-08</v>
+        <v>2.463159399406947e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>2.581035567898777e-08</v>
+        <v>2.581035567898798e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>2.347533704082993e-08</v>
+        <v>2.347533704082986e-08</v>
       </c>
       <c r="F4" t="n">
         <v>2.496917154593754e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>4.129394631337656e-08</v>
+        <v>4.129394631337664e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>4.219511099407025e-08</v>
+        <v>4.219511099407028e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>2.497658756879065e-08</v>
+        <v>4.104521655676597e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>4.152358268786043e-08</v>
+        <v>4.152358268786046e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>2.516500727929407e-08</v>
+        <v>2.516500727929409e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>2.563854479494773e-08</v>
+        <v>2.563854479494776e-08</v>
       </c>
     </row>
     <row r="5">
@@ -7367,37 +7367,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.844218985095684e-08</v>
+        <v>4.844218985095685e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>4.813387973026355e-08</v>
+        <v>4.813387973026369e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>4.843965863551425e-08</v>
+        <v>4.843965863551429e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>4.812693906233265e-08</v>
+        <v>4.812693906233279e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>4.812693906233265e-08</v>
+        <v>4.812693906233279e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>4.838260948687428e-08</v>
+        <v>4.838260948687429e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>4.844218985095684e-08</v>
+        <v>4.844218985095685e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>4.813387973026355e-08</v>
+        <v>4.813387973026369e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>4.844218985095684e-08</v>
+        <v>4.844218985095685e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>4.844218985095684e-08</v>
+        <v>4.844218985095685e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>4.844218985095684e-08</v>
+        <v>4.844218985095685e-08</v>
       </c>
     </row>
     <row r="6">
@@ -7407,37 +7407,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.510138482117444e-07</v>
+        <v>1.510138482117445e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>2.426758072430585e-07</v>
+        <v>2.426758072432831e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>2.620370454823869e-07</v>
+        <v>2.62037045482387e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>2.175245197588758e-07</v>
+        <v>2.17524519758876e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.536177582818082e-07</v>
+        <v>1.536177582818084e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>2.42909871636616e-07</v>
+        <v>2.429098716366159e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>2.429694520007013e-07</v>
+        <v>2.429694520007012e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>2.42661141880005e-07</v>
+        <v>2.426611418800053e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>2.429875239250626e-07</v>
+        <v>2.429875239250627e-07</v>
       </c>
       <c r="K6" t="n">
         <v>1.493057256600585e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>3.390247693734041e-07</v>
+        <v>3.390247693734042e-07</v>
       </c>
     </row>
     <row r="7">
@@ -7450,34 +7450,34 @@
         <v>1.187695344895035e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>1.495678961202439e-07</v>
+        <v>1.495678961202441e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>1.498762094961386e-07</v>
+        <v>1.498762094961387e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>1.854642972956566e-07</v>
+        <v>1.854642972956568e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>1.49567862999926e-07</v>
+        <v>1.495678629999263e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>1.498166258768545e-07</v>
+        <v>1.498166258768547e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>1.498762062409371e-07</v>
+        <v>1.498762062409372e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>1.495678961202439e-07</v>
+        <v>1.495678961202441e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>1.498762062409371e-07</v>
+        <v>1.498762062409372e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>1.31121650580606e-07</v>
+        <v>1.318528798319567e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>1.498762062409371e-07</v>
+        <v>1.498762062409372e-07</v>
       </c>
     </row>
     <row r="8">
@@ -7487,13 +7487,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.549601646926123e-08</v>
+        <v>2.549601646926125e-08</v>
       </c>
       <c r="C8" t="n">
         <v>2.091468731113124e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>1.920854230753758e-08</v>
+        <v>1.920854230753763e-08</v>
       </c>
       <c r="E8" t="n">
         <v>2.091468731113124e-08</v>
@@ -7502,22 +7502,22 @@
         <v>2.091468731113124e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.339016505615582e-08</v>
+        <v>2.339016505615581e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>8.081547347135771e-09</v>
+        <v>8.081547347135774e-09</v>
       </c>
       <c r="I8" t="n">
         <v>2.091468731113124e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.606453604971949e-08</v>
+        <v>2.60645360497195e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>2.656519705255644e-08</v>
+        <v>2.656519705255645e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>2.768926356069637e-08</v>
+        <v>5.247082348969822e-09</v>
       </c>
     </row>
     <row r="9">
@@ -7527,37 +7527,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.803747709635169e-08</v>
+        <v>2.803747709635171e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.205541503063405e-08</v>
+        <v>2.205541503063407e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>2.547692605168627e-08</v>
+        <v>2.547692605168629e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>2.205541503063405e-08</v>
+        <v>2.205541503063407e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.205541503063405e-08</v>
+        <v>2.205541503063407e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.714462522264232e-08</v>
+        <v>2.714462522264233e-08</v>
       </c>
       <c r="H9" t="n">
         <v>2.096544464635762e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.205541503063405e-08</v>
+        <v>2.205541503063407e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.82706816726032e-08</v>
+        <v>2.827068167260322e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.847315033524356e-08</v>
+        <v>2.847315033524357e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.893278927622778e-08</v>
+        <v>1.980925763985461e-08</v>
       </c>
     </row>
   </sheetData>
@@ -7643,37 +7643,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.31362446527469e-07</v>
+        <v>1.313624465274691e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>1.536176713893515e-07</v>
+        <v>1.536176713893512e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>4.242143478057774e-07</v>
+        <v>4.242143478057777e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.536176713893515e-07</v>
+        <v>1.536176713893512e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.536176713893515e-07</v>
+        <v>1.536176713893512e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>2.586671471842156e-07</v>
+        <v>2.586671471842161e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>2.388729184164359e-07</v>
+        <v>2.388729184164358e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.536176713893515e-07</v>
+        <v>1.536176713893512e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>2.09811390482616e-07</v>
+        <v>2.098113904826161e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.476347299631444e-07</v>
+        <v>1.476347299631443e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>7.787875983176566e-07</v>
+        <v>1.675890187799696e-07</v>
       </c>
     </row>
     <row r="3">
@@ -7683,37 +7683,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.414372404060685e-09</v>
+        <v>9.414372404060642e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>8.85101228835847e-09</v>
+        <v>8.851012288358318e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>9.414372404060685e-09</v>
+        <v>9.414372404060642e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>8.973103828538997e-09</v>
+        <v>8.973103828538966e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>8.973103828538997e-09</v>
+        <v>8.973103828538941e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>9.358101306341591e-09</v>
+        <v>9.358101306341561e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>9.414372404060671e-09</v>
+        <v>9.414372404060642e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>9.127205101549697e-09</v>
+        <v>9.1272051015497e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>9.414372404060685e-09</v>
+        <v>9.414372404060642e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>9.414372404060685e-09</v>
+        <v>9.414372404060642e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>9.414372404060685e-09</v>
+        <v>9.414372404060642e-09</v>
       </c>
     </row>
     <row r="4">
@@ -7723,37 +7723,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.342203073729689e-08</v>
+        <v>3.781975965663923e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>2.293735403605063e-08</v>
+        <v>2.293735403605056e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>2.390079954378565e-08</v>
+        <v>2.390079954378278e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>2.18683527666572e-08</v>
+        <v>2.186835276665706e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>2.314292924297914e-08</v>
+        <v>2.314292924297918e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>3.776348855892026e-08</v>
+        <v>2.336575963957764e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>3.838126160890499e-08</v>
+        <v>3.838126160890507e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>3.75325923541284e-08</v>
+        <v>3.75325923541281e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>3.795683493807097e-08</v>
+        <v>2.426750140125037e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>2.329474028362927e-08</v>
+        <v>2.329474028362937e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>2.361981188961922e-08</v>
+        <v>2.361981188961914e-08</v>
       </c>
     </row>
     <row r="5">
@@ -7763,37 +7763,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.524844454105e-08</v>
+        <v>4.524844454104995e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>4.496127723853901e-08</v>
+        <v>4.49612772385391e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>4.524608559033431e-08</v>
+        <v>4.524608559033409e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>4.495786977523928e-08</v>
+        <v>4.49578697752394e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>4.495786977523928e-08</v>
+        <v>4.495786977523941e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>4.51921734433309e-08</v>
+        <v>4.519217344333099e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>4.524844454105e-08</v>
+        <v>4.524844454104995e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>4.496127723853901e-08</v>
+        <v>4.49612772385391e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>4.524844454105e-08</v>
+        <v>4.524844454104995e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>4.524844454105e-08</v>
+        <v>4.524844454104995e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>4.524844454105e-08</v>
+        <v>4.524844454104995e-08</v>
       </c>
     </row>
     <row r="6">
@@ -7803,37 +7803,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.404741569466057e-07</v>
+        <v>1.404741569466059e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>2.255818945797304e-07</v>
+        <v>2.255818945799383e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>2.435562942480374e-07</v>
+        <v>2.435562942480367e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>2.022292712049726e-07</v>
+        <v>2.022292712049725e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.428927268038855e-07</v>
+        <v>1.428927268038852e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>2.257962608951477e-07</v>
+        <v>2.257962608951476e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>2.258525319928652e-07</v>
+        <v>2.258525319928653e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>2.255653646903556e-07</v>
+        <v>2.255653646903554e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>2.258693113025425e-07</v>
+        <v>2.258693113025426e-07</v>
       </c>
       <c r="K6" t="n">
         <v>1.388882097956416e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>3.150373839641731e-07</v>
+        <v>3.15037383964173e-07</v>
       </c>
     </row>
     <row r="7">
@@ -7843,37 +7843,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.028594432737327e-07</v>
+        <v>1.028594432737326e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>1.293309660129233e-07</v>
+        <v>1.29330966012923e-07</v>
       </c>
       <c r="D7" t="n">
         <v>1.296181447026466e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>1.602099130166555e-07</v>
+        <v>1.602099130166554e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>1.293309466350702e-07</v>
+        <v>1.293309466350701e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>1.295618622177152e-07</v>
+        <v>1.29561862217715e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>1.296181333154342e-07</v>
+        <v>1.296181333154341e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>1.293309660129233e-07</v>
+        <v>1.29330966012923e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>1.296181333154342e-07</v>
+        <v>1.296181333154341e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>1.14114048005206e-07</v>
+        <v>9.592416319233475e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.296181333154342e-07</v>
+        <v>1.296181333154341e-07</v>
       </c>
     </row>
     <row r="8">
@@ -7883,37 +7883,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.877052095719006e-08</v>
+        <v>2.877052095719009e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.138645003649597e-08</v>
+        <v>2.138645003649593e-08</v>
       </c>
       <c r="D8" t="n">
         <v>2.097665194914618e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.138645003649597e-08</v>
+        <v>2.138645003649593e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>2.138645003649597e-08</v>
+        <v>2.138645003649593e-08</v>
       </c>
       <c r="G8" t="n">
         <v>2.557481305691732e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.663730203589176e-08</v>
+        <v>2.663730203589173e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.138645003649597e-08</v>
+        <v>2.138645003649593e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.701142585176459e-08</v>
+        <v>2.701142585176458e-08</v>
       </c>
       <c r="K8" t="n">
         <v>2.840770065003016e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>2.818621218159049e-08</v>
+        <v>1.506481516017918e-08</v>
       </c>
     </row>
     <row r="9">
@@ -7923,37 +7923,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.917217090613472e-08</v>
+        <v>2.91721709061347e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.213256053481778e-08</v>
+        <v>2.213256053481776e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>2.599801883385409e-08</v>
+        <v>2.599801883385405e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>2.213256053481778e-08</v>
+        <v>2.213256053481776e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.213256053481778e-08</v>
+        <v>2.213256053481776e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.784306702509295e-08</v>
+        <v>2.784306702509297e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.830650117183271e-08</v>
+        <v>2.830650117183269e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.213256053481778e-08</v>
+        <v>2.213256053481776e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.845686130039888e-08</v>
+        <v>2.845686130039886e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.902448373594489e-08</v>
+        <v>2.902448373594488e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.893557649905778e-08</v>
+        <v>2.360127126400122e-08</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Hydrogen/hydrogen human toxicity non-carcinogenic results.xlsx
+++ b/Results/Hydrogen/hydrogen human toxicity non-carcinogenic results.xlsx
@@ -515,37 +515,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.208774686984519e-07</v>
+        <v>5.208774686984616e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>2.895706867005796e-07</v>
+        <v>2.8957068670058e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>6.460381455771412e-07</v>
+        <v>6.460381455771428e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>2.895706867005796e-07</v>
+        <v>2.8957068670058e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>2.895706867005796e-07</v>
+        <v>2.8957068670058e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>4.782335421662009e-07</v>
+        <v>4.782335421661946e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.388575731042435e-06</v>
+        <v>1.388575731042437e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>2.895706867005796e-07</v>
+        <v>2.8957068670058e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>3.915720700217504e-07</v>
+        <v>3.915720700217548e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>3.391835828110436e-07</v>
+        <v>3.391835828110431e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>2.413312780881303e-07</v>
+        <v>1.719332397625914e-06</v>
       </c>
     </row>
     <row r="3">
@@ -558,25 +558,25 @@
         <v>1.048586797748796e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>9.823604571966583e-09</v>
+        <v>9.823604571966567e-09</v>
       </c>
       <c r="D3" t="n">
         <v>1.048586797748796e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>9.971781075772172e-09</v>
+        <v>9.971781075772123e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>9.971781075772138e-09</v>
+        <v>9.971781075772123e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>1.042727558756841e-08</v>
+        <v>1.04272755875685e-08</v>
       </c>
       <c r="H3" t="n">
         <v>1.048586797748796e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.018386544921409e-08</v>
+        <v>1.018386544921411e-08</v>
       </c>
       <c r="J3" t="n">
         <v>1.048586797748796e-08</v>
@@ -595,34 +595,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.734344911612073e-08</v>
+        <v>2.73434491161207e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>2.673854634041299e-08</v>
+        <v>2.673854634041256e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>2.784781367627673e-08</v>
+        <v>2.784762507338721e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>2.548491360674053e-08</v>
+        <v>2.548491360674054e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>2.705652080202825e-08</v>
+        <v>2.705652080202821e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>4.486141036053311e-08</v>
+        <v>4.486141036053304e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>4.576358509163153e-08</v>
+        <v>4.57635850916316e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>2.704144658784685e-08</v>
+        <v>4.461800022217863e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>2.837711143408444e-08</v>
+        <v>4.503569823789021e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>2.723826078474672e-08</v>
+        <v>2.723826078474662e-08</v>
       </c>
       <c r="L4" t="n">
         <v>2.778459490500739e-08</v>
@@ -635,37 +635,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.203454469630301e-08</v>
+        <v>5.203454469630298e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>5.173254216802925e-08</v>
+        <v>5.173254216802916e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>5.203181954952342e-08</v>
+        <v>5.203181954952334e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>5.172579108225338e-08</v>
+        <v>5.172579108225326e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>5.172579108225338e-08</v>
+        <v>5.172579108225326e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>5.197595230638356e-08</v>
+        <v>5.197595230638355e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>5.203454469630301e-08</v>
+        <v>5.203454469630298e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>5.173254216802925e-08</v>
+        <v>5.173254216802916e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>5.203454469630301e-08</v>
+        <v>5.203454469630298e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>5.203454469630301e-08</v>
+        <v>5.203454469630298e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>5.203454469630301e-08</v>
+        <v>5.203454469630298e-08</v>
       </c>
     </row>
     <row r="6">
@@ -675,37 +675,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.619281433374784e-07</v>
+        <v>1.619281433374783e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>2.603099594229857e-07</v>
+        <v>2.603099594232249e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>2.810548786077118e-07</v>
+        <v>2.81054878607711e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>2.333228156862638e-07</v>
+        <v>2.333228156862635e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.647513435469377e-07</v>
+        <v>1.647513435469373e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>2.605369568454371e-07</v>
+        <v>2.605369568454368e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>2.605955492353581e-07</v>
+        <v>2.605955492353574e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>2.602935467070828e-07</v>
+        <v>2.602935467070824e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>2.606149402221153e-07</v>
+        <v>2.606149402221149e-07</v>
       </c>
       <c r="K6" t="n">
         <v>1.600953456156854e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>3.636619051434998e-07</v>
+        <v>3.636619051434994e-07</v>
       </c>
     </row>
     <row r="7">
@@ -718,7 +718,7 @@
         <v>1.377834581406584e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>1.737494566589815e-07</v>
+        <v>1.737494566589812e-07</v>
       </c>
       <c r="D7" t="n">
         <v>1.740514622792913e-07</v>
@@ -727,25 +727,25 @@
         <v>2.15601917834153e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>1.737494200014616e-07</v>
+        <v>1.737494200014617e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>1.739928667973358e-07</v>
+        <v>1.739928667973355e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>1.740514591872552e-07</v>
+        <v>1.740514591872551e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>1.737494566589815e-07</v>
+        <v>1.737494566589812e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>1.740514591872552e-07</v>
+        <v>1.740514591872551e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>1.53037638245926e-07</v>
+        <v>1.283835712529137e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>1.740514591872552e-07</v>
+        <v>1.740514591872551e-07</v>
       </c>
     </row>
     <row r="8">
@@ -755,37 +755,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.129908477934851e-08</v>
+        <v>2.129908477934793e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>1.948022917583351e-08</v>
+        <v>1.948022917583344e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>1.883962123709911e-08</v>
+        <v>1.883962123709898e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>1.948022917583351e-08</v>
+        <v>1.948022917583344e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>1.948022917583351e-08</v>
+        <v>1.948022917583344e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.258883102913952e-08</v>
+        <v>2.258883102913944e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>6.201465405900822e-09</v>
+        <v>6.201465405900854e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.948022917583351e-08</v>
+        <v>1.948022917583344e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.466628784649335e-08</v>
+        <v>2.466628784649329e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>2.542418024326627e-08</v>
+        <v>2.542418024326649e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>2.790675859272359e-08</v>
+        <v>2.790675859272356e-08</v>
       </c>
     </row>
     <row r="9">
@@ -795,37 +795,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.654779577831023e-08</v>
+        <v>2.654779577831035e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.174979435952174e-08</v>
+        <v>2.174979435952172e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>2.554638895067361e-08</v>
+        <v>2.554638895067355e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>2.174979435952174e-08</v>
+        <v>2.174979435952172e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.174979435952174e-08</v>
+        <v>2.174979435952172e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.704137330127063e-08</v>
+        <v>2.704137330127053e-08</v>
       </c>
       <c r="H9" t="n">
         <v>2.042150359905166e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.174979435952174e-08</v>
+        <v>2.174979435952172e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.792156397041605e-08</v>
+        <v>2.792156397041599e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.822820408805286e-08</v>
+        <v>2.822820408805279e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.924119555152723e-08</v>
+        <v>1.828895309095083e-08</v>
       </c>
     </row>
   </sheetData>
@@ -911,37 +911,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.31172094224209e-07</v>
+        <v>1.311720942242096e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>1.692107623922691e-07</v>
+        <v>1.692107623922695e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.798460775314915e-07</v>
+        <v>1.798460775314918e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.692107623922691e-07</v>
+        <v>1.692107623922695e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.692107623922691e-07</v>
+        <v>1.692107623922695e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.71445965096644e-07</v>
+        <v>1.714459650966433e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.916171655488511e-07</v>
+        <v>1.916171655488518e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.692107623922691e-07</v>
+        <v>1.692107623922695e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>2.182707071170221e-07</v>
+        <v>2.182707071170223e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.371884676106651e-07</v>
+        <v>1.371884676106654e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.794947993647032e-07</v>
+        <v>1.794947993647035e-07</v>
       </c>
     </row>
     <row r="3">
@@ -951,37 +951,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.383474804721348e-09</v>
+        <v>9.383474804721482e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>8.939804762932303e-09</v>
+        <v>8.939804762932323e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>9.383474804721348e-09</v>
+        <v>9.383474804721482e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>9.054048705352818e-09</v>
+        <v>9.054048705352947e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>9.054048705352822e-09</v>
+        <v>9.054048705352898e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>9.331560563048271e-09</v>
+        <v>9.331560563048389e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>9.383474804721348e-09</v>
+        <v>9.383474804721482e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>9.124121051533978e-09</v>
+        <v>9.124121051534123e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>9.383474804721348e-09</v>
+        <v>9.383474804721482e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>9.383474804721348e-09</v>
+        <v>9.383474804721482e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>9.383474804721348e-09</v>
+        <v>9.383474804721482e-09</v>
       </c>
     </row>
     <row r="4">
@@ -991,37 +991,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.699703963804612e-08</v>
+        <v>2.320374540545928e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>2.29203916130201e-08</v>
+        <v>2.29203916130206e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>3.726428723108952e-08</v>
+        <v>3.726428723108948e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>2.185133571467684e-08</v>
+        <v>2.185133571467663e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>2.298067051125998e-08</v>
+        <v>2.298067051126004e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>2.31518311637862e-08</v>
+        <v>3.694512539637311e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>3.756564040490161e-08</v>
+        <v>3.756564040490177e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>2.294439165227187e-08</v>
+        <v>2.294439165227196e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>3.713318755274423e-08</v>
+        <v>2.404641566564205e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>2.316848337931688e-08</v>
+        <v>2.316848337931692e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>2.322190109974802e-08</v>
+        <v>2.322190109974807e-08</v>
       </c>
     </row>
     <row r="5">
@@ -1031,37 +1031,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.51213726508533e-08</v>
+        <v>4.512137265085345e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>4.486201889766596e-08</v>
+        <v>4.486201889766598e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>4.511901048942464e-08</v>
+        <v>4.511901048942477e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>4.486329842553122e-08</v>
+        <v>4.486329842553131e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>4.486329842553122e-08</v>
+        <v>4.486329842553131e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>4.506945840918029e-08</v>
+        <v>4.506945840918033e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>4.51213726508533e-08</v>
+        <v>4.512137265085345e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>4.486201889766596e-08</v>
+        <v>4.486201889766598e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>4.51213726508533e-08</v>
+        <v>4.512137265085345e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>4.51213726508533e-08</v>
+        <v>4.512137265085345e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>4.51213726508533e-08</v>
+        <v>4.512137265085345e-08</v>
       </c>
     </row>
     <row r="6">
@@ -1071,37 +1071,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.40032623516946e-07</v>
+        <v>1.400326235169464e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>2.24900832961974e-07</v>
+        <v>2.249008329621832e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>2.427866320398819e-07</v>
+        <v>2.427866320398828e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>2.016220659224744e-07</v>
+        <v>2.01622065922475e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.424731900228125e-07</v>
+        <v>1.424731900228131e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>2.250873097673008e-07</v>
+        <v>2.250873097673018e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>2.251392240089741e-07</v>
+        <v>2.251392240089745e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>2.248798702557868e-07</v>
+        <v>2.248798702557878e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>2.251559499073103e-07</v>
+        <v>2.251559499073104e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.384517247178394e-07</v>
+        <v>1.384517247178397e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>3.14040184733099e-07</v>
+        <v>3.140401847331001e-07</v>
       </c>
     </row>
     <row r="7">
@@ -1111,37 +1111,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.68160975619152e-08</v>
+        <v>9.681609756191532e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.216479354593183e-07</v>
+        <v>1.216479354593186e-07</v>
       </c>
       <c r="D7" t="n">
         <v>1.219072985238701e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>1.506026243078714e-07</v>
+        <v>1.506026243078719e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>1.216479172878719e-07</v>
+        <v>1.216479172878717e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>1.218553749708325e-07</v>
+        <v>1.218553749708329e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>1.219072892125057e-07</v>
+        <v>1.219072892125059e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>1.216479354593183e-07</v>
+        <v>1.216479354593186e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>1.219072892125057e-07</v>
+        <v>1.219072892125059e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>1.073693581457653e-07</v>
+        <v>1.073693581457655e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>1.219072892125057e-07</v>
+        <v>1.219072892125059e-07</v>
       </c>
     </row>
     <row r="8">
@@ -1154,34 +1154,34 @@
         <v>2.860728578974069e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.094026148447188e-08</v>
+        <v>2.094026148447194e-08</v>
       </c>
       <c r="D8" t="n">
         <v>2.743641763275453e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.094026148447188e-08</v>
+        <v>2.094026148447194e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>2.094026148447188e-08</v>
+        <v>2.094026148447194e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.764582526098474e-08</v>
+        <v>2.764582526098469e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.755160981908976e-08</v>
+        <v>2.755160981908971e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.094026148447188e-08</v>
+        <v>2.094026148447194e-08</v>
       </c>
       <c r="J8" t="n">
         <v>2.662489829623669e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>2.851122855112327e-08</v>
+        <v>2.851122855112322e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>2.787421633221032e-08</v>
+        <v>2.787421633221024e-08</v>
       </c>
     </row>
     <row r="9">
@@ -1191,37 +1191,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.899713965852739e-08</v>
+        <v>2.899713965852737e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.195280739279198e-08</v>
+        <v>2.195280739279203e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>2.85203174119163e-08</v>
+        <v>2.852031741191629e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>2.195280739279198e-08</v>
+        <v>2.195280739279203e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.195280739279198e-08</v>
+        <v>2.195280739279203e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.858936100309136e-08</v>
+        <v>2.858936100309135e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.856932252562822e-08</v>
+        <v>2.856932252562815e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.195280739279198e-08</v>
+        <v>2.195280739279203e-08</v>
       </c>
       <c r="J9" t="n">
         <v>2.819096123733173e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.895808810624348e-08</v>
+        <v>2.895808810624344e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.875365955713376e-08</v>
+        <v>2.870006884633408e-08</v>
       </c>
     </row>
   </sheetData>
@@ -1307,34 +1307,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.222901508897998e-07</v>
+        <v>1.222901508897996e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>2.755615218627689e-07</v>
+        <v>2.755615218627686e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>4.059070558766436e-07</v>
+        <v>4.059070558766446e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>2.161378819984962e-07</v>
+        <v>2.161378819984956e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>2.161378819984962e-07</v>
+        <v>2.161378819984956e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>3.001147196069548e-07</v>
+        <v>3.001147196069547e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>7.062243832099794e-07</v>
+        <v>7.062243832099785e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>2.161378819984962e-07</v>
+        <v>2.161378819984956e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>3.588950044872087e-07</v>
+        <v>3.588950044872083e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>2.128699494007319e-07</v>
+        <v>2.128699494007313e-07</v>
       </c>
       <c r="L2" t="n">
         <v>4.201541786952031e-07</v>
@@ -1347,37 +1347,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.406723322978585e-09</v>
+        <v>9.406723322978701e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>8.550951276110697e-09</v>
+        <v>8.550951276110704e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>9.406723322978587e-09</v>
+        <v>9.406723322978674e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>8.950838397286356e-09</v>
+        <v>8.950838397286659e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>8.950838397286361e-09</v>
+        <v>8.950838397286654e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>9.350530755373849e-09</v>
+        <v>9.350530755374099e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>9.406723322978587e-09</v>
+        <v>9.406723322978702e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>9.120407671234034e-09</v>
+        <v>9.120407671234039e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>9.406723322978587e-09</v>
+        <v>9.406723322978702e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>9.406723322978587e-09</v>
+        <v>9.406723322978674e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>9.406723322978587e-09</v>
+        <v>9.406723322978674e-09</v>
       </c>
     </row>
     <row r="4">
@@ -1387,37 +1387,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.450685719762844e-08</v>
+        <v>3.972658361251513e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>2.426722144188986e-08</v>
+        <v>2.426722144188994e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>2.480070491325369e-08</v>
+        <v>2.480054858171643e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>2.291539308757225e-08</v>
+        <v>2.291539308757223e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>2.424123257561743e-08</v>
+        <v>2.424123257561736e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>3.967039104491034e-08</v>
+        <v>2.445066463002371e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>4.134183078703627e-08</v>
+        <v>4.13418307870364e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>3.944026796077055e-08</v>
+        <v>2.422054154588389e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>4.013704909342599e-08</v>
+        <v>4.013704909342604e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>2.442479590670002e-08</v>
+        <v>2.442479590670001e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>2.457707730033249e-08</v>
+        <v>2.45770773003325e-08</v>
       </c>
     </row>
     <row r="5">
@@ -1427,37 +1427,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.74887379512399e-08</v>
+        <v>4.748873795123992e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>4.73315764048413e-08</v>
+        <v>4.733157640484138e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>4.748637461450173e-08</v>
+        <v>4.74863746145017e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>4.720396177739957e-08</v>
+        <v>4.720396177739955e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>4.720396177739957e-08</v>
+        <v>4.720396177739955e-08</v>
       </c>
       <c r="G5" t="n">
         <v>4.743254538363519e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>4.74887379512399e-08</v>
+        <v>4.748873795123992e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>4.720242229949534e-08</v>
+        <v>4.720242229949542e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>4.74887379512399e-08</v>
+        <v>4.748873795123992e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>4.74887379512399e-08</v>
+        <v>4.748873795123992e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>4.74887379512399e-08</v>
+        <v>4.748873795123992e-08</v>
       </c>
     </row>
     <row r="6">
@@ -1467,37 +1467,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.487011848653513e-07</v>
+        <v>1.487011848653519e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>2.393930258419777e-07</v>
+        <v>2.393930258419778e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>2.583613559180391e-07</v>
+        <v>2.583613559180398e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>2.144205764458487e-07</v>
+        <v>2.144205764458488e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.512962626000835e-07</v>
+        <v>1.512962626000836e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>2.394716617563459e-07</v>
+        <v>2.394716617563461e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>2.395278543240015e-07</v>
+        <v>2.395278543240021e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>2.392415386722059e-07</v>
+        <v>2.392415386722062e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>2.395457043801114e-07</v>
+        <v>2.395457043801123e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.470140328483933e-07</v>
+        <v>1.470140328483934e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>3.34403905388718e-07</v>
+        <v>3.344039053887186e-07</v>
       </c>
     </row>
     <row r="7">
@@ -1513,31 +1513,31 @@
         <v>1.450445442219928e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>1.452017134817318e-07</v>
+        <v>1.452017134817321e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>1.797771515842615e-07</v>
+        <v>1.797771515842614e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>1.449153649573845e-07</v>
+        <v>1.449153649573844e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>1.451455132007866e-07</v>
+        <v>1.451455132007869e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>1.452017057683913e-07</v>
+        <v>1.452017057683916e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>1.449153901166469e-07</v>
+        <v>1.449153901166468e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>1.452017057683913e-07</v>
+        <v>1.452017057683916e-07</v>
       </c>
       <c r="K7" t="n">
         <v>1.276978729380507e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>1.452017057683913e-07</v>
+        <v>1.452017057683916e-07</v>
       </c>
     </row>
     <row r="8">
@@ -1547,34 +1547,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.032693913022161e-08</v>
+        <v>2.032693913022164e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>1.377093251256591e-08</v>
+        <v>1.377093251256593e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.09083791619904e-08</v>
+        <v>2.090837916199039e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>1.906880636493892e-08</v>
+        <v>1.906880636493893e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>1.906880636493892e-08</v>
+        <v>1.906880636493893e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.716615608516458e-08</v>
+        <v>2.716615608516462e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>1.577757305085087e-08</v>
+        <v>1.577757305085088e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>1.906880636493892e-08</v>
+        <v>1.906880636493893e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>1.88309953124173e-08</v>
+        <v>1.883099531241729e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>2.925695603717982e-08</v>
+        <v>2.925695603717988e-08</v>
       </c>
       <c r="L8" t="n">
         <v>2.123397572074477e-08</v>
@@ -1587,13 +1587,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.149687504071194e-08</v>
+        <v>2.149687504071196e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>1.618056749287086e-08</v>
+        <v>1.618056749287089e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>2.503122467749211e-08</v>
+        <v>2.503122467749212e-08</v>
       </c>
       <c r="E9" t="n">
         <v>2.066748785757403e-08</v>
@@ -1602,10 +1602,10 @@
         <v>2.066748785757403e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.969497440912717e-08</v>
+        <v>2.969497440912719e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.295307082965021e-08</v>
+        <v>2.29530708296502e-08</v>
       </c>
       <c r="I9" t="n">
         <v>2.066748785757403e-08</v>
@@ -1614,10 +1614,10 @@
         <v>2.214863460682897e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>3.066524464652454e-08</v>
+        <v>3.066524464652458e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.486182674665131e-08</v>
+        <v>2.486182674665133e-08</v>
       </c>
     </row>
   </sheetData>
@@ -1703,37 +1703,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.703254427529121e-08</v>
+        <v>7.703254427529127e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>2.190933287899243e-07</v>
+        <v>2.190933287899249e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>3.119500972891449e-07</v>
+        <v>3.119500972891447e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.713665719974643e-07</v>
+        <v>1.713665719974648e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.713665719974643e-07</v>
+        <v>1.713665719974648e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>2.228928323817647e-07</v>
+        <v>2.228928323817693e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>4.307435792107089e-07</v>
+        <v>4.30743579210709e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.713665719974643e-07</v>
+        <v>1.713665719974648e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>2.54755275964267e-07</v>
+        <v>2.547552759642672e-07</v>
       </c>
       <c r="K2" t="n">
         <v>1.4863946906799e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>2.153619997938588e-07</v>
+        <v>2.15361999793859e-07</v>
       </c>
     </row>
     <row r="3">
@@ -1743,37 +1743,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.256616975581432e-09</v>
+        <v>9.256616975581619e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>8.427059156811109e-09</v>
+        <v>8.427059156811152e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>9.256616975581432e-09</v>
+        <v>9.256616975581617e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>8.916583658806719e-09</v>
+        <v>8.916583658806842e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>8.916583658806777e-09</v>
+        <v>8.916583658806842e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>9.201654131900001e-09</v>
+        <v>9.201654131900127e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>9.256616975581432e-09</v>
+        <v>9.256616975581617e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>8.978136939799519e-09</v>
+        <v>8.978136939799592e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>9.256616975581432e-09</v>
+        <v>9.256616975581619e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>9.256616975581432e-09</v>
+        <v>9.256616975581617e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>9.256616975581432e-09</v>
+        <v>9.256616975581617e-09</v>
       </c>
     </row>
     <row r="4">
@@ -1783,37 +1783,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.749362977541449e-08</v>
+        <v>3.749362977541462e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>2.299815723843158e-08</v>
+        <v>2.29981572384311e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>3.805797531118256e-08</v>
+        <v>3.805797531118286e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>2.175582431443562e-08</v>
+        <v>2.175582431443566e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>2.296590684718869e-08</v>
+        <v>2.296590684718875e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>2.315898045577788e-08</v>
+        <v>3.743866693173303e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>3.919082193006713e-08</v>
+        <v>3.919082193006727e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>2.293546326367736e-08</v>
+        <v>2.293546326367742e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>2.408724713636754e-08</v>
+        <v>2.408724713636759e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>2.313047760120057e-08</v>
+        <v>2.313047760120064e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>2.323724867710523e-08</v>
+        <v>2.323724867710534e-08</v>
       </c>
     </row>
     <row r="5">
@@ -1823,37 +1823,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.55845008568563e-08</v>
+        <v>4.558450085685643e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>4.542865786007814e-08</v>
+        <v>4.542865786007816e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>4.558226725971213e-08</v>
+        <v>4.558226725971215e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>4.533208886723321e-08</v>
+        <v>4.533208886723331e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>4.533208886723321e-08</v>
+        <v>4.533208886723331e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>4.552953801317483e-08</v>
+        <v>4.552953801317481e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>4.55845008568563e-08</v>
+        <v>4.558450085685643e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>4.530602082107429e-08</v>
+        <v>4.530602082107434e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>4.55845008568563e-08</v>
+        <v>4.558450085685643e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>4.55845008568563e-08</v>
+        <v>4.558450085685643e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>4.55845008568563e-08</v>
+        <v>4.558450085685643e-08</v>
       </c>
     </row>
     <row r="6">
@@ -1863,37 +1863,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.41489650572248e-07</v>
+        <v>1.414896505722482e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>2.276972892632013e-07</v>
+        <v>2.276972892629029e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>2.457071634913693e-07</v>
+        <v>2.457071634913695e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>2.039619008728245e-07</v>
+        <v>2.039619008728247e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.4396422512753e-07</v>
+        <v>1.439642251275301e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>2.277534441817213e-07</v>
+        <v>2.277534441817214e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>2.278084070255332e-07</v>
+        <v>2.278084070255335e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>2.275299269896209e-07</v>
+        <v>2.275299269896208e-07</v>
       </c>
       <c r="J6" t="n">
         <v>2.2782537114642e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.398862353537941e-07</v>
+        <v>1.398862353537943e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>3.179755660096022e-07</v>
+        <v>3.179755660096023e-07</v>
       </c>
     </row>
     <row r="7">
@@ -1903,37 +1903,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.023885158749694e-07</v>
+        <v>1.023885158749697e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>1.289895925441024e-07</v>
+        <v>1.289895925441023e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>1.291454443759957e-07</v>
+        <v>1.291454443759959e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>1.597438554764727e-07</v>
+        <v>1.59743855476473e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>1.288669347278915e-07</v>
+        <v>1.288669347278918e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>1.29090472697199e-07</v>
+        <v>1.290904726971989e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>1.291454355408804e-07</v>
+        <v>1.291454355408807e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>1.288669555050984e-07</v>
+        <v>1.288669555050985e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>1.291454355408804e-07</v>
+        <v>1.291454355408807e-07</v>
       </c>
       <c r="K7" t="n">
         <v>1.136423749199363e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>1.291454355408804e-07</v>
+        <v>1.291454355408807e-07</v>
       </c>
     </row>
     <row r="8">
@@ -1943,37 +1943,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.115533345593645e-08</v>
+        <v>2.115533345593647e-08</v>
       </c>
       <c r="C8" t="n">
         <v>1.466893982085351e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.262501154870926e-08</v>
+        <v>2.26250115487093e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>1.991022127182272e-08</v>
+        <v>1.991022127182274e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>1.991022127182272e-08</v>
+        <v>1.991022127182274e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.854559223670908e-08</v>
+        <v>2.854559223670902e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.084939963775207e-08</v>
+        <v>2.084939963775212e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>1.991022127182272e-08</v>
+        <v>1.991022127182274e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.088599863775256e-08</v>
+        <v>2.088599863775264e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>3.041404849023879e-08</v>
+        <v>3.041404849023893e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>2.512072196223363e-08</v>
+        <v>2.51207219622337e-08</v>
       </c>
     </row>
     <row r="9">
@@ -1983,37 +1983,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.178033089110125e-08</v>
+        <v>2.178033089110127e-08</v>
       </c>
       <c r="C9" t="n">
         <v>1.648813265574647e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>2.569742821251102e-08</v>
+        <v>2.569742821251101e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>2.102866699668435e-08</v>
+        <v>2.102866699668436e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.102866699668435e-08</v>
+        <v>2.102866699668436e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>3.021147365024102e-08</v>
+        <v>3.021147365024104e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.498109170041735e-08</v>
+        <v>2.498109170041743e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.102866699668435e-08</v>
+        <v>2.102866699668436e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.302967959758933e-08</v>
+        <v>2.302967959758937e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>3.105875758221382e-08</v>
+        <v>3.1058757582214e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.646003424125762e-08</v>
+        <v>2.646003424125765e-08</v>
       </c>
     </row>
   </sheetData>
@@ -2099,37 +2099,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.533321102686825e-08</v>
+        <v>5.533321102686824e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.806259566777207e-07</v>
+        <v>1.806259566777204e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>2.546993268080718e-07</v>
+        <v>2.546993268080708e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.389545253771424e-07</v>
+        <v>1.389545253771423e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.389545253771424e-07</v>
+        <v>1.389545253771423e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.805754237370901e-07</v>
+        <v>1.805754237370941e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>2.998964285339338e-07</v>
+        <v>2.998964285339341e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.389545253771424e-07</v>
+        <v>1.389545253771423e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>1.733946140574753e-07</v>
+        <v>1.733946140574755e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.260629689860199e-07</v>
+        <v>1.260629689860197e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.6254864184983e-07</v>
+        <v>1.625486418498299e-07</v>
       </c>
     </row>
     <row r="3">
@@ -2139,37 +2139,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.306899834860908e-09</v>
+        <v>9.306899834860797e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>8.450956953818538e-09</v>
+        <v>8.4509569538185e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>9.306899834860906e-09</v>
+        <v>9.306899834860812e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>8.991885028386572e-09</v>
+        <v>8.991885028386513e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>8.991885028386574e-09</v>
+        <v>8.991885028386529e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>9.252317019504933e-09</v>
+        <v>9.252317019504921e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>9.306899834860906e-09</v>
+        <v>9.306899834860812e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>9.030901602257786e-09</v>
+        <v>9.030901602257808e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>9.306899834860908e-09</v>
+        <v>9.306899834860812e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>9.306899834860906e-09</v>
+        <v>9.306899834860812e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>9.306899834860906e-09</v>
+        <v>9.306899834860812e-09</v>
       </c>
     </row>
     <row r="4">
@@ -2179,37 +2179,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.303760155240823e-08</v>
+        <v>2.303760155240812e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>2.281055276576164e-08</v>
+        <v>2.281055276576174e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>2.322842792548337e-08</v>
+        <v>2.322857148952375e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>2.159679788947399e-08</v>
+        <v>2.159679788947378e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>2.279120054444306e-08</v>
+        <v>2.279120054444297e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>3.720908654524654e-08</v>
+        <v>3.720908654524647e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>3.915128060441244e-08</v>
+        <v>3.915128060441226e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>3.698767112799937e-08</v>
+        <v>3.69876711279993e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>3.770331554147413e-08</v>
+        <v>3.770331554147401e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>2.297671335839985e-08</v>
+        <v>2.29767133583994e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>2.305146289392925e-08</v>
+        <v>2.305146289392891e-08</v>
       </c>
     </row>
     <row r="5">
@@ -2219,37 +2219,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.573783728017276e-08</v>
+        <v>4.573783728017274e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>4.558231657185832e-08</v>
+        <v>4.558231657185833e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>4.573560857808972e-08</v>
+        <v>4.573560857808966e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>4.549534744030524e-08</v>
+        <v>4.549534744030514e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>4.549534744030524e-08</v>
+        <v>4.549534744030514e-08</v>
       </c>
       <c r="G5" t="n">
         <v>4.568325446481678e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>4.573783728017276e-08</v>
+        <v>4.573783728017274e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>4.54618390475697e-08</v>
+        <v>4.546183904756966e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>4.573783728017276e-08</v>
+        <v>4.573783728017274e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>4.573783728017276e-08</v>
+        <v>4.573783728017274e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>4.573783728017276e-08</v>
+        <v>4.573783728017274e-08</v>
       </c>
     </row>
     <row r="6">
@@ -2259,37 +2259,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.416985056632643e-07</v>
+        <v>1.416985056632641e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>2.280643641954678e-07</v>
+        <v>2.280643641958396e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>2.460980324162158e-07</v>
+        <v>2.460980324162156e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>2.042891440713848e-07</v>
+        <v>2.042891440713846e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.441847762988218e-07</v>
+        <v>1.441847762988214e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>2.281134333093034e-07</v>
+        <v>2.281134333093033e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>2.281680161248676e-07</v>
+        <v>2.281680161248677e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>2.278920178920564e-07</v>
+        <v>2.278920178920562e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>2.28185009872792e-07</v>
+        <v>2.281850098727919e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.400922901116483e-07</v>
+        <v>1.400922901116481e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>3.184926502762924e-07</v>
+        <v>3.184926502762919e-07</v>
       </c>
     </row>
     <row r="7">
@@ -2299,10 +2299,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.721600898699039e-08</v>
+        <v>9.721600898699048e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.223947805556847e-07</v>
+        <v>1.223947805556845e-07</v>
       </c>
       <c r="D7" t="n">
         <v>1.225503107314298e-07</v>
@@ -2311,22 +2311,22 @@
         <v>1.515095236662838e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>1.222742838014962e-07</v>
+        <v>1.222742838014961e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>1.224957184486432e-07</v>
+        <v>1.224957184486429e-07</v>
       </c>
       <c r="H7" t="n">
         <v>1.22550301263999e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>1.22274303031396e-07</v>
+        <v>1.222743030313959e-07</v>
       </c>
       <c r="J7" t="n">
         <v>1.22550301263999e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>9.064990267831616e-08</v>
+        <v>1.072759795935431e-07</v>
       </c>
       <c r="L7" t="n">
         <v>1.22550301263999e-07</v>
@@ -2339,37 +2339,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.158937556148096e-08</v>
+        <v>2.158937556148094e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>1.543687939126944e-08</v>
+        <v>1.543687939126941e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.389198091538589e-08</v>
+        <v>2.389198091538584e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.060286533428635e-08</v>
+        <v>2.060286533428631e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>2.060286533428635e-08</v>
+        <v>2.060286533428631e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.943952144682943e-08</v>
+        <v>2.943952144682936e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.353514756821376e-08</v>
+        <v>2.353514756821369e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.060286533428635e-08</v>
+        <v>2.060286533428631e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.273929686508668e-08</v>
+        <v>2.273929686508659e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>3.080763979198806e-08</v>
+        <v>3.080763979198794e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>2.621492037660921e-08</v>
+        <v>2.621492037660917e-08</v>
       </c>
     </row>
     <row r="9">
@@ -2382,34 +2382,34 @@
         <v>2.191159989865005e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>1.671735875220065e-08</v>
+        <v>1.671735875220061e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>2.613870283681156e-08</v>
+        <v>2.613870283681151e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>2.125896390847609e-08</v>
+        <v>2.125896390847605e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.125896390847609e-08</v>
+        <v>2.125896390847605e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>3.051311818990388e-08</v>
+        <v>3.051311818990384e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.599763897575071e-08</v>
+        <v>2.599763897575066e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.125896390847609e-08</v>
+        <v>2.125896390847605e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.376590366584357e-08</v>
+        <v>2.376590366584352e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>3.112986629909075e-08</v>
+        <v>3.112986629909073e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.689358214727726e-08</v>
+        <v>2.689358214727723e-08</v>
       </c>
     </row>
   </sheetData>
@@ -2495,34 +2495,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.568434661975119e-08</v>
+        <v>5.568434661975125e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.231590258313731e-07</v>
+        <v>1.231590258313732e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>2.884712142985515e-07</v>
+        <v>2.884712142985514e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.549909921922569e-07</v>
+        <v>1.549909921922561e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.549909921922569e-07</v>
+        <v>1.549909921922561e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>2.350830719629478e-07</v>
+        <v>2.350830719629539e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>5.849268824354491e-07</v>
+        <v>5.849268824354486e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.549909921922569e-07</v>
+        <v>1.549909921922561e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>3.442199200409544e-07</v>
+        <v>3.442199200409555e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.769459599961463e-07</v>
+        <v>1.769459599961464e-07</v>
       </c>
       <c r="L2" t="n">
         <v>4.106670879229748e-07</v>
@@ -2535,37 +2535,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.013130338153803e-09</v>
+        <v>9.013130338153829e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>8.08171640974278e-09</v>
+        <v>8.081716409742784e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>9.013130338153803e-09</v>
+        <v>9.013130338153829e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>8.698211915682962e-09</v>
+        <v>8.698211915682986e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>8.698211915682966e-09</v>
+        <v>8.698211915682985e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>8.957248085565348e-09</v>
+        <v>8.957248085565368e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>9.013130338153803e-09</v>
+        <v>9.013130338153829e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>8.728655077954001e-09</v>
+        <v>8.728655077954005e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>9.013130338153803e-09</v>
+        <v>9.013130338153829e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>9.013130338153803e-09</v>
+        <v>9.013130338153829e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>9.013130338153803e-09</v>
+        <v>9.013130338153829e-09</v>
       </c>
     </row>
     <row r="4">
@@ -2575,37 +2575,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.368956564862891e-08</v>
+        <v>2.368956564862893e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>2.327378672870766e-08</v>
+        <v>2.327378672870712e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>2.386929017417021e-08</v>
+        <v>2.386944550272006e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>2.214264097251469e-08</v>
+        <v>2.214264097251465e-08</v>
       </c>
       <c r="F4" t="n">
         <v>2.343597621196692e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>2.363368339604041e-08</v>
+        <v>2.363368339604047e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>4.014354416296125e-08</v>
+        <v>4.014354416296132e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>2.34050903884291e-08</v>
+        <v>3.830869004263504e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>3.89887769273487e-08</v>
+        <v>2.463063950673201e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>2.365614794937035e-08</v>
+        <v>2.365614794937039e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>2.377831507686739e-08</v>
+        <v>2.377831507686743e-08</v>
       </c>
     </row>
     <row r="5">
@@ -2615,37 +2615,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.700301859810201e-08</v>
+        <v>4.700301859810207e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>4.684418293868196e-08</v>
+        <v>4.684418293868206e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>4.700066386506623e-08</v>
+        <v>4.700066386506627e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>4.675876626807611e-08</v>
+        <v>4.675876626807614e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>4.675876626807611e-08</v>
+        <v>4.675876626807614e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>4.694713634551353e-08</v>
+        <v>4.694713634551357e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>4.700301859810201e-08</v>
+        <v>4.700301859810207e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>4.671854333790221e-08</v>
+        <v>4.671854333790223e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>4.700301859810201e-08</v>
+        <v>4.700301859810207e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>4.700301859810201e-08</v>
+        <v>4.700301859810207e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>4.700301859810201e-08</v>
+        <v>4.700301859810207e-08</v>
       </c>
     </row>
     <row r="6">
@@ -2655,37 +2655,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.480499285168223e-07</v>
+        <v>1.480499285168226e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>2.386100706038744e-07</v>
+        <v>2.386100706041542e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>2.575085386167894e-07</v>
+        <v>2.575085386167898e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>2.136829030882833e-07</v>
+        <v>2.136829030882838e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.506646261997596e-07</v>
+        <v>1.5066462619976e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>2.386537717006542e-07</v>
+        <v>2.386537717006544e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>2.387096539532845e-07</v>
+        <v>2.387096539532852e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>2.384251786930427e-07</v>
+        <v>2.384251786930433e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>2.387274712001818e-07</v>
+        <v>2.38727471200182e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.463658775707848e-07</v>
+        <v>1.463658775707851e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>3.334113180272546e-07</v>
+        <v>3.334113180272552e-07</v>
       </c>
     </row>
     <row r="7">
@@ -2695,34 +2695,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.127873739168899e-07</v>
+        <v>1.127873739168897e-07</v>
       </c>
       <c r="C7" t="n">
         <v>1.423364596617637e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>1.424953034233192e-07</v>
+        <v>1.424953034233189e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>1.764931094860206e-07</v>
+        <v>1.764931094860202e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>1.42210796628986e-07</v>
+        <v>1.422107966289859e-07</v>
       </c>
       <c r="G7" t="n">
         <v>1.424394130685953e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>1.424952953211837e-07</v>
+        <v>1.424952953211838e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>1.422108200609838e-07</v>
+        <v>1.422108200609839e-07</v>
       </c>
       <c r="J7" t="n">
         <v>1.424952953211837e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>1.05087717328066e-07</v>
+        <v>1.252824123952537e-07</v>
       </c>
       <c r="L7" t="n">
         <v>1.424952953211837e-07</v>
@@ -2735,37 +2735,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.261066709133016e-08</v>
+        <v>2.261066709133019e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>1.664195484885712e-08</v>
+        <v>1.664195484885714e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.315579825795741e-08</v>
+        <v>2.315579825795747e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.014171752483635e-08</v>
+        <v>2.014171752483642e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>2.014171752483635e-08</v>
+        <v>2.014171752483642e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.842863748024333e-08</v>
+        <v>2.842863748024336e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>1.778433528838871e-08</v>
+        <v>1.778433528838876e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.014171752483635e-08</v>
+        <v>2.014171752483642e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>1.894704909631124e-08</v>
+        <v>1.894704909631123e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>2.985628521828279e-08</v>
+        <v>2.98562852182828e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>2.121774874418491e-08</v>
+        <v>2.121774874418493e-08</v>
       </c>
     </row>
     <row r="9">
@@ -2775,37 +2775,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.288864784060868e-08</v>
+        <v>2.288864784060871e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>1.703400709846602e-08</v>
+        <v>1.703400709846604e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>2.568228674305407e-08</v>
+        <v>2.568228674305408e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>2.092130405786422e-08</v>
+        <v>2.09213040578642e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.092130405786422e-08</v>
+        <v>2.09213040578642e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>3.010043370650627e-08</v>
+        <v>3.010043370650628e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.350388648246188e-08</v>
+        <v>2.350388648246189e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.092130405786422e-08</v>
+        <v>2.09213040578642e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.208166840290695e-08</v>
+        <v>2.208166840290693e-08</v>
       </c>
       <c r="K9" t="n">
         <v>3.07830642756798e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.474057800221747e-08</v>
+        <v>2.474057800221751e-08</v>
       </c>
     </row>
   </sheetData>
@@ -2891,31 +2891,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.789617177504079e-08</v>
+        <v>5.789617177504075e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.267368563915147e-07</v>
+        <v>1.267368563915145e-07</v>
       </c>
       <c r="D2" t="n">
         <v>1.58614042096571e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.483856296805631e-07</v>
+        <v>1.483856296805618e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.483856296805631e-07</v>
+        <v>1.483856296805618e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.460459815975532e-07</v>
+        <v>1.460459815975529e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.818634917904482e-07</v>
+        <v>1.818634917904481e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.483856296805631e-07</v>
+        <v>1.483856296805618e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>2.026539955857039e-07</v>
+        <v>2.02653995585704e-07</v>
       </c>
       <c r="K2" t="n">
         <v>1.252605877348062e-07</v>
@@ -2931,37 +2931,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.994051808659057e-09</v>
+        <v>8.994051808659065e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>8.159448110272272e-09</v>
+        <v>8.159448110272305e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>8.994051808659057e-09</v>
+        <v>8.994051808659065e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>8.792010769437869e-09</v>
+        <v>8.792010769437861e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>8.792010769437869e-09</v>
+        <v>8.792010769437861e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>8.941214494305614e-09</v>
+        <v>8.941214494305637e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>8.994051808659057e-09</v>
+        <v>8.994051808659065e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>8.729033447270969e-09</v>
+        <v>8.729033447270951e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>8.994051808659057e-09</v>
+        <v>8.994051808659065e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>8.994051808659057e-09</v>
+        <v>8.994051808659065e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>8.994051808659057e-09</v>
+        <v>8.994051808659065e-09</v>
       </c>
     </row>
     <row r="4">
@@ -2971,37 +2971,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.25938326190747e-08</v>
+        <v>2.259383261907477e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>2.231910516448889e-08</v>
+        <v>2.231910516448862e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>2.262668579918808e-08</v>
+        <v>3.704493367207387e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>2.125199752617319e-08</v>
+        <v>2.125199752617318e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>2.237125063794667e-08</v>
+        <v>2.237125063794676e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>3.647706486822266e-08</v>
+        <v>2.25409953047213e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>3.812528958922428e-08</v>
+        <v>3.812528958922425e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>3.626488382118799e-08</v>
+        <v>3.626488382118797e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>2.343456893834268e-08</v>
+        <v>3.691166938177612e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>2.256959396915638e-08</v>
+        <v>2.25695939691564e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>2.261245099405164e-08</v>
+        <v>2.261245099405165e-08</v>
       </c>
     </row>
     <row r="5">
@@ -3011,37 +3011,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.518617543446479e-08</v>
+        <v>4.518617543446482e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>4.50312142480253e-08</v>
+        <v>4.503121424802531e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>4.518394461757159e-08</v>
+        <v>4.518394461757156e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>4.497357167865496e-08</v>
+        <v>4.497357167865486e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>4.497357167865496e-08</v>
+        <v>4.497357167865486e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>4.513333812011137e-08</v>
+        <v>4.513333812011134e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>4.518617543446479e-08</v>
+        <v>4.518617543446482e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>4.49211570730767e-08</v>
+        <v>4.492115707307676e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>4.518617543446479e-08</v>
+        <v>4.518617543446482e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>4.518617543446479e-08</v>
+        <v>4.518617543446482e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>4.518617543446479e-08</v>
+        <v>4.518617543446482e-08</v>
       </c>
     </row>
     <row r="6">
@@ -3051,37 +3051,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.408540978176053e-07</v>
+        <v>1.408540978176051e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>2.268365117375775e-07</v>
+        <v>2.268365117372801e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>2.447682833306104e-07</v>
+        <v>2.447682833306105e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>2.03179760806528e-07</v>
+        <v>2.031797608065279e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.43349885702322e-07</v>
+        <v>1.433498857023219e-07</v>
       </c>
       <c r="G6" t="n">
         <v>2.268687842819687e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>2.269216215964439e-07</v>
+        <v>2.269216215964438e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>2.26656603234934e-07</v>
+        <v>2.266566032349338e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>2.269385363430783e-07</v>
+        <v>2.269385363430784e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.392553493750551e-07</v>
+        <v>1.39255349375055e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>3.168263470444903e-07</v>
+        <v>3.168263470444902e-07</v>
       </c>
     </row>
     <row r="7">
@@ -3094,34 +3094,34 @@
         <v>1.00416105521724e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>1.265389981405962e-07</v>
+        <v>1.265389981405961e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>1.266939693517613e-07</v>
+        <v>1.266939693517612e-07</v>
       </c>
       <c r="E7" t="n">
         <v>1.567530144018712e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>1.264289235762501e-07</v>
+        <v>1.264289235762502e-07</v>
       </c>
       <c r="G7" t="n">
         <v>1.266411220126821e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>1.266939593270355e-07</v>
+        <v>1.266939593270354e-07</v>
       </c>
       <c r="I7" t="n">
         <v>1.264289409656474e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>1.266939593270355e-07</v>
+        <v>1.266939593270354e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>9.360544820764327e-08</v>
+        <v>1.114684718475047e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>1.266939593270355e-07</v>
+        <v>1.266939593270354e-07</v>
       </c>
     </row>
     <row r="8">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.290197221119512e-08</v>
+        <v>2.290197221119509e-08</v>
       </c>
       <c r="C8" t="n">
         <v>1.644873169808629e-08</v>
@@ -3140,28 +3140,28 @@
         <v>2.603986584655465e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.022857521620285e-08</v>
+        <v>2.022857521620286e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>2.022857521620285e-08</v>
+        <v>2.022857521620286e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>3.021943691883734e-08</v>
+        <v>3.021943691883729e-08</v>
       </c>
       <c r="H8" t="n">
         <v>2.587912052676843e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.022857521620285e-08</v>
+        <v>2.022857521620286e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.177260180295052e-08</v>
+        <v>2.177260180295055e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>3.079147215966484e-08</v>
+        <v>3.079147215966456e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>2.566288942727328e-08</v>
+        <v>2.56628894272733e-08</v>
       </c>
     </row>
     <row r="9">
@@ -3171,37 +3171,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.324088509012205e-08</v>
+        <v>2.324088509012204e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>1.697802482746272e-08</v>
+        <v>1.697802482746273e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>2.690309097365059e-08</v>
+        <v>2.690309097365057e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>2.102523065312199e-08</v>
+        <v>2.1025230653122e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.102523065312199e-08</v>
+        <v>2.1025230653122e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>3.081178661747512e-08</v>
+        <v>3.081178661747506e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.683958915205972e-08</v>
+        <v>2.683958915205971e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.102523065312199e-08</v>
+        <v>2.1025230653122e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.320857212561469e-08</v>
+        <v>2.320857212561468e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>3.110571819925611e-08</v>
+        <v>3.11057181992558e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.655295179992504e-08</v>
+        <v>2.655295179992503e-08</v>
       </c>
     </row>
   </sheetData>
@@ -3287,37 +3287,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.069204458324923e-08</v>
+        <v>6.069204458324918e-08</v>
       </c>
       <c r="C2" t="n">
         <v>1.334090384506791e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.589665275263016e-07</v>
+        <v>1.589665275263017e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.439869145618799e-07</v>
+        <v>1.439869145618807e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.439869145618799e-07</v>
+        <v>1.439869145618807e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.432637007950096e-07</v>
+        <v>1.432637007950109e-07</v>
       </c>
       <c r="H2" t="n">
         <v>1.671591230527352e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.439869145618799e-07</v>
+        <v>1.439869145618807e-07</v>
       </c>
       <c r="J2" t="n">
         <v>1.693613954624687e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.254793386931369e-07</v>
+        <v>1.254793386931368e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.571612068175299e-07</v>
+        <v>1.571612068175298e-07</v>
       </c>
     </row>
     <row r="3">
@@ -3327,37 +3327,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.497418079192038e-09</v>
+        <v>9.497418079191807e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>8.653137007384475e-09</v>
+        <v>8.653137007384503e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>9.497418079192038e-09</v>
+        <v>9.497418079191807e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>9.290519439811851e-09</v>
+        <v>9.290519439811848e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>9.290519439811845e-09</v>
+        <v>9.290519439811848e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>9.444449049764758e-09</v>
+        <v>9.444449049762409e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>9.497418079192038e-09</v>
+        <v>9.497418079191805e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>9.231718040937217e-09</v>
+        <v>9.231718040933513e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>9.497418079192038e-09</v>
+        <v>9.497418079191805e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>9.497418079192038e-09</v>
+        <v>9.497418079191807e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>9.497418079192038e-09</v>
+        <v>9.497418079191807e-09</v>
       </c>
     </row>
     <row r="4">
@@ -3367,37 +3367,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.732969641790005e-08</v>
+        <v>3.732969641789996e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>2.282329883655417e-08</v>
+        <v>2.282329883655364e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>2.311626560772087e-08</v>
+        <v>2.311626560772094e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>2.171859819323013e-08</v>
+        <v>2.171859819323e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>2.286328888984104e-08</v>
+        <v>2.286328888984121e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>3.727672738847082e-08</v>
+        <v>3.72767273884708e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>3.920868544049036e-08</v>
+        <v>2.310632770449409e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>2.282314659099195e-08</v>
+        <v>3.706399637964154e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>3.777048041669804e-08</v>
+        <v>2.393586560602818e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>2.306819439215674e-08</v>
+        <v>2.306819439215698e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>2.310060406840377e-08</v>
+        <v>2.310060406840362e-08</v>
       </c>
     </row>
     <row r="5">
@@ -3407,37 +3407,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.609885196558803e-08</v>
+        <v>4.609885196558804e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>4.59437427747142e-08</v>
+        <v>4.594374277471424e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>4.609661777722309e-08</v>
+        <v>4.609661777722312e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>4.588770997006104e-08</v>
+        <v>4.588770997006106e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>4.588770997006104e-08</v>
+        <v>4.588770997006106e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>4.604588293615884e-08</v>
+        <v>4.604588293615876e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>4.609885196558803e-08</v>
+        <v>4.609885196558804e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>4.583315192732956e-08</v>
+        <v>4.583315192732962e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>4.609885196558803e-08</v>
+        <v>4.609885196558804e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>4.609885196558803e-08</v>
+        <v>4.609885196558804e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>4.609885196558803e-08</v>
+        <v>4.609885196558804e-08</v>
       </c>
     </row>
     <row r="6">
@@ -3447,16 +3447,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.420528585110762e-07</v>
+        <v>1.420528585110759e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>2.286573136670218e-07</v>
+        <v>2.286573136674116e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>2.467156036127836e-07</v>
+        <v>2.467156036127833e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>2.048302186395894e-07</v>
+        <v>2.048302186395895e-07</v>
       </c>
       <c r="F6" t="n">
         <v>1.445688984001635e-07</v>
@@ -3468,13 +3468,13 @@
         <v>2.287403810890293e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>2.284746810505669e-07</v>
+        <v>2.284746810505668e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>2.28757417681031e-07</v>
+        <v>2.287574176810306e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.404425932726326e-07</v>
+        <v>1.404425932726324e-07</v>
       </c>
       <c r="L6" t="n">
         <v>3.192927471244169e-07</v>
@@ -3487,34 +3487,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.680711025193178e-08</v>
+        <v>9.68071102519319e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.218701019940346e-07</v>
+        <v>1.218701019940348e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>1.220252214453144e-07</v>
+        <v>1.220252214453145e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>1.508606526332239e-07</v>
+        <v>1.50860652633224e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>1.217594939025194e-07</v>
+        <v>1.217594939025195e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>1.219722421554793e-07</v>
+        <v>1.219722421554794e-07</v>
       </c>
       <c r="H7" t="n">
         <v>1.220252111849084e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>1.217595111466501e-07</v>
+        <v>1.217595111466502e-07</v>
       </c>
       <c r="J7" t="n">
         <v>1.220252111849084e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>1.06820942877648e-07</v>
+        <v>1.074137487807057e-07</v>
       </c>
       <c r="L7" t="n">
         <v>1.220252111849084e-07</v>
@@ -3527,37 +3527,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.372613791644332e-08</v>
+        <v>2.372613791644334e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>1.649508664794364e-08</v>
+        <v>1.649508664794367e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.634341578136238e-08</v>
+        <v>2.63434157813624e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.06447286803131e-08</v>
+        <v>2.064472868031312e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>2.06447286803131e-08</v>
+        <v>2.064472868031312e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>3.058814775445411e-08</v>
+        <v>3.05881477544541e-08</v>
       </c>
       <c r="H8" t="n">
         <v>2.650699592877281e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.06447286803131e-08</v>
+        <v>2.064472868031312e-08</v>
       </c>
       <c r="J8" t="n">
         <v>2.302025911146006e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>3.104091476214868e-08</v>
+        <v>3.10409147621487e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>2.640508706035524e-08</v>
+        <v>2.640508706035529e-08</v>
       </c>
     </row>
     <row r="9">
@@ -3567,37 +3567,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.408805657127596e-08</v>
+        <v>2.4088056571276e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>1.711264045684282e-08</v>
+        <v>1.711264045684283e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>2.720434557969297e-08</v>
+        <v>2.720434557969305e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>2.137106009057111e-08</v>
+        <v>2.137106009057113e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.137106009057111e-08</v>
+        <v>2.137106009057113e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>3.113427316238884e-08</v>
+        <v>3.113427316238881e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.727263980616678e-08</v>
+        <v>2.727263980616671e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.137106009057111e-08</v>
+        <v>2.137106009057113e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.39890381478825e-08</v>
+        <v>2.398903814788255e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>3.135183042448958e-08</v>
+        <v>3.135183042448954e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.701562034533597e-08</v>
+        <v>2.701562034533593e-08</v>
       </c>
     </row>
   </sheetData>
@@ -3683,37 +3683,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.738631250499752e-08</v>
+        <v>5.738631250499764e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.261642562957887e-07</v>
+        <v>1.261642562957885e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.786042160176886e-07</v>
+        <v>1.786042160176893e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.558915780655653e-07</v>
+        <v>1.558915780655655e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.558915780655653e-07</v>
+        <v>1.558915780655655e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.724956549212001e-07</v>
+        <v>1.724956549212073e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>5.106528671015374e-07</v>
+        <v>5.106528671015386e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.558915780655653e-07</v>
+        <v>1.558915780655655e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>1.639730118116251e-07</v>
+        <v>1.639730118116254e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.325242181666201e-07</v>
+        <v>1.325242181666209e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>3.587730042488136e-07</v>
+        <v>3.587730042488144e-07</v>
       </c>
     </row>
     <row r="3">
@@ -3723,37 +3723,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.977292411894232e-09</v>
+        <v>8.977292411894917e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>8.093550481976658e-09</v>
+        <v>8.093550481976661e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>8.977292411894232e-09</v>
+        <v>8.977292411894917e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>8.743228978306607e-09</v>
+        <v>8.743228978306564e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>8.743228978306606e-09</v>
+        <v>8.743228978306563e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>8.923655271241615e-09</v>
+        <v>8.923655271241516e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>8.977292411894232e-09</v>
+        <v>8.977292411894917e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>8.707092167158065e-09</v>
+        <v>8.707092167158115e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>8.977292411894232e-09</v>
+        <v>8.977292411894917e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>8.977292411894232e-09</v>
+        <v>8.977292411894917e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>8.977292411894232e-09</v>
+        <v>8.977292411894917e-09</v>
       </c>
     </row>
     <row r="4">
@@ -3763,37 +3763,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.341804155671857e-08</v>
+        <v>2.341804155671921e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>2.31012830735772e-08</v>
+        <v>2.310128307357697e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>2.345902220297546e-08</v>
+        <v>2.345902220297626e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>2.19912191261614e-08</v>
+        <v>2.199121912616133e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>2.318943770001751e-08</v>
+        <v>2.318943770001742e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>3.807651590675091e-08</v>
+        <v>2.336440441606588e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>3.965976638268825e-08</v>
+        <v>3.965976638268885e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>3.7859952802668e-08</v>
+        <v>2.314784131198238e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>3.850966127211743e-08</v>
+        <v>2.42878950600431e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>2.337559735011878e-08</v>
+        <v>2.337559735011979e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>2.349055948221897e-08</v>
+        <v>2.349055948221912e-08</v>
       </c>
     </row>
     <row r="5">
@@ -3803,37 +3803,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.688711736702597e-08</v>
+        <v>4.688711736702652e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>4.673124642832887e-08</v>
+        <v>4.673124642832881e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>4.688476276604538e-08</v>
+        <v>4.688476276604602e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>4.666550926152756e-08</v>
+        <v>4.666550926152745e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>4.666550926152756e-08</v>
+        <v>4.666550926152745e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>4.683348022637279e-08</v>
+        <v>4.683348022637345e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>4.688711736702597e-08</v>
+        <v>4.688711736702652e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>4.661691712228968e-08</v>
+        <v>4.66169171222896e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>4.688711736702597e-08</v>
+        <v>4.688711736702652e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>4.688711736702597e-08</v>
+        <v>4.688711736702652e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>4.688711736702597e-08</v>
+        <v>4.688711736702652e-08</v>
       </c>
     </row>
     <row r="6">
@@ -3843,37 +3843,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.477595739278919e-07</v>
+        <v>1.477595739278926e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>2.38169642521296e-07</v>
+        <v>2.381696425210173e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>2.57023793415217e-07</v>
+        <v>2.570237934152175e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>2.132969771822798e-07</v>
+        <v>2.132969771822796e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.503884355723886e-07</v>
+        <v>1.503884355723885e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>2.382046570770212e-07</v>
+        <v>2.382046570770218e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>2.38258294217716e-07</v>
+        <v>2.382582942177158e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>2.379880939729378e-07</v>
+        <v>2.379880939729377e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>2.38276079822535e-07</v>
+        <v>2.382760798225355e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.460785137351098e-07</v>
+        <v>1.460785137351097e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>3.327917749530343e-07</v>
+        <v>3.327917749530345e-07</v>
       </c>
     </row>
     <row r="7">
@@ -3883,34 +3883,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.113902188815742e-07</v>
+        <v>1.113902188815746e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>1.405661012288737e-07</v>
+        <v>1.405661012288733e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>1.407219790428296e-07</v>
+        <v>1.407219790428298e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>1.742999712056441e-07</v>
+        <v>1.742999712056436e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>1.404517492902817e-07</v>
+        <v>1.404517492902815e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>1.406683350269177e-07</v>
+        <v>1.406683350269178e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>1.407219721675708e-07</v>
+        <v>1.407219721675709e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>1.404517719228346e-07</v>
+        <v>1.404517719228341e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>1.407219721675708e-07</v>
+        <v>1.407219721675709e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>1.237270420106893e-07</v>
+        <v>1.237270420106892e-07</v>
       </c>
       <c r="L7" t="n">
         <v>1.407219721675709e-07</v>
@@ -3923,37 +3923,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.287112654032366e-08</v>
+        <v>2.287112654032407e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>1.66475866395891e-08</v>
+        <v>1.664758663958905e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.563199562472052e-08</v>
+        <v>2.563199562472072e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.006893610044935e-08</v>
+        <v>2.006893610044931e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>2.006893610044935e-08</v>
+        <v>2.006893610044931e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.973065588545567e-08</v>
+        <v>2.973065588545589e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>1.923544636616526e-08</v>
+        <v>1.92354463661655e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.006893610044935e-08</v>
+        <v>2.006893610044931e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.262957446913073e-08</v>
+        <v>2.262957446913045e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>3.06740555245357e-08</v>
+        <v>3.067405552453606e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>2.217318614766807e-08</v>
+        <v>2.217318614766833e-08</v>
       </c>
     </row>
     <row r="9">
@@ -3963,37 +3963,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.316677956213431e-08</v>
+        <v>2.316677956213494e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>1.707897708546276e-08</v>
+        <v>1.707897708546273e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>2.665503773239602e-08</v>
+        <v>2.66550377323966e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>2.086241549133844e-08</v>
+        <v>2.086241549133841e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.086241549133844e-08</v>
+        <v>2.086241549133841e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>3.057226657792522e-08</v>
+        <v>3.057226657792532e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.40577795539371e-08</v>
+        <v>2.40577795539378e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.086241549133844e-08</v>
+        <v>2.086241549133841e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.342343731337327e-08</v>
+        <v>2.342343731337353e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>3.099861568366497e-08</v>
+        <v>3.099861568366518e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.508241409201582e-08</v>
+        <v>2.508241409201608e-08</v>
       </c>
     </row>
   </sheetData>
@@ -4079,34 +4079,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.033331019700192e-08</v>
+        <v>6.033331019700189e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.291604636419104e-07</v>
+        <v>1.291604636419105e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.578151131609173e-07</v>
+        <v>1.578151131609172e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.482055430951907e-07</v>
+        <v>1.48205543095191e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.482055430951907e-07</v>
+        <v>1.48205543095191e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.419827576831403e-07</v>
+        <v>1.419827576831381e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.666587211162593e-07</v>
+        <v>1.66658721116259e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.482055430951907e-07</v>
+        <v>1.48205543095191e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>1.706503336172444e-07</v>
+        <v>1.706503336172445e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.274476829623193e-07</v>
+        <v>1.274476829623192e-07</v>
       </c>
       <c r="L2" t="n">
         <v>1.53892746983525e-07</v>
@@ -4119,37 +4119,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.037677108281328e-09</v>
+        <v>9.037677108281535e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>8.207045655983609e-09</v>
+        <v>8.207045655983595e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>9.037677108281328e-09</v>
+        <v>9.037677108281535e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>8.887319301276842e-09</v>
+        <v>8.887319301276882e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>8.887319301276844e-09</v>
+        <v>8.887319301276882e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>8.984865587071385e-09</v>
+        <v>8.984865587071464e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>9.037677108281328e-09</v>
+        <v>9.037677108281535e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>8.772742536853415e-09</v>
+        <v>8.77274253685359e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>9.037677108281328e-09</v>
+        <v>9.037677108281535e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>9.037677108281328e-09</v>
+        <v>9.037677108281535e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>9.037677108281328e-09</v>
+        <v>9.037677108281535e-09</v>
       </c>
     </row>
     <row r="4">
@@ -4159,37 +4159,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.258265765919125e-08</v>
+        <v>3.655298821689406e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>2.231665864230117e-08</v>
+        <v>2.231665864230038e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>2.261822041684664e-08</v>
+        <v>2.261807546420181e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>2.125229382559146e-08</v>
+        <v>2.125229382559151e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>2.236288611142954e-08</v>
+        <v>2.236288611142947e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>2.252984613798119e-08</v>
+        <v>2.252984613798109e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>3.813338342295985e-08</v>
+        <v>3.813338342295986e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>3.628805364546617e-08</v>
+        <v>3.628805364546607e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>3.693121661874563e-08</v>
+        <v>2.341168290311618e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>2.256935095675748e-08</v>
+        <v>2.256935095675659e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>2.25931476748148e-08</v>
+        <v>2.259314767481474e-08</v>
       </c>
     </row>
     <row r="5">
@@ -4199,13 +4199,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.53227100538159e-08</v>
+        <v>4.532271005381586e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>4.516806821674414e-08</v>
+        <v>4.51680682167441e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>4.532048039708097e-08</v>
+        <v>4.532048039708095e-08</v>
       </c>
       <c r="E5" t="n">
         <v>4.512429015255766e-08</v>
@@ -4214,22 +4214,22 @@
         <v>4.512429015255766e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>4.526989853260587e-08</v>
+        <v>4.526989853260581e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>4.53227100538159e-08</v>
+        <v>4.532271005381586e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>4.505777548238799e-08</v>
+        <v>4.505777548238798e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>4.53227100538159e-08</v>
+        <v>4.532271005381586e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>4.53227100538159e-08</v>
+        <v>4.532271005381586e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>4.53227100538159e-08</v>
+        <v>4.532271005381586e-08</v>
       </c>
     </row>
     <row r="6">
@@ -4242,31 +4242,31 @@
         <v>1.409389165611378e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>2.269913005625036e-07</v>
+        <v>2.269913005625035e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>2.449209138913149e-07</v>
+        <v>2.449209138913143e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>2.03317529377479e-07</v>
+        <v>2.033175293774787e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.434449792771512e-07</v>
+        <v>1.434449792771513e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>2.270097943475111e-07</v>
+        <v>2.27009794347512e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>2.270626058688428e-07</v>
+        <v>2.270626058688423e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>2.267976712972939e-07</v>
+        <v>2.267976712972938e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>2.270795316536867e-07</v>
+        <v>2.270795316536861e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.393391248150445e-07</v>
+        <v>1.393391248150447e-07</v>
       </c>
       <c r="L6" t="n">
         <v>3.170260009083445e-07</v>
@@ -4279,13 +4279,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.00395102379366e-07</v>
+        <v>1.003951023793659e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>1.265134949651132e-07</v>
+        <v>1.265134949651131e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>1.266681468758775e-07</v>
+        <v>1.266681468758773e-07</v>
       </c>
       <c r="E7" t="n">
         <v>1.567217145354631e-07</v>
@@ -4306,7 +4306,7 @@
         <v>1.266681368021849e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>1.114454417123927e-07</v>
+        <v>9.35856941329162e-08</v>
       </c>
       <c r="L7" t="n">
         <v>1.266681368021849e-07</v>
@@ -4319,37 +4319,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.654847493938213e-08</v>
+        <v>2.654847493938211e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>1.665370195708175e-08</v>
+        <v>1.665370195708176e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.606525858817164e-08</v>
+        <v>2.606525858817161e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.03372959980299e-08</v>
+        <v>2.033729599802989e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>2.03372959980299e-08</v>
+        <v>2.033729599802989e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>3.070625352187141e-08</v>
+        <v>3.070625352187139e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.621222898572614e-08</v>
+        <v>2.621222898572612e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.03372959980299e-08</v>
+        <v>2.033729599802989e-08</v>
       </c>
       <c r="J8" t="n">
         <v>2.249776575451139e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>3.102012155249082e-08</v>
+        <v>3.102012155249059e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>2.621250746000013e-08</v>
+        <v>2.621250746000012e-08</v>
       </c>
     </row>
     <row r="9">
@@ -4359,37 +4359,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.68638834843107e-08</v>
+        <v>2.686388348431067e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>1.721331068907125e-08</v>
+        <v>1.721331068907124e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>2.691737180767784e-08</v>
+        <v>2.691737180767785e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>2.113031151452518e-08</v>
+        <v>2.113031151452517e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.113031151452518e-08</v>
+        <v>2.113031151452517e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>3.123596669426085e-08</v>
+        <v>3.123596669426083e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.697889695087581e-08</v>
+        <v>2.697889695087578e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.113031151452518e-08</v>
+        <v>2.113031151452517e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.349483096576666e-08</v>
+        <v>2.34948309657666e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>3.136198925272503e-08</v>
+        <v>3.136198925272492e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.678879321238432e-08</v>
+        <v>2.678879321238431e-08</v>
       </c>
     </row>
   </sheetData>
@@ -4475,37 +4475,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.111903997314107e-08</v>
+        <v>6.111903997314087e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.3281209340598e-07</v>
+        <v>1.328120934059798e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.563187940029605e-07</v>
+        <v>1.563187940029602e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.442901161717174e-07</v>
+        <v>1.442901161717173e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.442901161717174e-07</v>
+        <v>1.442901161717173e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.427152915242505e-07</v>
+        <v>1.427152915242504e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.667322031765974e-07</v>
+        <v>1.667322031765972e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.442901161717174e-07</v>
+        <v>1.442901161717173e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>1.728738076666116e-07</v>
+        <v>1.728738076666114e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.274596436900415e-07</v>
+        <v>1.274596436900414e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.566222838712929e-07</v>
+        <v>1.566222838712928e-07</v>
       </c>
     </row>
     <row r="3">
@@ -4515,37 +4515,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.461285196390039e-09</v>
+        <v>9.461285196389932e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>8.619841160666423e-09</v>
+        <v>8.619841160666375e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>9.461285196390039e-09</v>
+        <v>9.461285196389932e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>9.310240514965779e-09</v>
+        <v>9.310240514965693e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>9.310240514965789e-09</v>
+        <v>9.310240514965695e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>9.407713017124708e-09</v>
+        <v>9.407713017124563e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>9.461285196390039e-09</v>
+        <v>9.461285196389932e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>9.191479615234814e-09</v>
+        <v>9.191479615234695e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>9.461285196390051e-09</v>
+        <v>9.461285196389932e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>9.461285196390039e-09</v>
+        <v>9.461285196389932e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>9.461285196390039e-09</v>
+        <v>9.461285196389932e-09</v>
       </c>
     </row>
     <row r="4">
@@ -4555,37 +4555,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.297638961903812e-08</v>
+        <v>3.7205332105931e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>2.271033342177411e-08</v>
+        <v>2.271033342177409e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>2.300095169421832e-08</v>
+        <v>2.300109589607655e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>2.16190323425463e-08</v>
+        <v>2.161903234254629e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>2.275052394132241e-08</v>
+        <v>2.275052394132246e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>3.715175992666559e-08</v>
+        <v>2.292281743977269e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>3.903877344542261e-08</v>
+        <v>3.903877344542247e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>3.693552652477584e-08</v>
+        <v>2.270658403788287e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>2.381336226462527e-08</v>
+        <v>3.763724380268092e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>2.29597121718231e-08</v>
+        <v>2.295971217182304e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>2.299142276543762e-08</v>
+        <v>2.299142276543776e-08</v>
       </c>
     </row>
     <row r="5">
@@ -4595,37 +4595,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.612863248835899e-08</v>
+        <v>4.612863248835889e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>4.597362658890315e-08</v>
+        <v>4.597362658890308e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>4.612639897726415e-08</v>
+        <v>4.612639897726406e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>4.593058664229198e-08</v>
+        <v>4.593058664229183e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>4.593058664229198e-08</v>
+        <v>4.593058664229183e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>4.607506030909353e-08</v>
+        <v>4.607506030909355e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>4.612863248835899e-08</v>
+        <v>4.612863248835889e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>4.58588269072037e-08</v>
+        <v>4.585882690720364e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>4.612863248835899e-08</v>
+        <v>4.612863248835889e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>4.612863248835899e-08</v>
+        <v>4.612863248835889e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>4.612863248835899e-08</v>
+        <v>4.612863248835889e-08</v>
       </c>
     </row>
     <row r="6">
@@ -4635,37 +4635,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.41994829011122e-07</v>
+        <v>1.419948290111217e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>2.285977087205141e-07</v>
+        <v>2.285977087201307e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>2.466357006830266e-07</v>
+        <v>2.46635700683026e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>2.047696213976735e-07</v>
+        <v>2.047696213976727e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.445164503228202e-07</v>
+        <v>1.4451645032282e-07</v>
       </c>
       <c r="G6" t="n">
         <v>2.286106626150997e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>2.286642347945656e-07</v>
+        <v>2.286642347945652e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>2.283944292132095e-07</v>
+        <v>2.283944292132094e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>2.286812678269325e-07</v>
+        <v>2.286812678269318e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.403849003013546e-07</v>
+        <v>1.403849003013544e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>3.191976763239832e-07</v>
+        <v>3.191976763239823e-07</v>
       </c>
     </row>
     <row r="7">
@@ -4675,37 +4675,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.674566433430578e-08</v>
+        <v>9.674566433430543e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.217999292053362e-07</v>
+        <v>1.217999292053359e-07</v>
       </c>
       <c r="D7" t="n">
         <v>1.219549453008707e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>1.507760812151515e-07</v>
+        <v>1.50776081215151e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>1.216851123462067e-07</v>
+        <v>1.216851123462065e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>1.219013629255264e-07</v>
+        <v>1.219013629255262e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>1.219549351047919e-07</v>
+        <v>1.219549351047917e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>1.216851295236369e-07</v>
+        <v>1.216851295236363e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>1.219549351047919e-07</v>
+        <v>1.219549351047917e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>1.067559905747611e-07</v>
+        <v>1.067559905747608e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>1.219549351047919e-07</v>
+        <v>1.219549351047917e-07</v>
       </c>
     </row>
     <row r="8">
@@ -4715,37 +4715,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.684815421686165e-08</v>
+        <v>3.684815421686175e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>1.681873717910693e-08</v>
+        <v>1.68187371791069e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.634205235837123e-08</v>
+        <v>2.634205235837124e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.062068181074977e-08</v>
+        <v>2.062068181074963e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>2.062068181074977e-08</v>
+        <v>2.062068181074963e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>3.177208053096557e-08</v>
+        <v>3.177208053096554e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.645033083915091e-08</v>
+        <v>2.64503308391509e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.062068181074977e-08</v>
+        <v>2.062068181074963e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.282830608994456e-08</v>
+        <v>2.282830608994457e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>3.111450015427325e-08</v>
+        <v>3.111450015427327e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>2.639010104952504e-08</v>
+        <v>2.639010104952506e-08</v>
       </c>
     </row>
     <row r="9">
@@ -4755,37 +4755,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.701112117825852e-08</v>
+        <v>3.701112117825848e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>1.742363964092621e-08</v>
+        <v>1.742363964092622e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>2.716649483939526e-08</v>
+        <v>2.716649483939522e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>2.13524585541948e-08</v>
+        <v>2.135245855419475e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.135245855419479e-08</v>
+        <v>2.135245855419475e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>3.229293896020993e-08</v>
+        <v>3.22929389602099e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.721225902431243e-08</v>
+        <v>2.721225902431233e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.13524585541948e-08</v>
+        <v>2.135245855419475e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.384781582623174e-08</v>
+        <v>2.384781582623172e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>3.145280109549704e-08</v>
+        <v>3.145280109549695e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.699499844888733e-08</v>
+        <v>2.699499844888739e-08</v>
       </c>
     </row>
   </sheetData>
@@ -4871,37 +4871,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.234229349537073e-07</v>
+        <v>4.23422934953711e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>2.134811764927823e-07</v>
+        <v>2.134811764927818e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>5.89276343068023e-07</v>
+        <v>5.892763430680225e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>2.134811764927823e-07</v>
+        <v>2.134811764927818e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>2.134811764927823e-07</v>
+        <v>2.134811764927818e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>4.435196110098139e-07</v>
+        <v>4.435196110098138e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.217273930828027e-06</v>
+        <v>1.217273930828024e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>2.134811764927823e-07</v>
+        <v>2.134811764927818e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>3.200750541785516e-07</v>
+        <v>3.200750541785509e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>2.838941568459404e-07</v>
+        <v>2.838941568459405e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>2.965736302165965e-07</v>
+        <v>2.965736302165963e-07</v>
       </c>
     </row>
     <row r="3">
@@ -4911,37 +4911,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.006222992302514e-08</v>
+        <v>1.006222992302515e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>9.353377117392571e-09</v>
+        <v>9.353377117392596e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>1.006222992302514e-08</v>
+        <v>1.006222992302515e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>9.497341697890422e-09</v>
+        <v>9.497341697890504e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>9.49734169789042e-09</v>
+        <v>9.497341697890504e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>1.000166908947243e-08</v>
+        <v>1.000166908947242e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.006222992302514e-08</v>
+        <v>1.006222992302515e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>9.747693865255138e-09</v>
+        <v>9.747693865255191e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>1.006222992302514e-08</v>
+        <v>1.006222992302515e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.006222992302514e-08</v>
+        <v>1.006222992302515e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.006222992302514e-08</v>
+        <v>1.006222992302515e-08</v>
       </c>
     </row>
     <row r="4">
@@ -4951,37 +4951,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.208948321227869e-08</v>
+        <v>2.56424932933791e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>2.49423279374647e-08</v>
+        <v>2.494232793746487e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>2.612958154645923e-08</v>
+        <v>2.61294041368956e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>2.377891105092296e-08</v>
+        <v>2.377891105092295e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>2.53173966095279e-08</v>
+        <v>2.531739660952793e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>4.202892237872593e-08</v>
+        <v>2.558193245982638e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>4.288751831035014e-08</v>
+        <v>4.288751831035016e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>4.177494715450864e-08</v>
+        <v>4.177494715450879e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>4.222380380160029e-08</v>
+        <v>2.659259097418005e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>2.550777789690239e-08</v>
+        <v>2.550777789690232e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>2.604747631641972e-08</v>
+        <v>2.604747631641973e-08</v>
       </c>
     </row>
     <row r="5">
@@ -4994,16 +4994,16 @@
         <v>4.898922576786779e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>4.867468971009783e-08</v>
+        <v>4.86746897100979e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>4.89866920116373e-08</v>
+        <v>4.898669201163733e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>4.86655049082768e-08</v>
+        <v>4.866550490827688e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>4.86655049082768e-08</v>
+        <v>4.866550490827688e-08</v>
       </c>
       <c r="G5" t="n">
         <v>4.892866493431511e-08</v>
@@ -5012,7 +5012,7 @@
         <v>4.898922576786779e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>4.867468971009783e-08</v>
+        <v>4.86746897100979e-08</v>
       </c>
       <c r="J5" t="n">
         <v>4.898922576786779e-08</v>
@@ -5031,37 +5031,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.518287846286136e-07</v>
+        <v>1.518287846286137e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>2.439234363061542e-07</v>
+        <v>2.439234363063791e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>2.633843964645997e-07</v>
+        <v>2.633843964645996e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>2.186517643805865e-07</v>
+        <v>2.186517643805867e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.544391097829538e-07</v>
+        <v>1.544391097829537e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>2.441648030200184e-07</v>
+        <v>2.441648030200186e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>2.442253638535724e-07</v>
+        <v>2.442253638535722e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>2.43910827795801e-07</v>
+        <v>2.439108277958011e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>2.442435224421889e-07</v>
+        <v>2.442435224421888e-07</v>
       </c>
       <c r="K6" t="n">
         <v>1.501124707318119e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>3.407413169428965e-07</v>
+        <v>3.407413169428967e-07</v>
       </c>
     </row>
     <row r="7">
@@ -5074,34 +5074,34 @@
         <v>1.203808919688882e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>1.515852170297743e-07</v>
+        <v>1.515852170297744e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>1.518997573907555e-07</v>
+        <v>1.518997573907557e-07</v>
       </c>
       <c r="E7" t="n">
         <v>1.879572764225724e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>1.515851834935032e-07</v>
+        <v>1.515851834935034e-07</v>
       </c>
       <c r="G7" t="n">
         <v>1.518391922539916e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>1.518997530875444e-07</v>
+        <v>1.518997530875445e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>1.515852170297743e-07</v>
+        <v>1.515852170297744e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>1.518997530875444e-07</v>
+        <v>1.518997530875445e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>1.336376029811915e-07</v>
+        <v>1.336376029811918e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>1.518997530875444e-07</v>
+        <v>1.518997530875445e-07</v>
       </c>
     </row>
     <row r="8">
@@ -5111,37 +5111,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.268894242352145e-08</v>
+        <v>2.268894242352144e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.065423255746462e-08</v>
+        <v>2.065423255746461e-08</v>
       </c>
       <c r="D8" t="n">
         <v>1.901969431467376e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.065423255746462e-08</v>
+        <v>2.065423255746461e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>2.065423255746462e-08</v>
+        <v>2.065423255746461e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.253436118665525e-08</v>
+        <v>2.25343611866552e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>7.668146522624764e-09</v>
+        <v>7.668146522624798e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>2.065423255746462e-08</v>
+        <v>2.065423255746461e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.558619503508232e-08</v>
+        <v>2.558619503508231e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>2.608893109993471e-08</v>
+        <v>2.608893109993472e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>2.636615787979193e-08</v>
+        <v>2.636615787979196e-08</v>
       </c>
     </row>
     <row r="9">
@@ -5151,37 +5151,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.706223378239063e-08</v>
+        <v>2.706223378239059e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.211076040049776e-08</v>
+        <v>2.211076040049775e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>2.556808225260651e-08</v>
+        <v>2.556808225260653e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>2.211076040049776e-08</v>
+        <v>2.211076040049775e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.211076040049776e-08</v>
+        <v>2.211076040049775e-08</v>
       </c>
       <c r="G9" t="n">
         <v>2.696170138998855e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.096578313950791e-08</v>
+        <v>2.096578313950792e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.211076040049776e-08</v>
+        <v>2.211076040049775e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.824420928029907e-08</v>
+        <v>2.824420928029909e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.844727083522512e-08</v>
+        <v>2.84472708352251e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.85631601366121e-08</v>
+        <v>1.854182937365874e-08</v>
       </c>
     </row>
   </sheetData>
@@ -5267,37 +5267,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.45601769604827e-07</v>
+        <v>3.456017696048272e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>2.377283877311913e-07</v>
+        <v>2.377283877311912e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>5.180537247560496e-07</v>
+        <v>5.180537247560517e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>2.377283877311913e-07</v>
+        <v>2.377283877311912e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>2.377283877311913e-07</v>
+        <v>2.377283877311912e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>4.046502396950956e-07</v>
+        <v>4.046502396951017e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.007982990251427e-06</v>
+        <v>1.007982990251425e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>2.377283877311913e-07</v>
+        <v>2.377283877311912e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>2.567243069469364e-07</v>
+        <v>2.56724306946937e-07</v>
       </c>
       <c r="K2" t="n">
         <v>2.635844236448981e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>3.118203593316165e-07</v>
+        <v>3.11820359331616e-07</v>
       </c>
     </row>
     <row r="3">
@@ -5307,28 +5307,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.010031958776196e-08</v>
+        <v>1.010031958776197e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>9.482350927300354e-09</v>
+        <v>9.482350927300359e-09</v>
       </c>
       <c r="D3" t="n">
         <v>1.010031958776197e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>9.613220854838644e-09</v>
+        <v>9.613220854838621e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>9.613220854838646e-09</v>
+        <v>9.613220854838629e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>1.004174299978071e-08</v>
+        <v>1.004174299978073e-08</v>
       </c>
       <c r="H3" t="n">
         <v>1.010031958776197e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>9.798471367483389e-09</v>
+        <v>9.7984713674834e-09</v>
       </c>
       <c r="J3" t="n">
         <v>1.010031958776197e-08</v>
@@ -5347,37 +5347,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.993794114929232e-08</v>
+        <v>2.456351427300911e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>2.399580223154468e-08</v>
+        <v>2.399580223154448e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>2.496357482429851e-08</v>
+        <v>2.49635748242992e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>2.290559066967146e-08</v>
+        <v>2.290559066967144e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>2.427714832756174e-08</v>
+        <v>2.427714832756182e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>3.987936456131107e-08</v>
+        <v>2.450493768502784e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>4.065013416896954e-08</v>
+        <v>4.065013416896957e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>3.963609292901383e-08</v>
+        <v>3.963609292901373e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>4.007454195010343e-08</v>
+        <v>2.544187802584856e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>2.444616244805347e-08</v>
+        <v>2.444616244805353e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>2.491526898142635e-08</v>
+        <v>2.491526898142632e-08</v>
       </c>
     </row>
     <row r="5">
@@ -5387,37 +5387,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.666352554911311e-08</v>
+        <v>4.666352554911325e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>4.636167732883454e-08</v>
+        <v>4.636167732883456e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>4.666115599700551e-08</v>
+        <v>4.666115599700557e-08</v>
       </c>
       <c r="E5" t="n">
         <v>4.635728855126732e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>4.635728855126732e-08</v>
+        <v>4.635728855126731e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>4.660494896113185e-08</v>
+        <v>4.660494896113191e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>4.666352554911313e-08</v>
+        <v>4.666352554911322e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>4.636167732883454e-08</v>
+        <v>4.636167732883456e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>4.666352554911313e-08</v>
+        <v>4.666352554911322e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>4.666352554911313e-08</v>
+        <v>4.666352554911322e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>4.666352554911313e-08</v>
+        <v>4.666352554911322e-08</v>
       </c>
     </row>
     <row r="6">
@@ -5427,37 +5427,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.42497974811016e-07</v>
+        <v>1.424979748110162e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>2.285827347778428e-07</v>
+        <v>2.285827347778432e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>2.467783346201622e-07</v>
+        <v>2.467783346201624e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>2.049587657470519e-07</v>
+        <v>2.049587657470521e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.449327433211268e-07</v>
+        <v>1.44932743321127e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>2.288102079755723e-07</v>
+        <v>2.288102079755725e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>2.288687845635552e-07</v>
+        <v>2.288687845635554e-07</v>
       </c>
       <c r="I6" t="n">
         <v>2.285669363432748e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>2.288857589147852e-07</v>
+        <v>2.288857589147855e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.408935926758919e-07</v>
+        <v>1.408935926758921e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>3.190903175713323e-07</v>
+        <v>3.190903175713328e-07</v>
       </c>
     </row>
     <row r="7">
@@ -5467,37 +5467,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.071177603570351e-07</v>
+        <v>1.071177603570352e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>1.346245311617741e-07</v>
+        <v>1.346245311617743e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>1.349263846251032e-07</v>
+        <v>1.349263846251034e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>1.667150560839704e-07</v>
+        <v>1.667150560839707e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>1.346245019343203e-07</v>
+        <v>1.346245019343206e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>1.348678027940715e-07</v>
+        <v>1.348678027940716e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>1.349263793820526e-07</v>
+        <v>1.34926379382053e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>1.346245311617741e-07</v>
+        <v>1.346245311617743e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>1.349263793820526e-07</v>
+        <v>1.34926379382053e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>9.991036284973201e-08</v>
+        <v>1.188139585112919e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>1.349263793820526e-07</v>
+        <v>1.34926379382053e-07</v>
       </c>
     </row>
     <row r="8">
@@ -5507,34 +5507,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.418689427310598e-08</v>
+        <v>2.418689427310599e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>1.993205436201284e-08</v>
+        <v>1.993205436201288e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>1.983235157702767e-08</v>
+        <v>1.983235157702756e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>1.993205436201284e-08</v>
+        <v>1.993205436201288e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>1.993205436201284e-08</v>
+        <v>1.993205436201288e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.285620174243456e-08</v>
+        <v>2.285620174243451e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>1.064135007491075e-08</v>
+        <v>1.06413500749108e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>1.993205436201284e-08</v>
+        <v>1.993205436201288e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.6726377884673e-08</v>
+        <v>2.672637788467304e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>2.61338061854436e-08</v>
+        <v>2.613380618544362e-08</v>
       </c>
       <c r="L8" t="n">
         <v>2.573669095934903e-08</v>
@@ -5547,37 +5547,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.776560888946646e-08</v>
+        <v>2.776560888946647e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.198869349536514e-08</v>
+        <v>2.198869349536518e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>2.599232391993443e-08</v>
+        <v>2.599232391993442e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>2.198869349536514e-08</v>
+        <v>2.198869349536518e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.198869349536514e-08</v>
+        <v>2.198869349536518e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.719122102214323e-08</v>
+        <v>2.719122102214322e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.2267400138528e-08</v>
+        <v>2.226740013852803e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.198869349536514e-08</v>
+        <v>2.198869349536518e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.880149352381825e-08</v>
+        <v>2.88014935238183e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.855882312109768e-08</v>
+        <v>2.855882312109774e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.840064066585888e-08</v>
+        <v>1.951031120707235e-08</v>
       </c>
     </row>
   </sheetData>
@@ -5663,37 +5663,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.06747216862514e-07</v>
+        <v>3.067472168625148e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>3.170870479399714e-07</v>
+        <v>3.170870479399729e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>4.588644812360013e-07</v>
+        <v>4.58864481236002e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>3.170870479399714e-07</v>
+        <v>3.170870479399729e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>3.170870479399714e-07</v>
+        <v>3.170870479399729e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>3.719392482129678e-07</v>
+        <v>3.719392482129716e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>8.351228759751896e-07</v>
+        <v>8.351228759751878e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>3.170870479399714e-07</v>
+        <v>3.170870479399729e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>2.570783313156013e-07</v>
+        <v>2.570783313156016e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>2.495593001563708e-07</v>
+        <v>2.495593001563706e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.237315721863134e-06</v>
+        <v>2.734156281480627e-07</v>
       </c>
     </row>
     <row r="3">
@@ -5703,37 +5703,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.048614390954907e-08</v>
+        <v>1.048614390954912e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.001203138536636e-08</v>
+        <v>1.001203138536644e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.048614390954907e-08</v>
+        <v>1.048614390954912e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.013686987167401e-08</v>
+        <v>1.013686987167397e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.013686987167396e-08</v>
+        <v>1.013686987167397e-08</v>
       </c>
       <c r="G3" t="n">
         <v>1.043208629549209e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.048614390954907e-08</v>
+        <v>1.048614390954912e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.021317715086926e-08</v>
+        <v>1.021317715086936e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.048614390954907e-08</v>
+        <v>1.048614390954912e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.048614390954907e-08</v>
+        <v>1.048614390954912e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.048614390954907e-08</v>
+        <v>1.048614390954912e-08</v>
       </c>
     </row>
     <row r="4">
@@ -5743,37 +5743,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.499673678565834e-08</v>
+        <v>2.499673678565846e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>2.467640523250181e-08</v>
+        <v>2.467640523250271e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>4.057605792118795e-08</v>
+        <v>2.531097606128908e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>2.357405212222762e-08</v>
+        <v>2.357405212222759e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>2.479589740876502e-08</v>
+        <v>2.479589740876501e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>2.494267917160141e-08</v>
+        <v>4.023980937244281e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>4.098367794987918e-08</v>
+        <v>4.098367794987967e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>4.002090022781989e-08</v>
+        <v>2.472377002697872e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>2.588837276243773e-08</v>
+        <v>4.042225173434277e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>2.487684012524054e-08</v>
+        <v>2.48768401252407e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>2.532053577537345e-08</v>
+        <v>2.532053577537344e-08</v>
       </c>
     </row>
     <row r="5">
@@ -5783,13 +5783,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.722460243562762e-08</v>
+        <v>4.722460243562772e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>4.695163567694772e-08</v>
+        <v>4.695163567694785e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>4.72222198111309e-08</v>
+        <v>4.722221981113098e-08</v>
       </c>
       <c r="E5" t="n">
         <v>4.695706305545498e-08</v>
@@ -5798,22 +5798,22 @@
         <v>4.695706305545498e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>4.717054482157059e-08</v>
+        <v>4.717054482157066e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>4.722460243562758e-08</v>
+        <v>4.722460243562765e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>4.695163567694772e-08</v>
+        <v>4.695163567694785e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>4.722460243562758e-08</v>
+        <v>4.722460243562765e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>4.722460243562758e-08</v>
+        <v>4.722460243562765e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>4.722460243562758e-08</v>
+        <v>4.722460243562765e-08</v>
       </c>
     </row>
     <row r="6">
@@ -5823,37 +5823,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.429873586583606e-07</v>
+        <v>1.429873586583607e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>2.292198429524624e-07</v>
+        <v>2.292198429524629e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>2.473998249239595e-07</v>
+        <v>2.473998249239603e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>2.055649452005493e-07</v>
+        <v>2.055649452005497e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.454603406215714e-07</v>
+        <v>1.454603406215717e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>2.294135287317142e-07</v>
+        <v>2.294135287317145e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>2.294675863457751e-07</v>
+        <v>2.294675863457759e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>2.291946195870914e-07</v>
+        <v>2.291946195870917e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>2.294845822006901e-07</v>
+        <v>2.294845822006904e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.413809440289253e-07</v>
+        <v>1.413809440289256e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>3.198034155358419e-07</v>
+        <v>3.198034155358425e-07</v>
       </c>
     </row>
     <row r="7">
@@ -5866,34 +5866,34 @@
         <v>1.027989715912187e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>1.290525234764251e-07</v>
+        <v>1.290525234764255e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>1.293254958587429e-07</v>
+        <v>1.293254958587431e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>1.596635351479052e-07</v>
+        <v>1.596635351479055e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>1.290524966970888e-07</v>
+        <v>1.290524966970894e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>1.292714326210482e-07</v>
+        <v>1.292714326210479e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>1.29325490235105e-07</v>
+        <v>1.293254902351051e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>1.290525234764251e-07</v>
+        <v>1.290525234764255e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>1.29325490235105e-07</v>
+        <v>1.293254902351051e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>1.139559235204419e-07</v>
+        <v>1.139559235204418e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>1.29325490235105e-07</v>
+        <v>1.293254902351051e-07</v>
       </c>
     </row>
     <row r="8">
@@ -5903,37 +5903,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.517954666095077e-08</v>
+        <v>2.517954666095081e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>1.820283585250849e-08</v>
+        <v>1.820283585250844e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.122413629126477e-08</v>
+        <v>2.122413629126479e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>1.820283585250849e-08</v>
+        <v>1.820283585250844e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>1.820283585250849e-08</v>
+        <v>1.820283585250844e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.369424205580726e-08</v>
+        <v>2.36942420558074e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>1.392137234666947e-08</v>
+        <v>1.39213723466695e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>1.820283585250849e-08</v>
+        <v>1.820283585250844e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.684632627417928e-08</v>
+        <v>2.684632627417932e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>2.650400361204833e-08</v>
+        <v>2.650400361204832e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>6.457609960761267e-09</v>
+        <v>6.457609960761096e-09</v>
       </c>
     </row>
     <row r="9">
@@ -5943,37 +5943,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.823968238971357e-08</v>
+        <v>2.823968238971356e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.152458857106478e-08</v>
+        <v>2.152458857106485e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>2.662892773504507e-08</v>
+        <v>2.662892773504509e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>2.152458857106478e-08</v>
+        <v>2.152458857106485e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.152458857106478e-08</v>
+        <v>2.152458857106485e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.761464540439515e-08</v>
+        <v>2.761464540439524e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.367016295746038e-08</v>
+        <v>2.367016295746041e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.152458857106478e-08</v>
+        <v>2.152458857106485e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.892012029571952e-08</v>
+        <v>2.892012029571954e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.877936143931115e-08</v>
+        <v>2.877936143931114e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.063291368637647e-08</v>
+        <v>2.063291368637646e-08</v>
       </c>
     </row>
   </sheetData>
@@ -6059,37 +6059,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.622309433000337e-07</v>
+        <v>1.62230943300037e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>1.536353610965953e-07</v>
+        <v>1.536353610965956e-07</v>
       </c>
       <c r="D2" t="n">
         <v>2.514686582432598e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.536353610965953e-07</v>
+        <v>1.536353610965956e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.536353610965953e-07</v>
+        <v>1.536353610965956e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>2.159674091740489e-07</v>
+        <v>2.159674091740477e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>4.497776642160709e-07</v>
+        <v>4.497776642160711e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.536353610965953e-07</v>
+        <v>1.536353610965956e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>2.486190790463584e-07</v>
+        <v>2.486190790463592e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.827648360721783e-07</v>
+        <v>1.827648360721792e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>4.517454878828083e-07</v>
+        <v>4.517454878828088e-07</v>
       </c>
     </row>
     <row r="3">
@@ -6099,37 +6099,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.323466214755464e-09</v>
+        <v>9.323466214755608e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>8.7884766755839e-09</v>
+        <v>8.788476675583829e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>9.323466214755464e-09</v>
+        <v>9.323466214755608e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>8.917732938237377e-09</v>
+        <v>8.917732938237266e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>8.917732938237373e-09</v>
+        <v>8.917732938237291e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>9.269001194073417e-09</v>
+        <v>9.269001194073432e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>9.323466214755464e-09</v>
+        <v>9.323466214755608e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>9.047780680622094e-09</v>
+        <v>9.047780680622214e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>9.323466214755464e-09</v>
+        <v>9.323466214755608e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>9.323466214755464e-09</v>
+        <v>9.323466214755608e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>9.323466214755464e-09</v>
+        <v>9.323466214755608e-09</v>
       </c>
     </row>
     <row r="4">
@@ -6139,37 +6139,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.436120721189232e-08</v>
+        <v>3.924548920171611e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>2.394313086241262e-08</v>
+        <v>2.394313086241289e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>3.951818021103787e-08</v>
+        <v>3.951818021103788e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>2.280141012952248e-08</v>
+        <v>2.280141012952255e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>2.410114409701226e-08</v>
+        <v>2.410114409701222e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>2.430674219121024e-08</v>
+        <v>3.919102418103405e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>3.990280502428282e-08</v>
+        <v>2.446830635570314e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>2.408552167775899e-08</v>
+        <v>3.896980366758265e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>3.936821151556464e-08</v>
+        <v>3.936821151556471e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>2.436028705801507e-08</v>
+        <v>2.436028705801508e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>2.445902709854763e-08</v>
+        <v>2.445902709854768e-08</v>
       </c>
     </row>
     <row r="5">
@@ -6179,37 +6179,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.716406049616561e-08</v>
+        <v>4.716406049616563e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>4.688837496203233e-08</v>
+        <v>4.688837496203223e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>4.716153262893037e-08</v>
+        <v>4.716153262893039e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>4.688660348781487e-08</v>
+        <v>4.688660348781485e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>4.688660348781487e-08</v>
+        <v>4.688660348781485e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>4.710959547548361e-08</v>
+        <v>4.71095954754836e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>4.716406049616561e-08</v>
+        <v>4.716406049616563e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>4.688837496203233e-08</v>
+        <v>4.688837496203223e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>4.716406049616561e-08</v>
+        <v>4.716406049616563e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>4.716406049616561e-08</v>
+        <v>4.716406049616563e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>4.716406049616561e-08</v>
+        <v>4.716406049616563e-08</v>
       </c>
     </row>
     <row r="6">
@@ -6219,37 +6219,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.490579415195518e-07</v>
+        <v>1.490579415195519e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>2.396942334202538e-07</v>
+        <v>2.396942334202543e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>2.58797690701757e-07</v>
+        <v>2.587976907017574e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>2.148331702972681e-07</v>
+        <v>2.148331702972683e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.516638616568858e-07</v>
+        <v>1.516638616568856e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>2.398960570025333e-07</v>
+        <v>2.398960570025334e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>2.399505220232159e-07</v>
+        <v>2.39950522023216e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>2.39674836489082e-07</v>
+        <v>2.396748364890823e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>2.399683850332962e-07</v>
+        <v>2.399683850332959e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.473695651711227e-07</v>
+        <v>1.473695651711225e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>3.348954226861066e-07</v>
+        <v>3.34895422686107e-07</v>
       </c>
     </row>
     <row r="7">
@@ -6259,37 +6259,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.138017051867589e-07</v>
+        <v>1.138017051867591e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>1.433370398923316e-07</v>
+        <v>1.433370398923319e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>1.436127330383926e-07</v>
+        <v>1.436127330383928e-07</v>
       </c>
       <c r="E7" t="n">
         <v>1.777383027674695e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>1.433370164789112e-07</v>
+        <v>1.433370164789113e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>1.435582604057832e-07</v>
+        <v>1.435582604057833e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>1.436127254264653e-07</v>
+        <v>1.436127254264655e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>1.433370398923316e-07</v>
+        <v>1.433370398923319e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>1.436127254264653e-07</v>
+        <v>1.436127254264655e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>1.263401064242174e-07</v>
+        <v>1.263401064242175e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>1.436127254264653e-07</v>
+        <v>1.436127254264655e-07</v>
       </c>
     </row>
     <row r="8">
@@ -6302,34 +6302,34 @@
         <v>2.793271916698292e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.128326367153279e-08</v>
+        <v>2.128326367153278e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.581372232632234e-08</v>
+        <v>2.581372232632235e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.128326367153279e-08</v>
+        <v>2.128326367153278e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>2.128326367153279e-08</v>
+        <v>2.128326367153278e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.672106451209043e-08</v>
+        <v>2.672106451209047e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.186115018664579e-08</v>
+        <v>2.186115018664582e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.128326367153279e-08</v>
+        <v>2.128326367153278e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.615242397762131e-08</v>
+        <v>2.615242397762133e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>2.744498047267637e-08</v>
+        <v>2.744498047267633e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>2.788701709263709e-08</v>
+        <v>2.240083565929803e-08</v>
       </c>
     </row>
     <row r="9">
@@ -6339,37 +6339,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.863453308779762e-08</v>
+        <v>2.863453308779764e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.189405553825356e-08</v>
+        <v>2.18940555382536e-08</v>
       </c>
       <c r="D9" t="n">
         <v>2.777158309275593e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>2.189405553825357e-08</v>
+        <v>2.18940555382536e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.189405553825357e-08</v>
+        <v>2.18940555382536e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.811859671054045e-08</v>
+        <v>2.811859671054048e-08</v>
       </c>
       <c r="H9" t="n">
         <v>2.616893141137078e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.189405553825357e-08</v>
+        <v>2.18940555382536e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.791078803376503e-08</v>
+        <v>2.7910788033765e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.843600056457214e-08</v>
+        <v>2.843600056457212e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.638696711453949e-08</v>
+        <v>2.638696711453947e-08</v>
       </c>
     </row>
   </sheetData>
@@ -6455,37 +6455,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.451768665279843e-07</v>
+        <v>1.451768665279844e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>1.632680223391607e-07</v>
+        <v>1.632680223391608e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.69531386763264e-07</v>
+        <v>1.695313867632641e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.632680223391607e-07</v>
+        <v>1.632680223391608e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.632680223391607e-07</v>
+        <v>1.632680223391608e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.69630522079946e-07</v>
+        <v>1.696305220799491e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.723853286358809e-07</v>
+        <v>1.723853286358808e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.632680223391607e-07</v>
+        <v>1.632680223391608e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>2.061874046739622e-07</v>
+        <v>2.061874046739627e-07</v>
       </c>
       <c r="K2" t="n">
         <v>1.688227760595999e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.553872987118481e-07</v>
+        <v>1.553872987118484e-07</v>
       </c>
     </row>
     <row r="3">
@@ -6495,37 +6495,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.225216720982309e-09</v>
+        <v>9.225216720982303e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>8.773509890047499e-09</v>
+        <v>8.773509890047522e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>9.225216720982309e-09</v>
+        <v>9.225216720982303e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>8.887109126597234e-09</v>
+        <v>8.887109126597247e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>8.887109126597273e-09</v>
+        <v>8.887109126597278e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>9.173037567394722e-09</v>
+        <v>9.173037567394755e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>9.225216720982309e-09</v>
+        <v>9.225216720982303e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>8.964141970570577e-09</v>
+        <v>8.964141970570617e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>9.225216720982309e-09</v>
+        <v>9.225216720982303e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>9.225216720982309e-09</v>
+        <v>9.225216720982303e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>9.225216720982309e-09</v>
+        <v>9.225216720982303e-09</v>
       </c>
     </row>
     <row r="4">
@@ -6535,37 +6535,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.682892452236305e-08</v>
+        <v>3.682892452236311e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>2.280615241584698e-08</v>
+        <v>2.280615241584701e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>2.312872112676434e-08</v>
+        <v>2.312855967920788e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>2.173947619704517e-08</v>
+        <v>2.173947619704521e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>2.287835388178924e-08</v>
+        <v>2.287835388178926e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>2.306723047414363e-08</v>
+        <v>3.677674536877546e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>2.312174523461985e-08</v>
+        <v>3.73465316727773e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>2.285833487731947e-08</v>
+        <v>3.656784977195141e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>3.692843670132254e-08</v>
+        <v>2.394252215001484e-08</v>
       </c>
       <c r="K4" t="n">
         <v>2.314503623688299e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>2.311639964309361e-08</v>
+        <v>2.311639964309359e-08</v>
       </c>
     </row>
     <row r="5">
@@ -6575,37 +6575,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.466218459315044e-08</v>
+        <v>4.46621845931504e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>4.440110984273872e-08</v>
+        <v>4.440110984273873e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>4.465982485520355e-08</v>
+        <v>4.465982485520352e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>4.440122865233689e-08</v>
+        <v>4.440122865233695e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>4.440122865233689e-08</v>
+        <v>4.440122865233695e-08</v>
       </c>
       <c r="G5" t="n">
         <v>4.461000543956286e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>4.466218459315044e-08</v>
+        <v>4.46621845931504e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>4.440110984273872e-08</v>
+        <v>4.440110984273873e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>4.466218459315044e-08</v>
+        <v>4.46621845931504e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>4.466218459315044e-08</v>
+        <v>4.46621845931504e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>4.466218459315044e-08</v>
+        <v>4.46621845931504e-08</v>
       </c>
     </row>
     <row r="6">
@@ -6615,34 +6615,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.394663485900729e-07</v>
+        <v>1.394663485900728e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>2.23998072280669e-07</v>
+        <v>2.239980722806688e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>2.418175992341246e-07</v>
+        <v>2.418175992341245e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>2.00810663466836e-07</v>
+        <v>2.008106634668359e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.418939260500836e-07</v>
+        <v>1.418939260500837e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>2.241871833912479e-07</v>
+        <v>2.24187183391248e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>2.242393625448347e-07</v>
+        <v>2.24239362544835e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>2.239782877944237e-07</v>
+        <v>2.239782877944236e-07</v>
       </c>
       <c r="J6" t="n">
         <v>2.24256022883831e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.378916463321634e-07</v>
+        <v>1.378916463321633e-07</v>
       </c>
       <c r="L6" t="n">
         <v>3.127918642367058e-07</v>
@@ -6658,34 +6658,34 @@
         <v>1.006039159879083e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>1.264929844524364e-07</v>
+        <v>1.264929844524365e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>1.267540688441089e-07</v>
+        <v>1.26754068844109e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>1.566696817155673e-07</v>
+        <v>1.566696817155677e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2649296665259e-07</v>
+        <v>1.264929666525901e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>1.267018800492605e-07</v>
+        <v>1.267018800492606e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>1.267540592028478e-07</v>
+        <v>1.267540592028481e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>1.264929844524364e-07</v>
+        <v>1.264929844524365e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>1.267540592028478e-07</v>
+        <v>1.267540592028481e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>1.109878520341415e-07</v>
+        <v>1.116025675796533e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>1.267540592028478e-07</v>
+        <v>1.267540592028481e-07</v>
       </c>
     </row>
     <row r="8">
@@ -6695,7 +6695,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.80946011379082e-08</v>
+        <v>2.809460113790822e-08</v>
       </c>
       <c r="C8" t="n">
         <v>2.091779426882776e-08</v>
@@ -6713,7 +6713,7 @@
         <v>2.759458176301112e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.803266448881332e-08</v>
+        <v>2.803266448881333e-08</v>
       </c>
       <c r="I8" t="n">
         <v>2.091779426882776e-08</v>
@@ -6725,7 +6725,7 @@
         <v>2.750618412753005e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>2.834786453689764e-08</v>
+        <v>2.821425105990332e-08</v>
       </c>
     </row>
     <row r="9">
@@ -6735,13 +6735,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.871118648768983e-08</v>
+        <v>2.871118648768985e-08</v>
       </c>
       <c r="C9" t="n">
         <v>2.181909405288182e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>2.853687546555392e-08</v>
+        <v>2.853687546555394e-08</v>
       </c>
       <c r="E9" t="n">
         <v>2.181909405288182e-08</v>
@@ -6750,22 +6750,22 @@
         <v>2.181909405288182e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.849084636407147e-08</v>
+        <v>2.849084636407148e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.868754168120159e-08</v>
+        <v>2.868754168120157e-08</v>
       </c>
       <c r="I9" t="n">
         <v>2.181909405288182e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.818008745412842e-08</v>
+        <v>2.818008745412844e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.847164608471443e-08</v>
+        <v>2.847164608471442e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.881538349388308e-08</v>
+        <v>2.876105167495004e-08</v>
       </c>
     </row>
   </sheetData>
@@ -6851,37 +6851,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.661080341049477e-07</v>
+        <v>1.661080341049475e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>1.721513655523564e-07</v>
+        <v>1.721513655523539e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.799343874583647e-07</v>
+        <v>1.799343874583643e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.721513655523564e-07</v>
+        <v>1.721513655523539e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.721513655523564e-07</v>
+        <v>1.721513655523539e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.704175192728285e-07</v>
+        <v>1.704175192728261e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.708281996530264e-07</v>
+        <v>1.708281996530257e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.721513655523564e-07</v>
+        <v>1.721513655523539e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>2.450915095471902e-07</v>
+        <v>2.450915095471895e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.632110427063904e-07</v>
+        <v>1.632110427063899e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.677976190359099e-07</v>
+        <v>1.688262467705722e-07</v>
       </c>
     </row>
     <row r="3">
@@ -6891,37 +6891,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.370549655624939e-09</v>
+        <v>9.370549655624819e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>8.927365236068781e-09</v>
+        <v>8.927365236068731e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>9.370549655624957e-09</v>
+        <v>9.370549655624819e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>9.04086351072702e-09</v>
+        <v>9.04086351072701e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>9.040863510726992e-09</v>
+        <v>9.04086351072701e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>9.318756114706005e-09</v>
+        <v>9.318756114705864e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>9.370549655624939e-09</v>
+        <v>9.370549655624819e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>9.111961199233635e-09</v>
+        <v>9.111961199233526e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>9.370549655624939e-09</v>
+        <v>9.370549655624819e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>9.370549655624939e-09</v>
+        <v>9.370549655624819e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>9.370549655624939e-09</v>
+        <v>9.370549655624819e-09</v>
       </c>
     </row>
     <row r="4">
@@ -6931,37 +6931,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.32489260607938e-08</v>
+        <v>2.324892606079373e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>2.294730376010172e-08</v>
+        <v>2.294730376010109e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>2.327255510491895e-08</v>
+        <v>2.327255510491888e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>2.187612291120385e-08</v>
+        <v>2.187612291120382e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>2.300792372562063e-08</v>
+        <v>2.300792372562053e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>3.703019928671031e-08</v>
+        <v>2.319713251987482e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>3.755467668863535e-08</v>
+        <v>3.755467668863534e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>2.299033760440254e-08</v>
+        <v>2.299033760440246e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>3.713597215975962e-08</v>
+        <v>2.408156828630144e-08</v>
       </c>
       <c r="K4" t="n">
         <v>2.324735807793402e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>2.324325985813568e-08</v>
+        <v>2.324325985813565e-08</v>
       </c>
     </row>
     <row r="5">
@@ -6971,37 +6971,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.504199039687543e-08</v>
+        <v>4.504199039687533e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>4.478340194048412e-08</v>
+        <v>4.4783401940484e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>4.503962988582165e-08</v>
+        <v>4.50396298858215e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>4.478336093143807e-08</v>
+        <v>4.478336093143799e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>4.478336093143807e-08</v>
+        <v>4.478336093143799e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>4.499019685595644e-08</v>
+        <v>4.499019685595636e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>4.504199039687543e-08</v>
+        <v>4.504199039687533e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>4.478340194048412e-08</v>
+        <v>4.4783401940484e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>4.504199039687543e-08</v>
+        <v>4.504199039687533e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>4.504199039687543e-08</v>
+        <v>4.504199039687533e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>4.504199039687543e-08</v>
+        <v>4.504199039687533e-08</v>
       </c>
     </row>
     <row r="6">
@@ -7011,34 +7011,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.398895138556116e-07</v>
+        <v>1.398895138556114e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>2.246627513475061e-07</v>
+        <v>2.246627513475058e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>2.425294830390753e-07</v>
+        <v>2.425294830390749e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>2.014099532755781e-07</v>
+        <v>2.01409953275578e-07</v>
       </c>
       <c r="F6" t="n">
         <v>1.423270628716635e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>2.248498670657516e-07</v>
+        <v>2.248498670657514e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>2.24901660606671e-07</v>
+        <v>2.249016606066712e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>2.246430721502793e-07</v>
+        <v>2.24643072150279e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>2.249183679420945e-07</v>
+        <v>2.249183679420942e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.383103695832392e-07</v>
+        <v>1.383103695832389e-07</v>
       </c>
       <c r="L6" t="n">
         <v>3.137039565002187e-07</v>
@@ -7051,37 +7051,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.674012751397901e-08</v>
+        <v>9.674012751397879e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.215501869516087e-07</v>
+        <v>1.215501869516084e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>1.218087849501097e-07</v>
+        <v>1.218087849501095e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>1.504788614722843e-07</v>
+        <v>1.504788614722841e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>1.215501691646502e-07</v>
+        <v>1.215501691646499e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>1.217569818670809e-07</v>
+        <v>1.217569818670807e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>1.218087754080001e-07</v>
+        <v>1.218087754079997e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>1.215501869516087e-07</v>
+        <v>1.215501869516084e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>1.218087754080001e-07</v>
+        <v>1.218087754079997e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>1.066946137081196e-07</v>
+        <v>1.066946137081193e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>1.218087754080001e-07</v>
+        <v>1.218087754079997e-07</v>
       </c>
     </row>
     <row r="8">
@@ -7091,37 +7091,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.769091839605854e-08</v>
+        <v>2.769091839605848e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.081836521563724e-08</v>
+        <v>2.081836521563718e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.743029377927287e-08</v>
+        <v>2.743029377927281e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.081836521563724e-08</v>
+        <v>2.081836521563718e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>2.081836521563724e-08</v>
+        <v>2.081836521563718e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.76725923239618e-08</v>
+        <v>2.767259232396176e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.805987506279545e-08</v>
+        <v>2.805987506279543e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.081836521563724e-08</v>
+        <v>2.081836521563718e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.595810651561827e-08</v>
+        <v>2.595810651561821e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>2.77827465754468e-08</v>
+        <v>2.778274657544672e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>2.798270494998217e-08</v>
+        <v>2.811943493714169e-08</v>
       </c>
     </row>
     <row r="9">
@@ -7131,37 +7131,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.861940813272313e-08</v>
+        <v>2.861940813272306e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.188086677600319e-08</v>
+        <v>2.188086677600312e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>2.851332225613849e-08</v>
+        <v>2.851332225613846e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>2.188086677600319e-08</v>
+        <v>2.188086677600312e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.188086677600319e-08</v>
+        <v>2.188086677600312e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.859624074851871e-08</v>
+        <v>2.859624074851867e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.877135451184887e-08</v>
+        <v>2.87713545118488e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.188086677600319e-08</v>
+        <v>2.188086677600312e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.791513176355129e-08</v>
+        <v>2.791513176355127e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.865691925618899e-08</v>
+        <v>2.865691925618898e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.879525237965148e-08</v>
+        <v>2.879525237965146e-08</v>
       </c>
     </row>
   </sheetData>
@@ -7247,37 +7247,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.925793104167715e-07</v>
+        <v>2.925793104167714e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>1.913822852518366e-07</v>
+        <v>1.913822852518365e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>5.526981784457451e-07</v>
+        <v>5.526981784457444e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.913822852518366e-07</v>
+        <v>1.913822852518365e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.913822852518366e-07</v>
+        <v>1.913822852518365e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>3.874859559975184e-07</v>
+        <v>3.874859559975121e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.102833075315942e-06</v>
+        <v>1.102833075315938e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>1.913822852518366e-07</v>
+        <v>1.913822852518365e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>2.844679119625281e-07</v>
+        <v>2.844679119625272e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>2.489602553960686e-07</v>
+        <v>2.48960255396068e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.367731742166388e-06</v>
+        <v>2.180124508544153e-07</v>
       </c>
     </row>
     <row r="3">
@@ -7287,37 +7287,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.84392227764221e-09</v>
+        <v>9.843922277642169e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>9.166946966084055e-09</v>
+        <v>9.166946966084005e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>9.84392227764221e-09</v>
+        <v>9.843922277642167e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>9.307668937558404e-09</v>
+        <v>9.307668937558371e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>9.307668937558402e-09</v>
+        <v>9.307668937558261e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>9.784341913559619e-09</v>
+        <v>9.78434191355954e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>9.84392227764221e-09</v>
+        <v>9.843922277642169e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>9.535612156949055e-09</v>
+        <v>9.535612156948994e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>9.84392227764221e-09</v>
+        <v>9.843922277642167e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>9.84392227764221e-09</v>
+        <v>9.843922277642167e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>9.84392227764221e-09</v>
+        <v>9.843922277642167e-09</v>
       </c>
     </row>
     <row r="4">
@@ -7327,37 +7327,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.528489768948398e-08</v>
+        <v>2.528489768948395e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>2.463159399406947e-08</v>
+        <v>2.463159399406866e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>2.581035567898798e-08</v>
+        <v>2.581035567898797e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>2.347533704082986e-08</v>
+        <v>2.347533704083006e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>2.496917154593754e-08</v>
+        <v>2.496917154593751e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>4.129394631337664e-08</v>
+        <v>4.129394631337658e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>4.219511099407028e-08</v>
+        <v>4.219511099407022e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>4.104521655676597e-08</v>
+        <v>4.104521655676591e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>4.152358268786046e-08</v>
+        <v>4.152358268786039e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>2.516500727929409e-08</v>
+        <v>2.516500727929416e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>2.563854479494776e-08</v>
+        <v>2.563854479494772e-08</v>
       </c>
     </row>
     <row r="5">
@@ -7367,37 +7367,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.844218985095685e-08</v>
+        <v>4.844218985095678e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>4.813387973026369e-08</v>
+        <v>4.813387973026363e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>4.843965863551429e-08</v>
+        <v>4.843965863551424e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>4.812693906233279e-08</v>
+        <v>4.812693906233254e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>4.812693906233279e-08</v>
+        <v>4.812693906233254e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>4.838260948687429e-08</v>
+        <v>4.838260948687414e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>4.844218985095685e-08</v>
+        <v>4.844218985095678e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>4.813387973026369e-08</v>
+        <v>4.813387973026363e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>4.844218985095685e-08</v>
+        <v>4.844218985095678e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>4.844218985095685e-08</v>
+        <v>4.844218985095678e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>4.844218985095685e-08</v>
+        <v>4.844218985095678e-08</v>
       </c>
     </row>
     <row r="6">
@@ -7407,37 +7407,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.510138482117445e-07</v>
+        <v>1.51013848211744e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>2.426758072432831e-07</v>
+        <v>2.426758072430583e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>2.62037045482387e-07</v>
+        <v>2.620370454823864e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>2.17524519758876e-07</v>
+        <v>2.175245197588756e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.536177582818084e-07</v>
+        <v>1.53617758281808e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>2.429098716366159e-07</v>
+        <v>2.429098716366156e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>2.429694520007012e-07</v>
+        <v>2.42969452000701e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>2.426611418800053e-07</v>
+        <v>2.426611418800044e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>2.429875239250627e-07</v>
+        <v>2.429875239250626e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.493057256600585e-07</v>
+        <v>1.49305725660058e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>3.390247693734042e-07</v>
+        <v>3.390247693734035e-07</v>
       </c>
     </row>
     <row r="7">
@@ -7447,34 +7447,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.187695344895035e-07</v>
+        <v>1.187695344895031e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>1.495678961202441e-07</v>
+        <v>1.495678961202439e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>1.498762094961387e-07</v>
+        <v>1.498762094961384e-07</v>
       </c>
       <c r="E7" t="n">
         <v>1.854642972956568e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>1.495678629999263e-07</v>
+        <v>1.495678629999259e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>1.498166258768547e-07</v>
+        <v>1.498166258768541e-07</v>
       </c>
       <c r="H7" t="n">
         <v>1.498762062409372e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>1.495678961202441e-07</v>
+        <v>1.495678961202439e-07</v>
       </c>
       <c r="J7" t="n">
         <v>1.498762062409372e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>1.318528798319567e-07</v>
+        <v>1.318528798319564e-07</v>
       </c>
       <c r="L7" t="n">
         <v>1.498762062409372e-07</v>
@@ -7487,37 +7487,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.549601646926125e-08</v>
+        <v>2.549601646926123e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.091468731113124e-08</v>
+        <v>2.091468731113117e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>1.920854230753763e-08</v>
+        <v>1.920854230753752e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.091468731113124e-08</v>
+        <v>2.091468731113117e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>2.091468731113124e-08</v>
+        <v>2.091468731113117e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.339016505615581e-08</v>
+        <v>2.33901650561558e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>8.081547347135774e-09</v>
+        <v>8.081547347135788e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>2.091468731113124e-08</v>
+        <v>2.091468731113117e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.60645360497195e-08</v>
+        <v>2.606453604971945e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>2.656519705255645e-08</v>
+        <v>2.65651970525564e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>5.247082348969822e-09</v>
+        <v>5.247082348969759e-09</v>
       </c>
     </row>
     <row r="9">
@@ -7527,37 +7527,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.803747709635171e-08</v>
+        <v>2.803747709635165e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.205541503063407e-08</v>
+        <v>2.205541503063398e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>2.547692605168629e-08</v>
+        <v>2.547692605168619e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>2.205541503063407e-08</v>
+        <v>2.205541503063398e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.205541503063407e-08</v>
+        <v>2.205541503063398e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.714462522264233e-08</v>
+        <v>2.714462522264232e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.096544464635762e-08</v>
+        <v>2.096544464635757e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.205541503063407e-08</v>
+        <v>2.205541503063398e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.827068167260322e-08</v>
+        <v>2.827068167260312e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.847315033524357e-08</v>
+        <v>2.847315033524352e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>1.980925763985461e-08</v>
+        <v>2.893278927622775e-08</v>
       </c>
     </row>
   </sheetData>
@@ -7643,37 +7643,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.313624465274691e-07</v>
+        <v>1.313624465274688e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>1.536176713893512e-07</v>
+        <v>1.536176713893511e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>4.242143478057777e-07</v>
+        <v>4.242143478057783e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.536176713893512e-07</v>
+        <v>1.536176713893511e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.536176713893512e-07</v>
+        <v>1.536176713893511e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>2.586671471842161e-07</v>
+        <v>2.586671471842148e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>2.388729184164358e-07</v>
+        <v>2.388729184164359e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.536176713893512e-07</v>
+        <v>1.536176713893511e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>2.098113904826161e-07</v>
+        <v>2.098113904826159e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.476347299631443e-07</v>
+        <v>1.476347299631442e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.675890187799696e-07</v>
+        <v>7.787875983176572e-07</v>
       </c>
     </row>
     <row r="3">
@@ -7683,37 +7683,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.414372404060642e-09</v>
+        <v>9.414372404060693e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>8.851012288358318e-09</v>
+        <v>8.851012288358445e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>9.414372404060642e-09</v>
+        <v>9.414372404060693e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>8.973103828538966e-09</v>
+        <v>8.973103828538976e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>8.973103828538941e-09</v>
+        <v>8.973103828538974e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>9.358101306341561e-09</v>
+        <v>9.35810130634156e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>9.414372404060642e-09</v>
+        <v>9.414372404060693e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>9.1272051015497e-09</v>
+        <v>9.127205101549672e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>9.414372404060642e-09</v>
+        <v>9.414372404060693e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>9.414372404060642e-09</v>
+        <v>9.414372404060693e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>9.414372404060642e-09</v>
+        <v>9.414372404060693e-09</v>
       </c>
     </row>
     <row r="4">
@@ -7723,37 +7723,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.781975965663923e-08</v>
+        <v>3.781975965663932e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>2.293735403605056e-08</v>
+        <v>2.293735403605072e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>2.390079954378278e-08</v>
+        <v>2.390063964562044e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>2.186835276665706e-08</v>
+        <v>2.186835276665713e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>2.314292924297918e-08</v>
+        <v>2.31429292429791e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>2.336575963957764e-08</v>
+        <v>3.776348855892024e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>3.838126160890507e-08</v>
+        <v>3.838126160890482e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>3.75325923541281e-08</v>
+        <v>3.753259235412833e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>2.426750140125037e-08</v>
+        <v>2.426750140125051e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>2.329474028362937e-08</v>
+        <v>2.329474028362921e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>2.361981188961914e-08</v>
+        <v>2.361981188961915e-08</v>
       </c>
     </row>
     <row r="5">
@@ -7763,37 +7763,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.524844454104995e-08</v>
+        <v>4.524844454104994e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>4.49612772385391e-08</v>
+        <v>4.496127723853892e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>4.524608559033409e-08</v>
+        <v>4.524608559033421e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>4.49578697752394e-08</v>
+        <v>4.495786977523919e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>4.495786977523941e-08</v>
+        <v>4.495786977523919e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>4.519217344333099e-08</v>
+        <v>4.51921734433308e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>4.524844454104995e-08</v>
+        <v>4.524844454104994e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>4.49612772385391e-08</v>
+        <v>4.496127723853892e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>4.524844454104995e-08</v>
+        <v>4.524844454104994e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>4.524844454104995e-08</v>
+        <v>4.524844454104994e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>4.524844454104995e-08</v>
+        <v>4.524844454104994e-08</v>
       </c>
     </row>
     <row r="6">
@@ -7803,37 +7803,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.404741569466059e-07</v>
+        <v>1.404741569466056e-07</v>
       </c>
       <c r="C6" t="n">
         <v>2.255818945799383e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>2.435562942480367e-07</v>
+        <v>2.435562942480371e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>2.022292712049725e-07</v>
+        <v>2.022292712049722e-07</v>
       </c>
       <c r="F6" t="n">
         <v>1.428927268038852e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>2.257962608951476e-07</v>
+        <v>2.257962608951471e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>2.258525319928653e-07</v>
+        <v>2.25852531992865e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>2.255653646903554e-07</v>
+        <v>2.255653646903552e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>2.258693113025426e-07</v>
+        <v>2.25869311302542e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.388882097956416e-07</v>
+        <v>1.388882097956413e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>3.15037383964173e-07</v>
+        <v>3.150373839641726e-07</v>
       </c>
     </row>
     <row r="7">
@@ -7843,16 +7843,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.028594432737326e-07</v>
+        <v>1.028594432737327e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>1.29330966012923e-07</v>
+        <v>1.293309660129232e-07</v>
       </c>
       <c r="D7" t="n">
         <v>1.296181447026466e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>1.602099130166554e-07</v>
+        <v>1.602099130166555e-07</v>
       </c>
       <c r="F7" t="n">
         <v>1.293309466350701e-07</v>
@@ -7864,13 +7864,13 @@
         <v>1.296181333154341e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>1.29330966012923e-07</v>
+        <v>1.293309660129232e-07</v>
       </c>
       <c r="J7" t="n">
         <v>1.296181333154341e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>9.592416319233475e-08</v>
+        <v>1.141140480052057e-07</v>
       </c>
       <c r="L7" t="n">
         <v>1.296181333154341e-07</v>
@@ -7883,37 +7883,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.877052095719009e-08</v>
+        <v>2.877052095719006e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.138645003649593e-08</v>
+        <v>2.138645003649592e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.097665194914618e-08</v>
+        <v>2.097665194914612e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.138645003649593e-08</v>
+        <v>2.138645003649592e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>2.138645003649593e-08</v>
+        <v>2.138645003649592e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.557481305691732e-08</v>
+        <v>2.557481305691726e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.663730203589173e-08</v>
+        <v>2.663730203589171e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.138645003649593e-08</v>
+        <v>2.138645003649592e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.701142585176458e-08</v>
+        <v>2.701142585176457e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>2.840770065003016e-08</v>
+        <v>2.840770065003011e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>1.506481516017918e-08</v>
+        <v>1.506481516017915e-08</v>
       </c>
     </row>
     <row r="9">
@@ -7923,34 +7923,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.91721709061347e-08</v>
+        <v>2.917217090613468e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.213256053481776e-08</v>
+        <v>2.213256053481773e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>2.599801883385405e-08</v>
+        <v>2.599801883385403e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>2.213256053481776e-08</v>
+        <v>2.213256053481773e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.213256053481776e-08</v>
+        <v>2.213256053481773e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.784306702509297e-08</v>
+        <v>2.784306702509293e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.830650117183269e-08</v>
+        <v>2.830650117183268e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.213256053481776e-08</v>
+        <v>2.213256053481773e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.845686130039886e-08</v>
+        <v>2.845686130039885e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.902448373594488e-08</v>
+        <v>2.902448373594487e-08</v>
       </c>
       <c r="L9" t="n">
         <v>2.360127126400122e-08</v>

--- a/Results/Hydrogen/hydrogen human toxicity non-carcinogenic results.xlsx
+++ b/Results/Hydrogen/hydrogen human toxicity non-carcinogenic results.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,321 +511,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.208774686984616e-07</v>
+        <v>3.079088033912748e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>2.8957068670058e-07</v>
+        <v>2.362367363988627e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>6.460381455771428e-07</v>
+        <v>3.090853726105922e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>2.8957068670058e-07</v>
+        <v>2.362367363988627e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>2.8957068670058e-07</v>
+        <v>2.362367363988627e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>4.782335421661946e-07</v>
+        <v>3.067178891406407e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.388575731042437e-06</v>
+        <v>3.153405308804537e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>2.8957068670058e-07</v>
+        <v>2.362367363988627e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>3.915720700217548e-07</v>
+        <v>3.063256040504251e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>3.391835828110431e-07</v>
+        <v>3.05943570668878e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.719332397625914e-06</v>
+        <v>3.04777674698514e-08</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.048586797748796e-08</v>
+        <v>3.06244800376902e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>9.823604571966567e-09</v>
+        <v>2.359861633153321e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.048586797748796e-08</v>
+        <v>3.06244800376902e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>9.971781075772123e-09</v>
+        <v>2.359861633153321e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>9.971781075772123e-09</v>
+        <v>2.359861633153321e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.04272755875685e-08</v>
+        <v>3.056771055795945e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.048586797748796e-08</v>
+        <v>3.06244800376902e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.018386544921411e-08</v>
+        <v>2.359861633153321e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.048586797748796e-08</v>
+        <v>3.06244800376902e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.048586797748796e-08</v>
+        <v>3.06244800376902e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.048586797748796e-08</v>
+        <v>3.06244800376902e-08</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.73434491161207e-08</v>
+        <v>5.208774686984623e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>2.673854634041256e-08</v>
+        <v>2.895706867005805e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>2.784762507338721e-08</v>
+        <v>6.460381455771429e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>2.548491360674054e-08</v>
+        <v>2.895706867005805e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>2.705652080202821e-08</v>
+        <v>2.895706867005805e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>4.486141036053304e-08</v>
+        <v>4.782335421661967e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>4.57635850916316e-08</v>
+        <v>1.388575731042438e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>4.461800022217863e-08</v>
+        <v>2.895706867005805e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>4.503569823789021e-08</v>
+        <v>3.915720700217549e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>2.723826078474662e-08</v>
+        <v>3.391835828110435e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>2.778459490500739e-08</v>
+        <v>1.719332397625919e-06</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.203454469630298e-08</v>
+        <v>1.048586797748796e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>5.173254216802916e-08</v>
+        <v>9.823604571966596e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>5.203181954952334e-08</v>
+        <v>1.048586797748796e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>5.172579108225326e-08</v>
+        <v>9.971781075772108e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>5.172579108225326e-08</v>
+        <v>9.971781075772099e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>5.197595230638355e-08</v>
+        <v>1.042727558756853e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>5.203454469630298e-08</v>
+        <v>1.048586797748796e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>5.173254216802916e-08</v>
+        <v>1.018386544921406e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>5.203454469630298e-08</v>
+        <v>1.048586797748796e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>5.203454469630298e-08</v>
+        <v>1.048586797748796e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>5.203454469630298e-08</v>
+        <v>1.048586797748796e-08</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.619281433374783e-07</v>
+        <v>2.734344911612073e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>2.603099594232249e-07</v>
+        <v>2.67385463404129e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>2.81054878607711e-07</v>
+        <v>2.784762507338724e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>2.333228156862635e-07</v>
+        <v>2.548491360674044e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.647513435469373e-07</v>
+        <v>2.705652080202825e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>2.605369568454368e-07</v>
+        <v>4.486141036053305e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.605955492353574e-07</v>
+        <v>4.576358509163164e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>2.602935467070824e-07</v>
+        <v>4.46180002221786e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>2.606149402221149e-07</v>
+        <v>4.503569823789026e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.600953456156854e-07</v>
+        <v>2.723826078474677e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>3.636619051434994e-07</v>
+        <v>2.778459490500737e-08</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.377834581406584e-07</v>
+        <v>5.203454469630307e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.737494566589812e-07</v>
+        <v>5.173254216802913e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.740514622792913e-07</v>
+        <v>5.203181954952328e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>2.15601917834153e-07</v>
+        <v>5.172579108225332e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.737494200014617e-07</v>
+        <v>5.172579108225332e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.739928667973355e-07</v>
+        <v>5.197595230638358e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.740514591872551e-07</v>
+        <v>5.203454469630307e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.737494566589812e-07</v>
+        <v>5.173254216802913e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.740514591872551e-07</v>
+        <v>5.203454469630307e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.283835712529137e-07</v>
+        <v>5.203454469630307e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.740514591872551e-07</v>
+        <v>5.203454469630307e-08</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.129908477934793e-08</v>
+        <v>1.619281433374784e-07</v>
       </c>
       <c r="C8" t="n">
-        <v>1.948022917583344e-08</v>
+        <v>2.603099594232252e-07</v>
       </c>
       <c r="D8" t="n">
-        <v>1.883962123709898e-08</v>
+        <v>2.810548786077115e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>1.948022917583344e-08</v>
+        <v>2.333228156862635e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>1.948022917583344e-08</v>
+        <v>1.647513435469373e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>2.258883102913944e-08</v>
+        <v>2.605369568454371e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>6.201465405900854e-09</v>
+        <v>2.605955492353576e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>1.948022917583344e-08</v>
+        <v>2.602935467070827e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>2.466628784649329e-08</v>
+        <v>2.606149402221152e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>2.542418024326649e-08</v>
+        <v>1.600953456156854e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>2.790675859272356e-08</v>
+        <v>3.636619051435e-07</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.377834581406585e-07</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1.737494566589812e-07</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.740514622792914e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2.156019178341529e-07</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.737494200014619e-07</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.739928667973356e-07</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.740514591872551e-07</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.737494566589812e-07</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.740514591872551e-07</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.283835712529138e-07</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.740514591872551e-07</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.129908477934795e-08</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.948022917583343e-08</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.883962123709904e-08</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.948022917583343e-08</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.948022917583343e-08</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.258883102913942e-08</v>
+      </c>
+      <c r="H10" t="n">
+        <v>6.201465405900873e-09</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.948022917583343e-08</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.466628784649334e-08</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.542418024326649e-08</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.790675859272358e-08</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B11" t="n">
         <v>2.654779577831035e-08</v>
       </c>
-      <c r="C9" t="n">
-        <v>2.174979435952172e-08</v>
-      </c>
-      <c r="D9" t="n">
-        <v>2.554638895067355e-08</v>
-      </c>
-      <c r="E9" t="n">
-        <v>2.174979435952172e-08</v>
-      </c>
-      <c r="F9" t="n">
-        <v>2.174979435952172e-08</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2.704137330127053e-08</v>
-      </c>
-      <c r="H9" t="n">
-        <v>2.042150359905166e-08</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2.174979435952172e-08</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2.792156397041599e-08</v>
-      </c>
-      <c r="K9" t="n">
-        <v>2.822820408805279e-08</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.828895309095083e-08</v>
+      <c r="C11" t="n">
+        <v>2.174979435952173e-08</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.554638895067354e-08</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2.174979435952173e-08</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.174979435952173e-08</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.70413733012706e-08</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.042150359905164e-08</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.174979435952173e-08</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.792156397041602e-08</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.822820408805281e-08</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.828895309095085e-08</v>
       </c>
     </row>
   </sheetData>
@@ -839,7 +919,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -907,321 +987,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.311720942242096e-07</v>
+        <v>2.950372214542894e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.692107623922695e-07</v>
+        <v>2.285708385989941e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.798460775314918e-07</v>
+        <v>2.9559648641582e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.692107623922695e-07</v>
+        <v>2.285708385989941e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.692107623922695e-07</v>
+        <v>2.285708385989941e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.714459650966433e-07</v>
+        <v>2.952059099982617e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.916171655488518e-07</v>
+        <v>2.955624094341565e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.692107623922695e-07</v>
+        <v>2.285708385989941e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>2.182707071170223e-07</v>
+        <v>2.959953635127175e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.371884676106654e-07</v>
+        <v>2.950837694283219e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.794947993647035e-07</v>
+        <v>2.95337923145691e-08</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.383474804721482e-09</v>
+        <v>2.972064609486768e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>8.939804762932323e-09</v>
+        <v>2.292766837154321e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>9.383474804721482e-09</v>
+        <v>2.972064609486768e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>9.054048705352947e-09</v>
+        <v>2.292766837154321e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>9.054048705352898e-09</v>
+        <v>2.292766837154321e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>9.331560563048389e-09</v>
+        <v>2.969247025980715e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>9.383474804721482e-09</v>
+        <v>2.972064609486768e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>9.124121051534123e-09</v>
+        <v>2.292766837154321e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>9.383474804721482e-09</v>
+        <v>2.972064609486768e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>9.383474804721482e-09</v>
+        <v>2.972064609486768e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>9.383474804721482e-09</v>
+        <v>2.972064609486768e-08</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.320374540545928e-08</v>
+        <v>1.311720942242091e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>2.29203916130206e-08</v>
+        <v>1.692107623922695e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>3.726428723108948e-08</v>
+        <v>1.798460775314918e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>2.185133571467663e-08</v>
+        <v>1.692107623922695e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>2.298067051126004e-08</v>
+        <v>1.692107623922695e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>3.694512539637311e-08</v>
+        <v>1.714459650966445e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>3.756564040490177e-08</v>
+        <v>1.916171655488517e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>2.294439165227196e-08</v>
+        <v>1.692107623922695e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>2.404641566564205e-08</v>
+        <v>2.182707071170219e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>2.316848337931692e-08</v>
+        <v>1.371884676106653e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>2.322190109974807e-08</v>
+        <v>1.794947993647035e-07</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.512137265085345e-08</v>
+        <v>9.383474804721364e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>4.486201889766598e-08</v>
+        <v>8.939804762932293e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>4.511901048942477e-08</v>
+        <v>9.383474804721364e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>4.486329842553131e-08</v>
+        <v>9.054048705352823e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>4.486329842553131e-08</v>
+        <v>9.054048705352825e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>4.506945840918033e-08</v>
+        <v>9.331560563048286e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>4.512137265085345e-08</v>
+        <v>9.383474804721364e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>4.486201889766598e-08</v>
+        <v>9.124121051533992e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>4.512137265085345e-08</v>
+        <v>9.383474804721364e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>4.512137265085345e-08</v>
+        <v>9.383474804721364e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>4.512137265085345e-08</v>
+        <v>9.383474804721364e-09</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.400326235169464e-07</v>
+        <v>2.320374540545923e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>2.249008329621832e-07</v>
+        <v>2.29203916130202e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>2.427866320398828e-07</v>
+        <v>3.726428723108948e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>2.01622065922475e-07</v>
+        <v>2.185133571467688e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.424731900228131e-07</v>
+        <v>2.298067051125997e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>2.250873097673018e-07</v>
+        <v>3.694512539637295e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.251392240089745e-07</v>
+        <v>3.756564040490155e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>2.248798702557878e-07</v>
+        <v>2.294439165227188e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>2.251559499073104e-07</v>
+        <v>2.404641566564169e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.384517247178397e-07</v>
+        <v>2.316848337931688e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>3.140401847331001e-07</v>
+        <v>2.322190109974801e-08</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.681609756191532e-08</v>
+        <v>4.512137265085344e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.216479354593186e-07</v>
+        <v>4.486201889766602e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.219072985238701e-07</v>
+        <v>4.511901048942471e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.506026243078719e-07</v>
+        <v>4.486329842553129e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.216479172878717e-07</v>
+        <v>4.486329842553129e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.218553749708329e-07</v>
+        <v>4.506945840918032e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.219072892125059e-07</v>
+        <v>4.512137265085344e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.216479354593186e-07</v>
+        <v>4.486201889766602e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.219072892125059e-07</v>
+        <v>4.512137265085344e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.073693581457655e-07</v>
+        <v>4.512137265085344e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.219072892125059e-07</v>
+        <v>4.512137265085344e-08</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.860728578974069e-08</v>
+        <v>1.400326235169464e-07</v>
       </c>
       <c r="C8" t="n">
-        <v>2.094026148447194e-08</v>
+        <v>2.249008329621832e-07</v>
       </c>
       <c r="D8" t="n">
-        <v>2.743641763275453e-08</v>
+        <v>2.427866320398823e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>2.094026148447194e-08</v>
+        <v>2.016220659224748e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>2.094026148447194e-08</v>
+        <v>1.424731900228127e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>2.764582526098469e-08</v>
+        <v>2.250873097673012e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>2.755160981908971e-08</v>
+        <v>2.251392240089745e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>2.094026148447194e-08</v>
+        <v>2.248798702557874e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>2.662489829623669e-08</v>
+        <v>2.251559499073106e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>2.851122855112322e-08</v>
+        <v>1.384517247178396e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>2.787421633221024e-08</v>
+        <v>3.140401847330998e-07</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>9.681609756191519e-08</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1.216479354593184e-07</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.219072985238703e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.506026243078716e-07</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.216479172878719e-07</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.218553749708328e-07</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.21907289212506e-07</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.216479354593184e-07</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.219072892125059e-07</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.073693581457653e-07</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.219072892125059e-07</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.860728578974073e-08</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2.094026148447193e-08</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.743641763275455e-08</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.094026148447193e-08</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2.094026148447193e-08</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.764582526098476e-08</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.755160981908977e-08</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.094026148447193e-08</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.662489829623669e-08</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.851122855112326e-08</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.787421633221032e-08</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>2.899713965852737e-08</v>
-      </c>
-      <c r="C9" t="n">
-        <v>2.195280739279203e-08</v>
-      </c>
-      <c r="D9" t="n">
-        <v>2.852031741191629e-08</v>
-      </c>
-      <c r="E9" t="n">
-        <v>2.195280739279203e-08</v>
-      </c>
-      <c r="F9" t="n">
-        <v>2.195280739279203e-08</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2.858936100309135e-08</v>
-      </c>
-      <c r="H9" t="n">
-        <v>2.856932252562815e-08</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2.195280739279203e-08</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2.819096123733173e-08</v>
-      </c>
-      <c r="K9" t="n">
+      <c r="B11" t="n">
+        <v>2.899713965852741e-08</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2.195280739279201e-08</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.852031741191634e-08</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2.195280739279201e-08</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.195280739279201e-08</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.858936100309138e-08</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.856932252562821e-08</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.195280739279201e-08</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.819096123733175e-08</v>
+      </c>
+      <c r="K11" t="n">
         <v>2.895808810624344e-08</v>
       </c>
-      <c r="L9" t="n">
-        <v>2.870006884633408e-08</v>
+      <c r="L11" t="n">
+        <v>2.870006884633413e-08</v>
       </c>
     </row>
   </sheetData>
@@ -1235,7 +1395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1303,321 +1463,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.222901508897996e-07</v>
+        <v>2.252636970853918e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>2.755615218627686e-07</v>
+        <v>1.80941679404331e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>4.059070558766446e-07</v>
+        <v>2.838340869019685e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>2.161378819984956e-07</v>
+        <v>2.200866949145529e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>2.161378819984956e-07</v>
+        <v>2.200866949145529e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>3.001147196069547e-07</v>
+        <v>3.186727663334657e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>7.062243832099785e-07</v>
+        <v>2.863978797383236e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>2.161378819984956e-07</v>
+        <v>2.200866949145529e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>3.588950044872083e-07</v>
+        <v>2.483851176136661e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>2.128699494007313e-07</v>
+        <v>3.19800741982532e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>4.201541786952031e-07</v>
+        <v>2.782369449120876e-08</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.406723322978701e-09</v>
+        <v>2.258954892652413e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>8.550951276110704e-09</v>
+        <v>1.79766183253939e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>9.406723322978674e-09</v>
+        <v>2.827576495152726e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>8.950838397286659e-09</v>
+        <v>2.201643766238434e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>8.950838397286654e-09</v>
+        <v>2.201643766238434e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>9.350530755374099e-09</v>
+        <v>3.19404132490426e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>9.406723322978702e-09</v>
+        <v>2.827576495152726e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>9.120407671234039e-09</v>
+        <v>2.201643766238434e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>9.406723322978702e-09</v>
+        <v>2.474277182851311e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>9.406723322978674e-09</v>
+        <v>3.214667107619785e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>9.406723322978674e-09</v>
+        <v>2.774352956654752e-08</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.972658361251513e-08</v>
+        <v>1.222901508897997e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>2.426722144188994e-08</v>
+        <v>2.755615218627697e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>2.480054858171643e-08</v>
+        <v>4.05907055876646e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>2.291539308757223e-08</v>
+        <v>2.161378819984963e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>2.424123257561736e-08</v>
+        <v>2.161378819984963e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>2.445066463002371e-08</v>
+        <v>3.001147196069588e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>4.13418307870364e-08</v>
+        <v>7.062243832099815e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>2.422054154588389e-08</v>
+        <v>2.161378819984963e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>4.013704909342604e-08</v>
+        <v>3.58895004487209e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>2.442479590670001e-08</v>
+        <v>2.128699494007315e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>2.45770773003325e-08</v>
+        <v>4.201541786952033e-07</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.748873795123992e-08</v>
+        <v>9.406723322978588e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>4.733157640484138e-08</v>
+        <v>8.550951276110768e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>4.74863746145017e-08</v>
+        <v>9.406723322978592e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>4.720396177739955e-08</v>
+        <v>8.950838397286644e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>4.720396177739955e-08</v>
+        <v>8.950838397286666e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>4.743254538363519e-08</v>
+        <v>9.35053075537389e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>4.748873795123992e-08</v>
+        <v>9.406723322978592e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>4.720242229949542e-08</v>
+        <v>9.120407671234042e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>4.748873795123992e-08</v>
+        <v>9.406723322978588e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>4.748873795123992e-08</v>
+        <v>9.406723322978592e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>4.748873795123992e-08</v>
+        <v>9.406723322978592e-09</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.487011848653519e-07</v>
+        <v>3.972658361251523e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>2.393930258419778e-07</v>
+        <v>2.42672214418897e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>2.583613559180398e-07</v>
+        <v>2.480054858171646e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>2.144205764458488e-07</v>
+        <v>2.291539308757221e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.512962626000836e-07</v>
+        <v>2.424123257561746e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>2.394716617563461e-07</v>
+        <v>2.445066463002378e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.395278543240021e-07</v>
+        <v>4.134183078703633e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>2.392415386722062e-07</v>
+        <v>2.422054154588396e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>2.395457043801123e-07</v>
+        <v>4.013704909342608e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.470140328483934e-07</v>
+        <v>2.442479590670006e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>3.344039053887186e-07</v>
+        <v>2.457707730033252e-08</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.149916308108079e-07</v>
+        <v>4.748873795124003e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.450445442219928e-07</v>
+        <v>4.733157640484137e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.452017134817321e-07</v>
+        <v>4.74863746145018e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.797771515842614e-07</v>
+        <v>4.720396177739965e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.449153649573844e-07</v>
+        <v>4.720396177739965e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.451455132007869e-07</v>
+        <v>4.743254538363523e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.452017057683916e-07</v>
+        <v>4.748873795124003e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.449153901166468e-07</v>
+        <v>4.720242229949544e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.452017057683916e-07</v>
+        <v>4.748873795124003e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.276978729380507e-07</v>
+        <v>4.748873795124003e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.452017057683916e-07</v>
+        <v>4.748873795124003e-08</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.032693913022164e-08</v>
+        <v>1.487011848653516e-07</v>
       </c>
       <c r="C8" t="n">
-        <v>1.377093251256593e-08</v>
+        <v>2.393930258419782e-07</v>
       </c>
       <c r="D8" t="n">
-        <v>2.090837916199039e-08</v>
+        <v>2.583613559180393e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>1.906880636493893e-08</v>
+        <v>2.144205764458486e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>1.906880636493893e-08</v>
+        <v>1.512962626000834e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>2.716615608516462e-08</v>
+        <v>2.394716617563458e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>1.577757305085088e-08</v>
+        <v>2.395278543240016e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>1.906880636493893e-08</v>
+        <v>2.392415386722063e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>1.883099531241729e-08</v>
+        <v>2.395457043801114e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>2.925695603717988e-08</v>
+        <v>1.470140328483933e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>2.123397572074477e-08</v>
+        <v>3.344039053887175e-07</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.149916308108082e-07</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1.45044544221993e-07</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.45201713481732e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.797771515842618e-07</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.449153649573849e-07</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.451455132007869e-07</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.452017057683916e-07</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.449153901166472e-07</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.452017057683916e-07</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.276978729380509e-07</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.452017057683916e-07</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.032693913022163e-08</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.377093251256592e-08</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.090837916199037e-08</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.906880636493891e-08</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.90688063649389e-08</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.716615608516451e-08</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.577757305085084e-08</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.906880636493891e-08</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.883099531241744e-08</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.925695603717996e-08</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.123397572074479e-08</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>2.149687504071196e-08</v>
-      </c>
-      <c r="C9" t="n">
+      <c r="B11" t="n">
+        <v>2.149687504071194e-08</v>
+      </c>
+      <c r="C11" t="n">
         <v>1.618056749287089e-08</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D11" t="n">
         <v>2.503122467749212e-08</v>
       </c>
-      <c r="E9" t="n">
-        <v>2.066748785757403e-08</v>
-      </c>
-      <c r="F9" t="n">
-        <v>2.066748785757403e-08</v>
-      </c>
-      <c r="G9" t="n">
+      <c r="E11" t="n">
+        <v>2.066748785757406e-08</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.066748785757406e-08</v>
+      </c>
+      <c r="G11" t="n">
         <v>2.969497440912719e-08</v>
       </c>
-      <c r="H9" t="n">
-        <v>2.29530708296502e-08</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2.066748785757403e-08</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2.214863460682897e-08</v>
-      </c>
-      <c r="K9" t="n">
-        <v>3.066524464652458e-08</v>
-      </c>
-      <c r="L9" t="n">
-        <v>2.486182674665133e-08</v>
+      <c r="H11" t="n">
+        <v>2.295307082965021e-08</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.066748785757406e-08</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.214863460682899e-08</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.066524464652465e-08</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.486182674665131e-08</v>
       </c>
     </row>
   </sheetData>
@@ -1631,7 +1871,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1699,321 +1939,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.703254427529127e-08</v>
+        <v>2.239107062378599e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>2.190933287899249e-07</v>
+        <v>1.794794874047484e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>3.119500972891447e-07</v>
+        <v>2.824309922347226e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.713665719974648e-07</v>
+        <v>2.200196655852335e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.713665719974648e-07</v>
+        <v>2.200196655852335e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>2.228928323817693e-07</v>
+        <v>3.172111377478481e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>4.30743579210709e-07</v>
+        <v>2.833467178940358e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.713665719974648e-07</v>
+        <v>2.200196655852335e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>2.547552759642672e-07</v>
+        <v>2.482040652864954e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.4863946906799e-07</v>
+        <v>3.178636770675263e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>2.15361999793859e-07</v>
+        <v>2.766831727783534e-08</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.256616975581619e-09</v>
+        <v>2.249760918144368e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>8.427059156811152e-09</v>
+        <v>1.787730434893544e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>9.256616975581617e-09</v>
+        <v>2.821985370531851e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>8.916583658806842e-09</v>
+        <v>2.204932620570414e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>8.916583658806842e-09</v>
+        <v>2.204932620570414e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>9.201654131900127e-09</v>
+        <v>3.186345938204666e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>9.256616975581617e-09</v>
+        <v>2.821985370531851e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>8.978136939799592e-09</v>
+        <v>2.204932620570414e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>9.256616975581619e-09</v>
+        <v>2.482163465738432e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>9.256616975581617e-09</v>
+        <v>3.201318042080533e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>9.256616975581617e-09</v>
+        <v>2.777627047618247e-08</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.749362977541462e-08</v>
+        <v>7.703254427529137e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>2.29981572384311e-08</v>
+        <v>2.190933287899249e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>3.805797531118286e-08</v>
+        <v>3.119500972891454e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>2.175582431443566e-08</v>
+        <v>1.713665719974647e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>2.296590684718875e-08</v>
+        <v>1.713665719974647e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>3.743866693173303e-08</v>
+        <v>2.228928323817663e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>3.919082193006727e-08</v>
+        <v>4.307435792107081e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>2.293546326367742e-08</v>
+        <v>1.713665719974647e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>2.408724713636759e-08</v>
+        <v>2.547552759642671e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>2.313047760120064e-08</v>
+        <v>1.486394690679901e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>2.323724867710534e-08</v>
+        <v>2.15361999793859e-07</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.558450085685643e-08</v>
+        <v>9.256616975581521e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>4.542865786007816e-08</v>
+        <v>8.427059156811134e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>4.558226725971215e-08</v>
+        <v>9.256616975581521e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>4.533208886723331e-08</v>
+        <v>8.916583658806775e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>4.533208886723331e-08</v>
+        <v>8.916583658806731e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>4.552953801317481e-08</v>
+        <v>9.201654131900072e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>4.558450085685643e-08</v>
+        <v>9.256616975581521e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>4.530602082107434e-08</v>
+        <v>8.978136939799588e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>4.558450085685643e-08</v>
+        <v>9.256616975581521e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>4.558450085685643e-08</v>
+        <v>9.256616975581521e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>4.558450085685643e-08</v>
+        <v>9.256616975581521e-09</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.414896505722482e-07</v>
+        <v>3.749362977541459e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>2.276972892629029e-07</v>
+        <v>2.299815723843206e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>2.457071634913695e-07</v>
+        <v>3.805797531118284e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>2.039619008728247e-07</v>
+        <v>2.175582431443571e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.439642251275301e-07</v>
+        <v>2.29659068471888e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>2.277534441817214e-07</v>
+        <v>3.743866693173303e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.278084070255335e-07</v>
+        <v>3.919082193006716e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>2.275299269896208e-07</v>
+        <v>2.293546326367745e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>2.2782537114642e-07</v>
+        <v>2.408724713636756e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.398862353537943e-07</v>
+        <v>2.313047760120065e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>3.179755660096023e-07</v>
+        <v>2.323724867710539e-08</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.023885158749697e-07</v>
+        <v>4.55845008568563e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.289895925441023e-07</v>
+        <v>4.542865786007824e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.291454443759959e-07</v>
+        <v>4.55822672597121e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.59743855476473e-07</v>
+        <v>4.533208886723328e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.288669347278918e-07</v>
+        <v>4.533208886723328e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.290904726971989e-07</v>
+        <v>4.552953801317477e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.291454355408807e-07</v>
+        <v>4.55845008568563e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.288669555050985e-07</v>
+        <v>4.530602082107427e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.291454355408807e-07</v>
+        <v>4.55845008568563e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.136423749199363e-07</v>
+        <v>4.55845008568563e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.291454355408807e-07</v>
+        <v>4.55845008568563e-08</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.115533345593647e-08</v>
+        <v>1.414896505722481e-07</v>
       </c>
       <c r="C8" t="n">
-        <v>1.466893982085351e-08</v>
+        <v>2.276972892629021e-07</v>
       </c>
       <c r="D8" t="n">
-        <v>2.26250115487093e-08</v>
+        <v>2.457071634913693e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>1.991022127182274e-08</v>
+        <v>2.039619008728246e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>1.991022127182274e-08</v>
+        <v>1.439642251275299e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>2.854559223670902e-08</v>
+        <v>2.277534441817208e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>2.084939963775212e-08</v>
+        <v>2.278084070255335e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>1.991022127182274e-08</v>
+        <v>2.275299269896207e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>2.088599863775264e-08</v>
+        <v>2.278253711464202e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>3.041404849023893e-08</v>
+        <v>1.39886235353794e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>2.51207219622337e-08</v>
+        <v>3.179755660096019e-07</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.023885158749696e-07</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1.289895925441024e-07</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.291454443759955e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.597438554764728e-07</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.288669347278917e-07</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.290904726971987e-07</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.291454355408803e-07</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.288669555050985e-07</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.291454355408803e-07</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.136423749199362e-07</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.291454355408803e-07</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.115533345593645e-08</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.46689398208535e-08</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.262501154870923e-08</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.991022127182273e-08</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.991022127182273e-08</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.854559223670911e-08</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.084939963775214e-08</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.991022127182273e-08</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.088599863775256e-08</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3.041404849023869e-08</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.512072196223365e-08</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>2.178033089110127e-08</v>
-      </c>
-      <c r="C9" t="n">
+      <c r="B11" t="n">
+        <v>2.178033089110124e-08</v>
+      </c>
+      <c r="C11" t="n">
         <v>1.648813265574647e-08</v>
       </c>
-      <c r="D9" t="n">
-        <v>2.569742821251101e-08</v>
-      </c>
-      <c r="E9" t="n">
-        <v>2.102866699668436e-08</v>
-      </c>
-      <c r="F9" t="n">
-        <v>2.102866699668436e-08</v>
-      </c>
-      <c r="G9" t="n">
-        <v>3.021147365024104e-08</v>
-      </c>
-      <c r="H9" t="n">
+      <c r="D11" t="n">
+        <v>2.569742821251096e-08</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2.102866699668427e-08</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.102866699668427e-08</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3.021147365024103e-08</v>
+      </c>
+      <c r="H11" t="n">
         <v>2.498109170041743e-08</v>
       </c>
-      <c r="I9" t="n">
-        <v>2.102866699668436e-08</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2.302967959758937e-08</v>
-      </c>
-      <c r="K9" t="n">
-        <v>3.1058757582214e-08</v>
-      </c>
-      <c r="L9" t="n">
-        <v>2.646003424125765e-08</v>
+      <c r="I11" t="n">
+        <v>2.102866699668427e-08</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.302967959758936e-08</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.105875758221383e-08</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.646003424125762e-08</v>
       </c>
     </row>
   </sheetData>
@@ -2027,7 +2347,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2095,321 +2415,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.533321102686824e-08</v>
+        <v>2.228958155230094e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.806259566777204e-07</v>
+        <v>1.776256206850875e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>2.546993268080708e-07</v>
+        <v>2.804950342435889e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.389545253771423e-07</v>
+        <v>2.187677973175311e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.389545253771423e-07</v>
+        <v>2.187677973175311e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.805754237370941e-07</v>
+        <v>3.156746842978078e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>2.998964285339341e-07</v>
+        <v>2.807079987342176e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.389545253771423e-07</v>
+        <v>2.187677973175311e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.733946140574755e-07</v>
+        <v>2.469981238837167e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.260629689860197e-07</v>
+        <v>3.16086029937967e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.625486418498299e-07</v>
+        <v>2.759567119519196e-08</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.306899834860797e-09</v>
+        <v>2.24200986522358e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>8.4509569538185e-09</v>
+        <v>1.773401344792051e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>9.306899834860812e-09</v>
+        <v>2.809151323281873e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>8.991885028386513e-09</v>
+        <v>2.196069279832517e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>8.991885028386529e-09</v>
+        <v>2.196069279832517e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>9.252317019504921e-09</v>
+        <v>3.17567584914022e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>9.306899834860812e-09</v>
+        <v>2.809151323281873e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>9.030901602257808e-09</v>
+        <v>2.196069279832517e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>9.306899834860812e-09</v>
+        <v>2.479182913211054e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>9.306899834860812e-09</v>
+        <v>3.185980098246512e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>9.306899834860812e-09</v>
+        <v>2.775796242173333e-08</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.303760155240812e-08</v>
+        <v>5.533321102686834e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>2.281055276576174e-08</v>
+        <v>1.806259566777206e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>2.322857148952375e-08</v>
+        <v>2.546993268080709e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>2.159679788947378e-08</v>
+        <v>1.389545253771423e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>2.279120054444297e-08</v>
+        <v>1.389545253771423e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>3.720908654524647e-08</v>
+        <v>1.805754237370916e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>3.915128060441226e-08</v>
+        <v>2.998964285339347e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>3.69876711279993e-08</v>
+        <v>1.389545253771423e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>3.770331554147401e-08</v>
+        <v>1.733946140574755e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>2.29767133583994e-08</v>
+        <v>1.260629689860197e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>2.305146289392891e-08</v>
+        <v>1.6254864184983e-07</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.573783728017274e-08</v>
+        <v>9.306899834860875e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>4.558231657185833e-08</v>
+        <v>8.450956953818538e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>4.573560857808966e-08</v>
+        <v>9.306899834860875e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>4.549534744030514e-08</v>
+        <v>8.991885028386635e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>4.549534744030514e-08</v>
+        <v>8.99188502838665e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>4.568325446481678e-08</v>
+        <v>9.252317019504906e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>4.573783728017274e-08</v>
+        <v>9.306899834860875e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>4.546183904756966e-08</v>
+        <v>9.030901602257864e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>4.573783728017274e-08</v>
+        <v>9.306899834860875e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>4.573783728017274e-08</v>
+        <v>9.306899834860875e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>4.573783728017274e-08</v>
+        <v>9.306899834860875e-09</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.416985056632641e-07</v>
+        <v>2.303760155240826e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>2.280643641958396e-07</v>
+        <v>2.281055276576186e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>2.460980324162156e-07</v>
+        <v>2.322857148952299e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>2.042891440713846e-07</v>
+        <v>2.15967978894739e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.441847762988214e-07</v>
+        <v>2.279120054444311e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>2.281134333093033e-07</v>
+        <v>3.720908654524661e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.281680161248677e-07</v>
+        <v>3.915128060441253e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>2.278920178920562e-07</v>
+        <v>3.698767112799953e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>2.281850098727919e-07</v>
+        <v>3.77033155414742e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.400922901116481e-07</v>
+        <v>2.29767133583997e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>3.184926502762919e-07</v>
+        <v>2.305146289392902e-08</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.721600898699048e-08</v>
+        <v>4.573783728017284e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.223947805556845e-07</v>
+        <v>4.55823165718584e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.225503107314298e-07</v>
+        <v>4.573560857808976e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.515095236662838e-07</v>
+        <v>4.549534744030535e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.222742838014961e-07</v>
+        <v>4.549534744030535e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.224957184486429e-07</v>
+        <v>4.568325446481689e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.22550301263999e-07</v>
+        <v>4.573783728017284e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.222743030313959e-07</v>
+        <v>4.546183904756978e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.22550301263999e-07</v>
+        <v>4.573783728017284e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.072759795935431e-07</v>
+        <v>4.573783728017284e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.22550301263999e-07</v>
+        <v>4.573783728017284e-08</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.158937556148094e-08</v>
+        <v>1.416985056632646e-07</v>
       </c>
       <c r="C8" t="n">
-        <v>1.543687939126941e-08</v>
+        <v>2.280643641958399e-07</v>
       </c>
       <c r="D8" t="n">
-        <v>2.389198091538584e-08</v>
+        <v>2.460980324162151e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>2.060286533428631e-08</v>
+        <v>2.042891440713847e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>2.060286533428631e-08</v>
+        <v>1.441847762988215e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>2.943952144682936e-08</v>
+        <v>2.281134333093031e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>2.353514756821369e-08</v>
+        <v>2.281680161248674e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>2.060286533428631e-08</v>
+        <v>2.278920178920564e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>2.273929686508659e-08</v>
+        <v>2.281850098727921e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>3.080763979198794e-08</v>
+        <v>1.400922901116482e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>2.621492037660917e-08</v>
+        <v>3.18492650276292e-07</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>9.721600898699057e-08</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1.223947805556848e-07</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.225503107314301e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.515095236662841e-07</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.222742838014964e-07</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.224957184486433e-07</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.225503012639992e-07</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.222743030313962e-07</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.225503012639992e-07</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.072759795935434e-07</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.225503012639992e-07</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.158937556148096e-08</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.543687939126941e-08</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.389198091538586e-08</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.060286533428629e-08</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2.060286533428629e-08</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.943952144682941e-08</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.353514756821371e-08</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.060286533428629e-08</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.273929686508668e-08</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3.080763979198833e-08</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.621492037660919e-08</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>2.191159989865005e-08</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1.671735875220061e-08</v>
-      </c>
-      <c r="D9" t="n">
-        <v>2.613870283681151e-08</v>
-      </c>
-      <c r="E9" t="n">
-        <v>2.125896390847605e-08</v>
-      </c>
-      <c r="F9" t="n">
-        <v>2.125896390847605e-08</v>
-      </c>
-      <c r="G9" t="n">
+      <c r="B11" t="n">
+        <v>2.191159989865007e-08</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1.671735875220063e-08</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.613870283681153e-08</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2.125896390847603e-08</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.125896390847603e-08</v>
+      </c>
+      <c r="G11" t="n">
         <v>3.051311818990384e-08</v>
       </c>
-      <c r="H9" t="n">
-        <v>2.599763897575066e-08</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2.125896390847605e-08</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2.376590366584352e-08</v>
-      </c>
-      <c r="K9" t="n">
-        <v>3.112986629909073e-08</v>
-      </c>
-      <c r="L9" t="n">
-        <v>2.689358214727723e-08</v>
+      <c r="H11" t="n">
+        <v>2.599763897575067e-08</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.125896390847603e-08</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.376590366584357e-08</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.112986629909101e-08</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.689358214727724e-08</v>
       </c>
     </row>
   </sheetData>
@@ -2423,7 +2823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2491,321 +2891,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.568434661975125e-08</v>
+        <v>2.324434519502195e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.231590258313732e-07</v>
+        <v>1.739383322818374e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>2.884712142985514e-07</v>
+        <v>2.780456854155205e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.549909921922561e-07</v>
+        <v>2.163096519934515e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.549909921922561e-07</v>
+        <v>2.163096519934515e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>2.350830719629539e-07</v>
+        <v>3.161384416490228e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>5.849268824354486e-07</v>
+        <v>2.807020104995208e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.549909921922561e-07</v>
+        <v>2.163096519934515e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>3.442199200409555e-07</v>
+        <v>2.462979297489424e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.769459599961464e-07</v>
+        <v>3.1726684644857e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>4.106670879229748e-07</v>
+        <v>2.762057662251116e-08</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.013130338153829e-09</v>
+        <v>2.339241404326858e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>8.081716409742784e-09</v>
+        <v>1.743277596868446e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>9.013130338153829e-09</v>
+        <v>2.782012119023242e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>8.698211915682986e-09</v>
+        <v>2.170140141729226e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>8.698211915682985e-09</v>
+        <v>2.170140141729226e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>8.957248085565368e-09</v>
+        <v>3.175479101556486e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>9.013130338153829e-09</v>
+        <v>2.782012119023242e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>8.728655077954005e-09</v>
+        <v>2.170140141729226e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>9.013130338153829e-09</v>
+        <v>2.454728365695901e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>9.013130338153829e-09</v>
+        <v>3.193016161417579e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>9.013130338153829e-09</v>
+        <v>2.754737170898234e-08</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.368956564862893e-08</v>
+        <v>5.568434661974952e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>2.327378672870712e-08</v>
+        <v>1.23159025831366e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>2.386944550272006e-08</v>
+        <v>2.884712142985532e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>2.214264097251465e-08</v>
+        <v>1.54990992192251e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>2.343597621196692e-08</v>
+        <v>1.54990992192251e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>2.363368339604047e-08</v>
+        <v>2.350830719629596e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>4.014354416296132e-08</v>
+        <v>5.849268824354737e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>3.830869004263504e-08</v>
+        <v>1.54990992192251e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>2.463063950673201e-08</v>
+        <v>3.442199200409593e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>2.365614794937039e-08</v>
+        <v>1.769459599961469e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>2.377831507686743e-08</v>
+        <v>4.106670879229926e-07</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.700301859810207e-08</v>
+        <v>9.013130338153374e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>4.684418293868206e-08</v>
+        <v>8.081716409743218e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>4.700066386506627e-08</v>
+        <v>9.013130338153374e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>4.675876626807614e-08</v>
+        <v>8.698211915685498e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>4.675876626807614e-08</v>
+        <v>8.698211915685508e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>4.694713634551357e-08</v>
+        <v>8.957248085565905e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>4.700301859810207e-08</v>
+        <v>9.013130338153374e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>4.671854333790223e-08</v>
+        <v>8.728655077952211e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>4.700301859810207e-08</v>
+        <v>9.013130338153374e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>4.700301859810207e-08</v>
+        <v>9.013130338153374e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>4.700301859810207e-08</v>
+        <v>9.013130338153374e-09</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.480499285168226e-07</v>
+        <v>2.368956564863123e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>2.386100706041542e-07</v>
+        <v>2.327378672872636e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>2.575085386167898e-07</v>
+        <v>2.386944550272193e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>2.136829030882838e-07</v>
+        <v>2.214264097251635e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5066462619976e-07</v>
+        <v>2.343597621197077e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>2.386537717006544e-07</v>
+        <v>2.363368339605018e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.387096539532852e-07</v>
+        <v>4.01435441629492e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>2.384251786930433e-07</v>
+        <v>3.830869004262145e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>2.38727471200182e-07</v>
+        <v>2.463063950673659e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.463658775707851e-07</v>
+        <v>2.365614794936945e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>3.334113180272552e-07</v>
+        <v>2.377831507686737e-08</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.127873739168897e-07</v>
+        <v>4.700301859808732e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.423364596617637e-07</v>
+        <v>4.684418293869002e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.424953034233189e-07</v>
+        <v>4.700066386507212e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.764931094860202e-07</v>
+        <v>4.6758766268083e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.422107966289859e-07</v>
+        <v>4.6758766268083e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.424394130685953e-07</v>
+        <v>4.694713634548585e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.424952953211838e-07</v>
+        <v>4.700301859808732e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.422108200609839e-07</v>
+        <v>4.67185433379218e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.424952953211837e-07</v>
+        <v>4.700301859808732e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.252824123952537e-07</v>
+        <v>4.700301859808732e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.424952953211837e-07</v>
+        <v>4.700301859808732e-08</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.261066709133019e-08</v>
+        <v>1.480499285168146e-07</v>
       </c>
       <c r="C8" t="n">
-        <v>1.664195484885714e-08</v>
+        <v>2.386100706041482e-07</v>
       </c>
       <c r="D8" t="n">
-        <v>2.315579825795747e-08</v>
+        <v>2.575085386168123e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>2.014171752483642e-08</v>
+        <v>2.13682903088287e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>2.014171752483642e-08</v>
+        <v>1.506646261997918e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>2.842863748024336e-08</v>
+        <v>2.38653771700635e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>1.778433528838876e-08</v>
+        <v>2.387096539532558e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>2.014171752483642e-08</v>
+        <v>2.384251786930255e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>1.894704909631123e-08</v>
+        <v>2.387274712001504e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>2.98562852182828e-08</v>
+        <v>1.463658775707695e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>2.121774874418493e-08</v>
+        <v>3.334113180272486e-07</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.127873739168777e-07</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1.423364596617535e-07</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.424953034233304e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.764931094860201e-07</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.422107966289921e-07</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.424394130685986e-07</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.424952953211953e-07</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.422108200609761e-07</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.424952953211953e-07</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.252824123952454e-07</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.424952953211953e-07</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.261066709133312e-08</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.664195484885711e-08</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.31557982579523e-08</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.01417175248365e-08</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2.01417175248365e-08</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.842863748023945e-08</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.778433528838236e-08</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.01417175248365e-08</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.894704909631153e-08</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.985628521828557e-08</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.121774874418545e-08</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>2.288864784060871e-08</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1.703400709846604e-08</v>
-      </c>
-      <c r="D9" t="n">
-        <v>2.568228674305408e-08</v>
-      </c>
-      <c r="E9" t="n">
-        <v>2.09213040578642e-08</v>
-      </c>
-      <c r="F9" t="n">
-        <v>2.09213040578642e-08</v>
-      </c>
-      <c r="G9" t="n">
-        <v>3.010043370650628e-08</v>
-      </c>
-      <c r="H9" t="n">
-        <v>2.350388648246189e-08</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2.09213040578642e-08</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2.208166840290693e-08</v>
-      </c>
-      <c r="K9" t="n">
-        <v>3.07830642756798e-08</v>
-      </c>
-      <c r="L9" t="n">
-        <v>2.474057800221751e-08</v>
+      <c r="B11" t="n">
+        <v>2.28886478406066e-08</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1.703400709846793e-08</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.568228674305253e-08</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2.092130405787e-08</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.092130405787e-08</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3.01004337065032e-08</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.350388648246161e-08</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.092130405787e-08</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.208166840291131e-08</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.078306427567999e-08</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.47405780022155e-08</v>
       </c>
     </row>
   </sheetData>
@@ -2819,7 +3299,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2887,321 +3367,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.789617177504075e-08</v>
+        <v>2.364894281688643e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.267368563915145e-07</v>
+        <v>1.744437065274632e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.58614042096571e-07</v>
+        <v>2.775030518728518e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.483856296805618e-07</v>
+        <v>2.174966250723278e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.483856296805618e-07</v>
+        <v>2.174966250723278e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.460459815975529e-07</v>
+        <v>3.14970902876883e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.818634917904481e-07</v>
+        <v>2.775994299846201e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.483856296805618e-07</v>
+        <v>2.174966250723278e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>2.02653995585704e-07</v>
+        <v>2.44538540504844e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.252605877348062e-07</v>
+        <v>3.157870253133665e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.789737172727349e-07</v>
+        <v>2.741543349343871e-08</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.994051808659065e-09</v>
+        <v>2.379879609857137e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>8.159448110272305e-09</v>
+        <v>1.747366039925019e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>8.994051808659065e-09</v>
+        <v>2.790186206590571e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>8.792010769437861e-09</v>
+        <v>2.182072198596137e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>8.792010769437861e-09</v>
+        <v>2.182072198596137e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>8.941214494305637e-09</v>
+        <v>3.172558828233962e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>8.994051808659065e-09</v>
+        <v>2.790186206590571e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>8.729033447270951e-09</v>
+        <v>2.182072198596137e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>8.994051808659065e-09</v>
+        <v>2.450946598537051e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>8.994051808659065e-09</v>
+        <v>3.183099088346932e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>8.994051808659065e-09</v>
+        <v>2.755844031244121e-08</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.259383261907477e-08</v>
+        <v>5.789617177504073e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>2.231910516448862e-08</v>
+        <v>1.267368563915145e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>3.704493367207387e-08</v>
+        <v>1.586140420965708e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>2.125199752617318e-08</v>
+        <v>1.48385629680562e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>2.237125063794676e-08</v>
+        <v>1.48385629680562e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>2.25409953047213e-08</v>
+        <v>1.460459815975533e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>3.812528958922425e-08</v>
+        <v>1.818634917904479e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>3.626488382118797e-08</v>
+        <v>1.48385629680562e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>3.691166938177612e-08</v>
+        <v>2.026539955857038e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>2.25695939691564e-08</v>
+        <v>1.252605877348063e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>2.261245099405165e-08</v>
+        <v>1.789737172727347e-07</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.518617543446482e-08</v>
+        <v>8.994051808659073e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>4.503121424802531e-08</v>
+        <v>8.159448110272281e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>4.518394461757156e-08</v>
+        <v>8.994051808659052e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>4.497357167865486e-08</v>
+        <v>8.792010769437935e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>4.497357167865486e-08</v>
+        <v>8.792010769437933e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>4.513333812011134e-08</v>
+        <v>8.94121449430561e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>4.518617543446482e-08</v>
+        <v>8.994051808659073e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>4.492115707307676e-08</v>
+        <v>8.729033447271012e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>4.518617543446482e-08</v>
+        <v>8.994051808659073e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>4.518617543446482e-08</v>
+        <v>8.994051808659073e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>4.518617543446482e-08</v>
+        <v>8.994051808659073e-09</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.408540978176051e-07</v>
+        <v>2.259383261907471e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>2.268365117372801e-07</v>
+        <v>2.231910516448863e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>2.447682833306105e-07</v>
+        <v>3.704493367207391e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>2.031797608065279e-07</v>
+        <v>2.12519975261732e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.433498857023219e-07</v>
+        <v>2.237125063794675e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>2.268687842819687e-07</v>
+        <v>2.254099530472133e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.269216215964438e-07</v>
+        <v>3.81252895892242e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>2.266566032349338e-07</v>
+        <v>3.626488382118811e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>2.269385363430784e-07</v>
+        <v>3.691166938177612e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.39255349375055e-07</v>
+        <v>2.256959396915722e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>3.168263470444902e-07</v>
+        <v>2.261245099405166e-08</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.00416105521724e-07</v>
+        <v>4.51861754344648e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.265389981405961e-07</v>
+        <v>4.503121424802524e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.266939693517612e-07</v>
+        <v>4.518394461757168e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.567530144018712e-07</v>
+        <v>4.497357167865494e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.264289235762502e-07</v>
+        <v>4.497357167865494e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.266411220126821e-07</v>
+        <v>4.513333812011134e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.266939593270354e-07</v>
+        <v>4.51861754344648e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.264289409656474e-07</v>
+        <v>4.492115707307673e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.266939593270354e-07</v>
+        <v>4.51861754344648e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.114684718475047e-07</v>
+        <v>4.51861754344648e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.266939593270354e-07</v>
+        <v>4.51861754344648e-08</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.290197221119509e-08</v>
+        <v>1.408540978176051e-07</v>
       </c>
       <c r="C8" t="n">
-        <v>1.644873169808629e-08</v>
+        <v>2.268365117372803e-07</v>
       </c>
       <c r="D8" t="n">
-        <v>2.603986584655465e-08</v>
+        <v>2.447682833306102e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>2.022857521620286e-08</v>
+        <v>2.03179760806528e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>2.022857521620286e-08</v>
+        <v>1.433498857023221e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>3.021943691883729e-08</v>
+        <v>2.268687842819686e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>2.587912052676843e-08</v>
+        <v>2.269216215964436e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>2.022857521620286e-08</v>
+        <v>2.26656603234934e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>2.177260180295055e-08</v>
+        <v>2.269385363430787e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>3.079147215966456e-08</v>
+        <v>1.392553493750549e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>2.56628894272733e-08</v>
+        <v>3.168263470444899e-07</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.004161055217242e-07</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1.265389981405963e-07</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.266939693517613e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.567530144018713e-07</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.264289235762503e-07</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.266411220126823e-07</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.266939593270356e-07</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.264289409656477e-07</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.266939593270356e-07</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.11468471847505e-07</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.266939593270356e-07</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.290197221119511e-08</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.64487316980863e-08</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.60398658465547e-08</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.022857521620287e-08</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2.022857521620287e-08</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3.021943691883734e-08</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.587912052676844e-08</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.022857521620287e-08</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.177260180295053e-08</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3.079147215966474e-08</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.566288942727329e-08</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>2.324088509012204e-08</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1.697802482746273e-08</v>
-      </c>
-      <c r="D9" t="n">
-        <v>2.690309097365057e-08</v>
-      </c>
-      <c r="E9" t="n">
-        <v>2.1025230653122e-08</v>
-      </c>
-      <c r="F9" t="n">
-        <v>2.1025230653122e-08</v>
-      </c>
-      <c r="G9" t="n">
-        <v>3.081178661747506e-08</v>
-      </c>
-      <c r="H9" t="n">
-        <v>2.683958915205971e-08</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2.1025230653122e-08</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2.320857212561468e-08</v>
-      </c>
-      <c r="K9" t="n">
-        <v>3.11057181992558e-08</v>
-      </c>
-      <c r="L9" t="n">
-        <v>2.655295179992503e-08</v>
+      <c r="B11" t="n">
+        <v>2.324088509012205e-08</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1.697802482746274e-08</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.690309097365056e-08</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2.102523065312197e-08</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.102523065312197e-08</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3.081178661747514e-08</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.683958915205972e-08</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.102523065312197e-08</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.32085721256147e-08</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.110571819925597e-08</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.655295179992504e-08</v>
       </c>
     </row>
   </sheetData>
@@ -3215,7 +3775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3283,321 +3843,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.069204458324918e-08</v>
+        <v>2.45236073353743e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.334090384506791e-07</v>
+        <v>1.764831392520023e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.589665275263017e-07</v>
+        <v>2.805268451908386e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.439869145618807e-07</v>
+        <v>2.20444016083141e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.439869145618807e-07</v>
+        <v>2.204440160831411e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.432637007950109e-07</v>
+        <v>3.178689015473096e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.671591230527352e-07</v>
+        <v>2.804654925718693e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.439869145618807e-07</v>
+        <v>2.204440160831411e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.693613954624687e-07</v>
+        <v>2.488077418284294e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.254793386931368e-07</v>
+        <v>3.182445558034663e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.571612068175298e-07</v>
+        <v>2.766633567568102e-08</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.497418079191807e-09</v>
+        <v>2.468338563848914e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>8.653137007384503e-09</v>
+        <v>1.767238272824556e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>9.497418079191807e-09</v>
+        <v>2.820788390813926e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>9.290519439811848e-09</v>
+        <v>2.212458978296248e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>9.290519439811848e-09</v>
+        <v>2.212458978296249e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>9.444449049762409e-09</v>
+        <v>3.202246076864696e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>9.497418079191805e-09</v>
+        <v>2.820788390813926e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>9.231718040933513e-09</v>
+        <v>2.212458978296249e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>9.497418079191805e-09</v>
+        <v>2.498010480223538e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>9.497418079191807e-09</v>
+        <v>3.207964409318835e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>9.497418079191807e-09</v>
+        <v>2.78352206269042e-08</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.732969641789996e-08</v>
+        <v>6.069204458324932e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>2.282329883655364e-08</v>
+        <v>1.334090384506792e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>2.311626560772094e-08</v>
+        <v>1.589665275263017e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>2.171859819323e-08</v>
+        <v>1.439869145618807e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>2.286328888984121e-08</v>
+        <v>1.439869145618807e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>3.72767273884708e-08</v>
+        <v>1.432637007950131e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>2.310632770449409e-08</v>
+        <v>1.671591230527352e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>3.706399637964154e-08</v>
+        <v>1.439869145618807e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>2.393586560602818e-08</v>
+        <v>1.693613954624688e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>2.306819439215698e-08</v>
+        <v>1.25479338693137e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>2.310060406840362e-08</v>
+        <v>1.5716120681753e-07</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.609885196558804e-08</v>
+        <v>9.497418079192033e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>4.594374277471424e-08</v>
+        <v>8.653137007384329e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>4.609661777722312e-08</v>
+        <v>9.497418079192033e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>4.588770997006106e-08</v>
+        <v>9.290519439811827e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>4.588770997006106e-08</v>
+        <v>9.29051943981183e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>4.604588293615876e-08</v>
+        <v>9.444449049762841e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>4.609885196558804e-08</v>
+        <v>9.497418079192033e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>4.583315192732962e-08</v>
+        <v>9.231718040933541e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>4.609885196558804e-08</v>
+        <v>9.497418079192033e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>4.609885196558804e-08</v>
+        <v>9.497418079192033e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>4.609885196558804e-08</v>
+        <v>9.497418079192033e-09</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.420528585110759e-07</v>
+        <v>3.732969641790014e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>2.286573136674116e-07</v>
+        <v>2.282329883655398e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>2.467156036127833e-07</v>
+        <v>2.31162656077209e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>2.048302186395895e-07</v>
+        <v>2.171859819323044e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.445688984001635e-07</v>
+        <v>2.286328888984108e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>2.286874120593964e-07</v>
+        <v>3.727672738847095e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.287403810890293e-07</v>
+        <v>2.310632770449401e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>2.284746810505668e-07</v>
+        <v>3.706399637964163e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>2.287574176810306e-07</v>
+        <v>2.39358656060282e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.404425932726324e-07</v>
+        <v>2.306819439215694e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>3.192927471244169e-07</v>
+        <v>2.310060406840382e-08</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.68071102519319e-08</v>
+        <v>4.60988519655881e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.218701019940348e-07</v>
+        <v>4.594374277471421e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.220252214453145e-07</v>
+        <v>4.609661777722317e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.50860652633224e-07</v>
+        <v>4.588770997006107e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.217594939025195e-07</v>
+        <v>4.588770997006107e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.219722421554794e-07</v>
+        <v>4.60458829361589e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.220252111849084e-07</v>
+        <v>4.60988519655881e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.217595111466502e-07</v>
+        <v>4.583315192732953e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.220252111849084e-07</v>
+        <v>4.60988519655881e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.074137487807057e-07</v>
+        <v>4.60988519655881e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.220252111849084e-07</v>
+        <v>4.60988519655881e-08</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.372613791644334e-08</v>
+        <v>1.420528585110759e-07</v>
       </c>
       <c r="C8" t="n">
-        <v>1.649508664794367e-08</v>
+        <v>2.286573136674114e-07</v>
       </c>
       <c r="D8" t="n">
-        <v>2.63434157813624e-08</v>
+        <v>2.467156036127832e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>2.064472868031312e-08</v>
+        <v>2.048302186395892e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>2.064472868031312e-08</v>
+        <v>1.445688984001633e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>3.05881477544541e-08</v>
+        <v>2.286874120593961e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>2.650699592877281e-08</v>
+        <v>2.287403810890291e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>2.064472868031312e-08</v>
+        <v>2.284746810505666e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>2.302025911146006e-08</v>
+        <v>2.287574176810307e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>3.10409147621487e-08</v>
+        <v>1.404425932726325e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>2.640508706035529e-08</v>
+        <v>3.192927471244165e-07</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>9.68071102519318e-08</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1.218701019940347e-07</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.220252214453143e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.50860652633224e-07</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.217594939025194e-07</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.219722421554794e-07</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.220252111849088e-07</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.217595111466503e-07</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.220252111849088e-07</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.074137487807055e-07</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.220252111849088e-07</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.372613791644333e-08</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.649508664794363e-08</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.634341578136239e-08</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.06447286803131e-08</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2.06447286803131e-08</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3.05881477544541e-08</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.650699592877282e-08</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.06447286803131e-08</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.302025911146008e-08</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3.104091476214869e-08</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.640508706035524e-08</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>2.4088056571276e-08</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1.711264045684283e-08</v>
-      </c>
-      <c r="D9" t="n">
-        <v>2.720434557969305e-08</v>
-      </c>
-      <c r="E9" t="n">
-        <v>2.137106009057113e-08</v>
-      </c>
-      <c r="F9" t="n">
-        <v>2.137106009057113e-08</v>
-      </c>
-      <c r="G9" t="n">
-        <v>3.113427316238881e-08</v>
-      </c>
-      <c r="H9" t="n">
-        <v>2.727263980616671e-08</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2.137106009057113e-08</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2.398903814788255e-08</v>
-      </c>
-      <c r="K9" t="n">
-        <v>3.135183042448954e-08</v>
-      </c>
-      <c r="L9" t="n">
-        <v>2.701562034533593e-08</v>
+      <c r="B11" t="n">
+        <v>2.408805657127597e-08</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1.711264045684282e-08</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.720434557969299e-08</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2.137106009057112e-08</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.137106009057112e-08</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3.113427316238887e-08</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.727263980616679e-08</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.137106009057112e-08</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.398903814788253e-08</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.135183042448958e-08</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.701562034533599e-08</v>
       </c>
     </row>
   </sheetData>
@@ -3611,7 +4251,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3679,321 +4319,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.738631250499764e-08</v>
+        <v>2.354043473326184e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.261642562957885e-07</v>
+        <v>1.747068708689081e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.786042160176893e-07</v>
+        <v>2.762329945241026e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.558915780655655e-07</v>
+        <v>2.158256051097972e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.558915780655655e-07</v>
+        <v>2.158256051097971e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.724956549212073e-07</v>
+        <v>3.144810979399137e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>5.106528671015386e-07</v>
+        <v>2.793649157118703e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.558915780655655e-07</v>
+        <v>2.158256051097971e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.639730118116254e-07</v>
+        <v>2.417341255845423e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.325242181666209e-07</v>
+        <v>3.147835465248514e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>3.587730042488144e-07</v>
+        <v>2.749186237290462e-08</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.977292411894917e-09</v>
+        <v>2.369234094487786e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>8.093550481976661e-09</v>
+        <v>1.750848171193688e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>8.977292411894917e-09</v>
+        <v>2.776002845631499e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>8.743228978306564e-09</v>
+        <v>2.165166132197742e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>8.743228978306563e-09</v>
+        <v>2.165166132197742e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>8.923655271241516e-09</v>
+        <v>3.165557254857793e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>8.977292411894917e-09</v>
+        <v>2.776002845631499e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>8.707092167158115e-09</v>
+        <v>2.165166132197742e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>8.977292411894917e-09</v>
+        <v>2.427786016650593e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>8.977292411894917e-09</v>
+        <v>3.172841949983597e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>8.977292411894917e-09</v>
+        <v>2.746863978564441e-08</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.341804155671921e-08</v>
+        <v>5.73863125049976e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>2.310128307357697e-08</v>
+        <v>1.261642562957886e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>2.345902220297626e-08</v>
+        <v>1.786042160176892e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>2.199121912616133e-08</v>
+        <v>1.558915780655661e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>2.318943770001742e-08</v>
+        <v>1.558915780655661e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>2.336440441606588e-08</v>
+        <v>1.724956549212084e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>3.965976638268885e-08</v>
+        <v>5.106528671015394e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>2.314784131198238e-08</v>
+        <v>1.558915780655661e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>2.42878950600431e-08</v>
+        <v>1.639730118116258e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>2.337559735011979e-08</v>
+        <v>1.325242181666205e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>2.349055948221912e-08</v>
+        <v>3.587730042488142e-07</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.688711736702652e-08</v>
+        <v>8.977292411894909e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>4.673124642832881e-08</v>
+        <v>8.093550481976717e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>4.688476276604602e-08</v>
+        <v>8.977292411894909e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>4.666550926152745e-08</v>
+        <v>8.743228978306538e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>4.666550926152745e-08</v>
+        <v>8.743228978306622e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>4.683348022637345e-08</v>
+        <v>8.923655271241725e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>4.688711736702652e-08</v>
+        <v>8.977292411894909e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>4.66169171222896e-08</v>
+        <v>8.70709216715816e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>4.688711736702652e-08</v>
+        <v>8.977292411894909e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>4.688711736702652e-08</v>
+        <v>8.977292411894909e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>4.688711736702652e-08</v>
+        <v>8.977292411894909e-09</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.477595739278926e-07</v>
+        <v>2.341804155671916e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>2.381696425210173e-07</v>
+        <v>2.310128307357725e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>2.570237934152175e-07</v>
+        <v>2.3459022202976e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>2.132969771822796e-07</v>
+        <v>2.199121912616111e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.503884355723885e-07</v>
+        <v>2.318943770001734e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>2.382046570770218e-07</v>
+        <v>2.336440441606603e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.382582942177158e-07</v>
+        <v>3.96597663826889e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>2.379880939729377e-07</v>
+        <v>2.314784131198235e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>2.382760798225355e-07</v>
+        <v>2.428789506004278e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.460785137351097e-07</v>
+        <v>2.337559735011962e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>3.327917749530345e-07</v>
+        <v>2.349055948221912e-08</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.113902188815746e-07</v>
+        <v>4.688711736702643e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.405661012288733e-07</v>
+        <v>4.673124642832891e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.407219790428298e-07</v>
+        <v>4.688476276604587e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.742999712056436e-07</v>
+        <v>4.666550926152763e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.404517492902815e-07</v>
+        <v>4.666550926152763e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.406683350269178e-07</v>
+        <v>4.683348022637328e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.407219721675709e-07</v>
+        <v>4.688711736702643e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.404517719228341e-07</v>
+        <v>4.661691712228962e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.407219721675709e-07</v>
+        <v>4.688711736702643e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.237270420106892e-07</v>
+        <v>4.688711736702643e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.407219721675709e-07</v>
+        <v>4.688711736702643e-08</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.287112654032407e-08</v>
+        <v>1.477595739278928e-07</v>
       </c>
       <c r="C8" t="n">
-        <v>1.664758663958905e-08</v>
+        <v>2.381696425210176e-07</v>
       </c>
       <c r="D8" t="n">
-        <v>2.563199562472072e-08</v>
+        <v>2.570237934152182e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>2.006893610044931e-08</v>
+        <v>2.132969771822801e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>2.006893610044931e-08</v>
+        <v>1.503884355723888e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>2.973065588545589e-08</v>
+        <v>2.382046570770217e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>1.92354463661655e-08</v>
+        <v>2.382582942177165e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>2.006893610044931e-08</v>
+        <v>2.379880939729381e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>2.262957446913045e-08</v>
+        <v>2.382760798225356e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>3.067405552453606e-08</v>
+        <v>1.460785137351099e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>2.217318614766833e-08</v>
+        <v>3.327917749530348e-07</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.113902188815747e-07</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1.405661012288733e-07</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.407219790428298e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.742999712056439e-07</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.404517492902818e-07</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.406683350269179e-07</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.407219721675709e-07</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.404517719228342e-07</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.407219721675709e-07</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.237270420106893e-07</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.407219721675709e-07</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.287112654032404e-08</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.664758663958912e-08</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.563199562472076e-08</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.006893610044933e-08</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2.006893610044933e-08</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.973065588545585e-08</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.923544636616547e-08</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.006893610044933e-08</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.262957446913056e-08</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3.067405552453581e-08</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.217318614766829e-08</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>2.316677956213494e-08</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1.707897708546273e-08</v>
-      </c>
-      <c r="D9" t="n">
-        <v>2.66550377323966e-08</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="B11" t="n">
+        <v>2.316677956213482e-08</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1.707897708546277e-08</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.665503773239667e-08</v>
+      </c>
+      <c r="E11" t="n">
         <v>2.086241549133841e-08</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F11" t="n">
         <v>2.086241549133841e-08</v>
       </c>
-      <c r="G9" t="n">
-        <v>3.057226657792532e-08</v>
-      </c>
-      <c r="H9" t="n">
-        <v>2.40577795539378e-08</v>
-      </c>
-      <c r="I9" t="n">
+      <c r="G11" t="n">
+        <v>3.057226657792536e-08</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.405777955393776e-08</v>
+      </c>
+      <c r="I11" t="n">
         <v>2.086241549133841e-08</v>
       </c>
-      <c r="J9" t="n">
-        <v>2.342343731337353e-08</v>
-      </c>
-      <c r="K9" t="n">
-        <v>3.099861568366518e-08</v>
-      </c>
-      <c r="L9" t="n">
-        <v>2.508241409201608e-08</v>
+      <c r="J11" t="n">
+        <v>2.342343731337359e-08</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.099861568366499e-08</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.508241409201602e-08</v>
       </c>
     </row>
   </sheetData>
@@ -4007,7 +4727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4075,321 +4795,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.033331019700189e-08</v>
+        <v>2.729823168055081e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.291604636419105e-07</v>
+        <v>1.770590472148797e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.578151131609172e-07</v>
+        <v>2.775596644409183e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.48205543095191e-07</v>
+        <v>2.185301196790618e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.48205543095191e-07</v>
+        <v>2.185301196790618e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.419827576831381e-07</v>
+        <v>3.187772587679963e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.66658721116259e-07</v>
+        <v>2.775061958803565e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.48205543095191e-07</v>
+        <v>2.185301196790618e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.706503336172445e-07</v>
+        <v>2.440305041853291e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.274476829623192e-07</v>
+        <v>3.185940145814004e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.53892746983525e-07</v>
+        <v>2.741080758517711e-08</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.037677108281535e-09</v>
+        <v>2.750307967365809e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>8.207045655983595e-09</v>
+        <v>1.773631862152602e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>9.037677108281535e-09</v>
+        <v>2.790831081444644e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>8.887319301276882e-09</v>
+        <v>2.192563751811102e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>8.887319301276882e-09</v>
+        <v>2.192563751811102e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>8.984865587071464e-09</v>
+        <v>3.211670338495241e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>9.037677108281535e-09</v>
+        <v>2.790831081444644e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>8.77274253685359e-09</v>
+        <v>2.192563751811102e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>9.037677108281535e-09</v>
+        <v>2.449383848343433e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>9.037677108281535e-09</v>
+        <v>3.211332753397266e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>9.037677108281535e-09</v>
+        <v>2.757956244076297e-08</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.655298821689406e-08</v>
+        <v>6.033331019700193e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>2.231665864230038e-08</v>
+        <v>1.291604636419102e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>2.261807546420181e-08</v>
+        <v>1.578151131609171e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>2.125229382559151e-08</v>
+        <v>1.482055430951908e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>2.236288611142947e-08</v>
+        <v>1.482055430951908e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>2.252984613798109e-08</v>
+        <v>1.419827576831386e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>3.813338342295986e-08</v>
+        <v>1.666587211162591e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>3.628805364546607e-08</v>
+        <v>1.482055430951908e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>2.341168290311618e-08</v>
+        <v>1.706503336172442e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>2.256935095675659e-08</v>
+        <v>1.274476829623189e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>2.259314767481474e-08</v>
+        <v>1.53892746983525e-07</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.532271005381586e-08</v>
+        <v>9.037677108281725e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>4.51680682167441e-08</v>
+        <v>8.207045655983635e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>4.532048039708095e-08</v>
+        <v>9.037677108281725e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>4.512429015255766e-08</v>
+        <v>8.887319301276889e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>4.512429015255766e-08</v>
+        <v>8.887319301276882e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>4.526989853260581e-08</v>
+        <v>8.984865587071386e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>4.532271005381586e-08</v>
+        <v>9.037677108281725e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>4.505777548238798e-08</v>
+        <v>8.772742536853503e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>4.532271005381586e-08</v>
+        <v>9.037677108281684e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>4.532271005381586e-08</v>
+        <v>9.037677108281725e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>4.532271005381586e-08</v>
+        <v>9.037677108281725e-09</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.409389165611378e-07</v>
+        <v>3.6552988216894e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>2.269913005625035e-07</v>
+        <v>2.231665864230086e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>2.449209138913143e-07</v>
+        <v>2.261807546420195e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>2.033175293774787e-07</v>
+        <v>2.12522938255915e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.434449792771513e-07</v>
+        <v>2.236288611142957e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>2.27009794347512e-07</v>
+        <v>2.252984613798121e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.270626058688423e-07</v>
+        <v>3.813338342295964e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>2.267976712972938e-07</v>
+        <v>3.628805364546609e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>2.270795316536861e-07</v>
+        <v>2.341168290311614e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.393391248150447e-07</v>
+        <v>2.256935095675776e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>3.170260009083445e-07</v>
+        <v>2.259314767481483e-08</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.003951023793659e-07</v>
+        <v>4.532271005381571e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.265134949651131e-07</v>
+        <v>4.516806821674408e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.266681468758773e-07</v>
+        <v>4.532048039708093e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.567217145354631e-07</v>
+        <v>4.512429015255761e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.264031850729008e-07</v>
+        <v>4.512429015255761e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.266153252809748e-07</v>
+        <v>4.526989853260576e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.266681368021849e-07</v>
+        <v>4.532271005381571e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.264032022307569e-07</v>
+        <v>4.505777548238788e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.266681368021849e-07</v>
+        <v>4.532271005381571e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>9.35856941329162e-08</v>
+        <v>4.532271005381571e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.266681368021849e-07</v>
+        <v>4.532271005381571e-08</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.654847493938211e-08</v>
+        <v>1.409389165611375e-07</v>
       </c>
       <c r="C8" t="n">
-        <v>1.665370195708176e-08</v>
+        <v>2.269913005625033e-07</v>
       </c>
       <c r="D8" t="n">
-        <v>2.606525858817161e-08</v>
+        <v>2.449209138913143e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>2.033729599802989e-08</v>
+        <v>2.033175293774785e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>2.033729599802989e-08</v>
+        <v>1.434449792771513e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>3.070625352187139e-08</v>
+        <v>2.270097943475119e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>2.621222898572612e-08</v>
+        <v>2.27062605868842e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>2.033729599802989e-08</v>
+        <v>2.267976712972937e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>2.249776575451139e-08</v>
+        <v>2.270795316536859e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>3.102012155249059e-08</v>
+        <v>1.393391248150446e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>2.621250746000012e-08</v>
+        <v>3.170260009083449e-07</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.003951023793656e-07</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1.26513494965113e-07</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.266681468758772e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.567217145354627e-07</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.264031850729007e-07</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.266153252809748e-07</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.26668136802185e-07</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.26403202230757e-07</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.26668136802185e-07</v>
+      </c>
+      <c r="K9" t="n">
+        <v>9.358569413291606e-08</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.26668136802185e-07</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.654847493938214e-08</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.665370195708175e-08</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.606525858817156e-08</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.033729599802987e-08</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2.033729599802987e-08</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3.070625352187131e-08</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.621222898572611e-08</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.033729599802987e-08</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.24977657545114e-08</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3.102012155249055e-08</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.621250746000016e-08</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>2.686388348431067e-08</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1.721331068907124e-08</v>
-      </c>
-      <c r="D9" t="n">
-        <v>2.691737180767785e-08</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="B11" t="n">
+        <v>2.686388348431047e-08</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1.721331068907122e-08</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.691737180767781e-08</v>
+      </c>
+      <c r="E11" t="n">
         <v>2.113031151452517e-08</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F11" t="n">
         <v>2.113031151452517e-08</v>
       </c>
-      <c r="G9" t="n">
-        <v>3.123596669426083e-08</v>
-      </c>
-      <c r="H9" t="n">
-        <v>2.697889695087578e-08</v>
-      </c>
-      <c r="I9" t="n">
+      <c r="G11" t="n">
+        <v>3.123596669426074e-08</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.697889695087572e-08</v>
+      </c>
+      <c r="I11" t="n">
         <v>2.113031151452517e-08</v>
       </c>
-      <c r="J9" t="n">
-        <v>2.34948309657666e-08</v>
-      </c>
-      <c r="K9" t="n">
-        <v>3.136198925272492e-08</v>
-      </c>
-      <c r="L9" t="n">
-        <v>2.678879321238431e-08</v>
+      <c r="J11" t="n">
+        <v>2.349483096576658e-08</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.136198925272485e-08</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.678879321238419e-08</v>
       </c>
     </row>
   </sheetData>
@@ -4403,7 +5203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4471,321 +5271,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.111903997314087e-08</v>
+        <v>3.745171583406701e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.328120934059798e-07</v>
+        <v>1.795328863215304e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.563187940029602e-07</v>
+        <v>2.798600392961321e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.442901161717173e-07</v>
+        <v>2.202973709718858e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.442901161717173e-07</v>
+        <v>2.202973709718858e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.427152915242504e-07</v>
+        <v>3.294019922484796e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.667322031765972e-07</v>
+        <v>2.798250106071256e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.442901161717173e-07</v>
+        <v>2.202973709718858e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.728738076666114e-07</v>
+        <v>2.477711340391909e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.274596436900414e-07</v>
+        <v>3.194788150014101e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.566222838712928e-07</v>
+        <v>2.764104726597353e-08</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.461285196389932e-09</v>
+        <v>3.78164873375518e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>8.619841160666375e-09</v>
+        <v>1.798279274306696e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>9.461285196389932e-09</v>
+        <v>2.814315862305882e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>9.310240514965693e-09</v>
+        <v>2.21091956555444e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>9.310240514965695e-09</v>
+        <v>2.21091956555444e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>9.407713017124563e-09</v>
+        <v>3.319462059969493e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>9.461285196389932e-09</v>
+        <v>2.814315862305882e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>9.191479615234695e-09</v>
+        <v>2.21091956555444e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>9.461285196389932e-09</v>
+        <v>2.48707040436836e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>9.461285196389932e-09</v>
+        <v>3.220258133478948e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>9.461285196389932e-09</v>
+        <v>2.780997861481037e-08</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.7205332105931e-08</v>
+        <v>6.111903997314083e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>2.271033342177409e-08</v>
+        <v>1.328120934059797e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>2.300109589607655e-08</v>
+        <v>1.563187940029605e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>2.161903234254629e-08</v>
+        <v>1.442901161717172e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>2.275052394132246e-08</v>
+        <v>1.442901161717172e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>2.292281743977269e-08</v>
+        <v>1.42715291524253e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>3.903877344542247e-08</v>
+        <v>1.667322031765972e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>2.270658403788287e-08</v>
+        <v>1.442901161717172e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>3.763724380268092e-08</v>
+        <v>1.728738076666116e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>2.295971217182304e-08</v>
+        <v>1.274596436900414e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>2.299142276543776e-08</v>
+        <v>1.566222838712929e-07</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.612863248835889e-08</v>
+        <v>9.461285196389892e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>4.597362658890308e-08</v>
+        <v>8.619841160666408e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>4.612639897726406e-08</v>
+        <v>9.461285196389892e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>4.593058664229183e-08</v>
+        <v>9.310240514965667e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>4.593058664229183e-08</v>
+        <v>9.310240514965667e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>4.607506030909355e-08</v>
+        <v>9.407713017124493e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>4.612863248835889e-08</v>
+        <v>9.461285196389892e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>4.585882690720364e-08</v>
+        <v>9.191479615234621e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>4.612863248835889e-08</v>
+        <v>9.461285196389892e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>4.612863248835889e-08</v>
+        <v>9.461285196389892e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>4.612863248835889e-08</v>
+        <v>9.461285196389892e-09</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.419948290111217e-07</v>
+        <v>3.720533210593107e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>2.285977087201307e-07</v>
+        <v>2.271033342177397e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>2.46635700683026e-07</v>
+        <v>2.300109589607654e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>2.047696213976727e-07</v>
+        <v>2.161903234254623e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.4451645032282e-07</v>
+        <v>2.27505239413225e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>2.286106626150997e-07</v>
+        <v>2.29228174397727e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.286642347945652e-07</v>
+        <v>3.903877344542257e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>2.283944292132094e-07</v>
+        <v>2.27065840378829e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>2.286812678269318e-07</v>
+        <v>3.763724380268092e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.403849003013544e-07</v>
+        <v>2.295971217182301e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>3.191976763239823e-07</v>
+        <v>2.299142276543786e-08</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.674566433430543e-08</v>
+        <v>4.612863248835887e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.217999292053359e-07</v>
+        <v>4.597362658890308e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.219549453008707e-07</v>
+        <v>4.612639897726406e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.50776081215151e-07</v>
+        <v>4.593058664229187e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.216851123462065e-07</v>
+        <v>4.593058664229187e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.219013629255262e-07</v>
+        <v>4.60750603090936e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.219549351047917e-07</v>
+        <v>4.612863248835887e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.216851295236363e-07</v>
+        <v>4.585882690720372e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.219549351047917e-07</v>
+        <v>4.612863248835887e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.067559905747608e-07</v>
+        <v>4.612863248835887e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.219549351047917e-07</v>
+        <v>4.612863248835887e-08</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.684815421686175e-08</v>
+        <v>1.419948290111217e-07</v>
       </c>
       <c r="C8" t="n">
-        <v>1.68187371791069e-08</v>
+        <v>2.285977087201308e-07</v>
       </c>
       <c r="D8" t="n">
-        <v>2.634205235837124e-08</v>
+        <v>2.466357006830259e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>2.062068181074963e-08</v>
+        <v>2.04769621397673e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>2.062068181074963e-08</v>
+        <v>1.445164503228201e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>3.177208053096554e-08</v>
+        <v>2.286106626150997e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>2.64503308391509e-08</v>
+        <v>2.286642347945655e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>2.062068181074963e-08</v>
+        <v>2.283944292132097e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>2.282830608994457e-08</v>
+        <v>2.28681267826932e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>3.111450015427327e-08</v>
+        <v>1.403849003013546e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>2.639010104952506e-08</v>
+        <v>3.191976763239827e-07</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>9.67456643343057e-08</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1.217999292053361e-07</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.219549453008708e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.507760812151517e-07</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.216851123462068e-07</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.219013629255265e-07</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.219549351047919e-07</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.216851295236368e-07</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.219549351047919e-07</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.06755990574761e-07</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.219549351047919e-07</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>3.684815421686176e-08</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.681873717910693e-08</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.63420523583713e-08</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.062068181074967e-08</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2.062068181074967e-08</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3.177208053096556e-08</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.645033083915088e-08</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.062068181074967e-08</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.28283060899446e-08</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3.111450015427319e-08</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.639010104952513e-08</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>3.701112117825848e-08</v>
-      </c>
-      <c r="C9" t="n">
+      <c r="B11" t="n">
+        <v>3.701112117825851e-08</v>
+      </c>
+      <c r="C11" t="n">
         <v>1.742363964092622e-08</v>
       </c>
-      <c r="D9" t="n">
-        <v>2.716649483939522e-08</v>
-      </c>
-      <c r="E9" t="n">
-        <v>2.135245855419475e-08</v>
-      </c>
-      <c r="F9" t="n">
-        <v>2.135245855419475e-08</v>
-      </c>
-      <c r="G9" t="n">
+      <c r="D11" t="n">
+        <v>2.716649483939528e-08</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2.135245855419479e-08</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.135245855419479e-08</v>
+      </c>
+      <c r="G11" t="n">
         <v>3.22929389602099e-08</v>
       </c>
-      <c r="H9" t="n">
-        <v>2.721225902431233e-08</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2.135245855419475e-08</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2.384781582623172e-08</v>
-      </c>
-      <c r="K9" t="n">
-        <v>3.145280109549695e-08</v>
-      </c>
-      <c r="L9" t="n">
-        <v>2.699499844888739e-08</v>
+      <c r="H11" t="n">
+        <v>2.721225902431239e-08</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.135245855419479e-08</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.384781582623175e-08</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.145280109549709e-08</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.69949984488874e-08</v>
       </c>
     </row>
   </sheetData>
@@ -4799,7 +5679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4867,320 +5747,400 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.23422934953711e-07</v>
+        <v>3.063253495170887e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>2.134811764927818e-07</v>
+        <v>2.335883475025176e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>5.892763430680225e-07</v>
+        <v>3.080790300465038e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>2.134811764927818e-07</v>
+        <v>2.335883475025176e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>2.134811764927818e-07</v>
+        <v>2.335883475025176e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>4.435196110098138e-07</v>
+        <v>3.057202820268812e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.217273930828024e-06</v>
+        <v>3.137059431217047e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>2.134811764927818e-07</v>
+        <v>2.335883475025176e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>3.200750541785509e-07</v>
+        <v>3.049625127836087e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>2.838941568459405e-07</v>
+        <v>3.04705663216543e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>2.965736302165963e-07</v>
+        <v>3.04603165547369e-08</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.006222992302515e-08</v>
+        <v>3.053570322170891e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>9.353377117392596e-09</v>
+        <v>2.339723389444794e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.006222992302515e-08</v>
+        <v>3.053570322170891e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>9.497341697890504e-09</v>
+        <v>2.339723389444794e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>9.497341697890504e-09</v>
+        <v>2.339723389444794e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.000166908947242e-08</v>
+        <v>3.046908981570971e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.006222992302515e-08</v>
+        <v>3.053570322170891e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>9.747693865255191e-09</v>
+        <v>2.339723389444794e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.006222992302515e-08</v>
+        <v>3.053570322170891e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.006222992302515e-08</v>
+        <v>3.053570322170891e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.006222992302515e-08</v>
+        <v>3.053570322170891e-08</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.56424932933791e-08</v>
+        <v>4.234229349537083e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>2.494232793746487e-08</v>
+        <v>2.134811764927825e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>2.61294041368956e-08</v>
+        <v>5.892763430680232e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>2.377891105092295e-08</v>
+        <v>2.134811764927825e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>2.531739660952793e-08</v>
+        <v>2.134811764927825e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>2.558193245982638e-08</v>
+        <v>4.435196110098134e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>4.288751831035016e-08</v>
+        <v>1.217273930828025e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>4.177494715450879e-08</v>
+        <v>2.134811764927825e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>2.659259097418005e-08</v>
+        <v>3.200750541785515e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>2.550777789690232e-08</v>
+        <v>2.838941568459405e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>2.604747631641973e-08</v>
+        <v>2.965736302165954e-07</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.898922576786779e-08</v>
+        <v>1.006222992302531e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>4.86746897100979e-08</v>
+        <v>9.353377117392565e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>4.898669201163733e-08</v>
+        <v>1.006222992302531e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>4.866550490827688e-08</v>
+        <v>9.497341697890447e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>4.866550490827688e-08</v>
+        <v>9.497341697890453e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>4.892866493431511e-08</v>
+        <v>1.000166908947259e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>4.898922576786779e-08</v>
+        <v>1.006222992302531e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>4.86746897100979e-08</v>
+        <v>9.74769386525526e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>4.898922576786779e-08</v>
+        <v>1.006222992302531e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>4.898922576786779e-08</v>
+        <v>1.006222992302531e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>4.898922576786779e-08</v>
+        <v>1.006222992302531e-08</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.518287846286137e-07</v>
+        <v>2.564249329337908e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>2.439234363063791e-07</v>
+        <v>2.494232793746439e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>2.633843964645996e-07</v>
+        <v>2.612940413689557e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>2.186517643805867e-07</v>
+        <v>2.377891105092292e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.544391097829537e-07</v>
+        <v>2.531739660952786e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>2.441648030200186e-07</v>
+        <v>2.558193245982639e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.442253638535722e-07</v>
+        <v>4.288751831035016e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>2.439108277958011e-07</v>
+        <v>4.177494715450862e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>2.442435224421888e-07</v>
+        <v>2.659259097418005e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.501124707318119e-07</v>
+        <v>2.550777789690241e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>3.407413169428967e-07</v>
+        <v>2.60474763164197e-08</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.203808919688882e-07</v>
+        <v>4.898922576786776e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.515852170297744e-07</v>
+        <v>4.867468971009783e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.518997573907557e-07</v>
+        <v>4.898669201163724e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.879572764225724e-07</v>
+        <v>4.866550490827684e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.515851834935034e-07</v>
+        <v>4.866550490827684e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.518391922539916e-07</v>
+        <v>4.892866493431506e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.518997530875445e-07</v>
+        <v>4.898922576786776e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.515852170297744e-07</v>
+        <v>4.867468971009783e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.518997530875445e-07</v>
+        <v>4.898922576786776e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.336376029811918e-07</v>
+        <v>4.898922576786776e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.518997530875445e-07</v>
+        <v>4.898922576786776e-08</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.268894242352144e-08</v>
+        <v>1.518287846286136e-07</v>
       </c>
       <c r="C8" t="n">
-        <v>2.065423255746461e-08</v>
+        <v>2.439234363063784e-07</v>
       </c>
       <c r="D8" t="n">
-        <v>1.901969431467376e-08</v>
+        <v>2.633843964645994e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>2.065423255746461e-08</v>
+        <v>2.186517643805864e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>2.065423255746461e-08</v>
+        <v>1.544391097829535e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>2.25343611866552e-08</v>
+        <v>2.441648030200186e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>7.668146522624798e-09</v>
+        <v>2.44225363853572e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>2.065423255746461e-08</v>
+        <v>2.439108277958008e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>2.558619503508231e-08</v>
+        <v>2.442435224421887e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>2.608893109993472e-08</v>
+        <v>1.501124707318119e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>2.636615787979196e-08</v>
+        <v>3.407413169428956e-07</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.203808919688882e-07</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1.515852170297743e-07</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.518997573907556e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.879572764225724e-07</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.515851834935032e-07</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.518391922539916e-07</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.518997530875443e-07</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.515852170297743e-07</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.518997530875443e-07</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.336376029811915e-07</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.518997530875443e-07</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.268894242352146e-08</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2.065423255746461e-08</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.901969431467375e-08</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.065423255746461e-08</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2.065423255746461e-08</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.253436118665521e-08</v>
+      </c>
+      <c r="H10" t="n">
+        <v>7.668146522624778e-09</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.065423255746461e-08</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.558619503508235e-08</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.608893109993473e-08</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.636615787979194e-08</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>2.706223378239059e-08</v>
-      </c>
-      <c r="C9" t="n">
+      <c r="B11" t="n">
+        <v>2.706223378239061e-08</v>
+      </c>
+      <c r="C11" t="n">
         <v>2.211076040049775e-08</v>
       </c>
-      <c r="D9" t="n">
-        <v>2.556808225260653e-08</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="D11" t="n">
+        <v>2.556808225260651e-08</v>
+      </c>
+      <c r="E11" t="n">
         <v>2.211076040049775e-08</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F11" t="n">
         <v>2.211076040049775e-08</v>
       </c>
-      <c r="G9" t="n">
-        <v>2.696170138998855e-08</v>
-      </c>
-      <c r="H9" t="n">
-        <v>2.096578313950792e-08</v>
-      </c>
-      <c r="I9" t="n">
+      <c r="G11" t="n">
+        <v>2.696170138998852e-08</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.09657831395079e-08</v>
+      </c>
+      <c r="I11" t="n">
         <v>2.211076040049775e-08</v>
       </c>
-      <c r="J9" t="n">
-        <v>2.824420928029909e-08</v>
-      </c>
-      <c r="K9" t="n">
-        <v>2.84472708352251e-08</v>
-      </c>
-      <c r="L9" t="n">
+      <c r="J11" t="n">
+        <v>2.824420928029907e-08</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.844727083522511e-08</v>
+      </c>
+      <c r="L11" t="n">
         <v>1.854182937365874e-08</v>
       </c>
     </row>
@@ -5195,7 +6155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5263,321 +6223,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.456017696048272e-07</v>
+        <v>3.072733155142396e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>2.377283877311912e-07</v>
+        <v>2.37000978073179e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>5.180537247560517e-07</v>
+        <v>3.093537738571176e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>2.377283877311912e-07</v>
+        <v>2.37000978073179e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>2.377283877311912e-07</v>
+        <v>2.37000978073179e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>4.046502396951017e-07</v>
+        <v>3.073209851733612e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.007982990251425e-06</v>
+        <v>3.139238857775242e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>2.377283877311912e-07</v>
+        <v>2.37000978073179e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>2.56724306946937e-07</v>
+        <v>3.060774304965869e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>2.635844236448981e-07</v>
+        <v>3.063469465850146e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>3.11820359331616e-07</v>
+        <v>3.065720089666682e-08</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.010031958776197e-08</v>
+        <v>3.069612925828493e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>9.482350927300359e-09</v>
+        <v>2.369335617606798e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.010031958776197e-08</v>
+        <v>3.069612925828493e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>9.613220854838621e-09</v>
+        <v>2.369335617606798e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>9.613220854838629e-09</v>
+        <v>2.369335617606798e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.004174299978073e-08</v>
+        <v>3.063829557788796e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.010031958776197e-08</v>
+        <v>3.069612925828493e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>9.7984713674834e-09</v>
+        <v>2.369335617606798e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.010031958776197e-08</v>
+        <v>3.069612925828493e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.010031958776197e-08</v>
+        <v>3.069612925828493e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.010031958776197e-08</v>
+        <v>3.069612925828493e-08</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.456351427300911e-08</v>
+        <v>3.456017696048279e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>2.399580223154448e-08</v>
+        <v>2.377283877311917e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>2.49635748242992e-08</v>
+        <v>5.180537247560524e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>2.290559066967144e-08</v>
+        <v>2.377283877311917e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>2.427714832756182e-08</v>
+        <v>2.377283877311917e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>2.450493768502784e-08</v>
+        <v>4.046502396951014e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>4.065013416896957e-08</v>
+        <v>1.007982990251426e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>3.963609292901373e-08</v>
+        <v>2.377283877311917e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>2.544187802584856e-08</v>
+        <v>2.567243069469368e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>2.444616244805353e-08</v>
+        <v>2.63584423644898e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>2.491526898142632e-08</v>
+        <v>3.118203593316153e-07</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.666352554911325e-08</v>
+        <v>1.010031958776197e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>4.636167732883456e-08</v>
+        <v>9.48235092730034e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>4.666115599700557e-08</v>
+        <v>1.010031958776196e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>4.635728855126732e-08</v>
+        <v>9.613220854838596e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>4.635728855126731e-08</v>
+        <v>9.613220854838671e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>4.660494896113191e-08</v>
+        <v>1.004174299978066e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>4.666352554911322e-08</v>
+        <v>1.010031958776196e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>4.636167732883456e-08</v>
+        <v>9.798471367483301e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>4.666352554911322e-08</v>
+        <v>1.010031958776196e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>4.666352554911322e-08</v>
+        <v>1.010031958776196e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>4.666352554911322e-08</v>
+        <v>1.010031958776196e-08</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.424979748110162e-07</v>
+        <v>2.456351427300911e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>2.285827347778432e-07</v>
+        <v>2.399580223154446e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>2.467783346201624e-07</v>
+        <v>2.496357482429915e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>2.049587657470521e-07</v>
+        <v>2.290559066967144e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.44932743321127e-07</v>
+        <v>2.427714832756181e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>2.288102079755725e-07</v>
+        <v>2.450493768502788e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.288687845635554e-07</v>
+        <v>4.065013416896975e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>2.285669363432748e-07</v>
+        <v>3.963609292901383e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>2.288857589147855e-07</v>
+        <v>2.544187802584859e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.408935926758921e-07</v>
+        <v>2.444616244805356e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>3.190903175713328e-07</v>
+        <v>2.491526898142635e-08</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.071177603570352e-07</v>
+        <v>4.666352554911321e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.346245311617743e-07</v>
+        <v>4.636167732883464e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.349263846251034e-07</v>
+        <v>4.666115599700569e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.667150560839707e-07</v>
+        <v>4.635728855126746e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.346245019343206e-07</v>
+        <v>4.635728855126747e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.348678027940716e-07</v>
+        <v>4.660494896113201e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.34926379382053e-07</v>
+        <v>4.666352554911323e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.346245311617743e-07</v>
+        <v>4.636167732883464e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.34926379382053e-07</v>
+        <v>4.666352554911323e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.188139585112919e-07</v>
+        <v>4.666352554911323e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.34926379382053e-07</v>
+        <v>4.666352554911323e-08</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.418689427310599e-08</v>
+        <v>1.424979748110162e-07</v>
       </c>
       <c r="C8" t="n">
-        <v>1.993205436201288e-08</v>
+        <v>2.285827347778433e-07</v>
       </c>
       <c r="D8" t="n">
-        <v>1.983235157702756e-08</v>
+        <v>2.467783346201625e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>1.993205436201288e-08</v>
+        <v>2.04958765747052e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>1.993205436201288e-08</v>
+        <v>1.449327433211271e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>2.285620174243451e-08</v>
+        <v>2.288102079755724e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>1.06413500749108e-08</v>
+        <v>2.288687845635554e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>1.993205436201288e-08</v>
+        <v>2.285669363432748e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>2.672637788467304e-08</v>
+        <v>2.288857589147853e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>2.613380618544362e-08</v>
+        <v>1.40893592675892e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>2.573669095934903e-08</v>
+        <v>3.19090317571333e-07</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.071177603570351e-07</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1.346245311617746e-07</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.349263846251038e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.66715056083971e-07</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.346245019343208e-07</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.348678027940718e-07</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.34926379382053e-07</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.346245311617746e-07</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.34926379382053e-07</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.188139585112919e-07</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.34926379382053e-07</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.418689427310597e-08</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.99320543620129e-08</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.983235157702756e-08</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.99320543620129e-08</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.99320543620129e-08</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.285620174243452e-08</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.064135007491084e-08</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.99320543620129e-08</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.672637788467304e-08</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.613380618544363e-08</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.573669095934905e-08</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>2.776560888946647e-08</v>
-      </c>
-      <c r="C9" t="n">
-        <v>2.198869349536518e-08</v>
-      </c>
-      <c r="D9" t="n">
-        <v>2.599232391993442e-08</v>
-      </c>
-      <c r="E9" t="n">
-        <v>2.198869349536518e-08</v>
-      </c>
-      <c r="F9" t="n">
-        <v>2.198869349536518e-08</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2.719122102214322e-08</v>
-      </c>
-      <c r="H9" t="n">
-        <v>2.226740013852803e-08</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2.198869349536518e-08</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2.88014935238183e-08</v>
-      </c>
-      <c r="K9" t="n">
-        <v>2.855882312109774e-08</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.951031120707235e-08</v>
+      <c r="B11" t="n">
+        <v>2.776560888946648e-08</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2.198869349536519e-08</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.599232391993435e-08</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2.198869349536519e-08</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.198869349536519e-08</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.719122102214326e-08</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.226740013852804e-08</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.198869349536519e-08</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.880149352381828e-08</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.855882312109769e-08</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.951031120707234e-08</v>
       </c>
     </row>
   </sheetData>
@@ -5591,7 +6631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5659,321 +6699,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.067472168625148e-07</v>
+        <v>3.08044246752897e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>3.170870479399729e-07</v>
+        <v>2.421092641164666e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>4.58864481236002e-07</v>
+        <v>3.099339434397326e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>3.170870479399729e-07</v>
+        <v>2.421092641164666e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>3.170870479399729e-07</v>
+        <v>2.421092641164666e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>3.719392482129716e-07</v>
+        <v>3.083847940245744e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>8.351228759751878e-07</v>
+        <v>3.13574104337073e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>3.170870479399729e-07</v>
+        <v>2.421092641164666e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>2.570783313156016e-07</v>
+        <v>3.072647254556524e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>2.495593001563706e-07</v>
+        <v>3.074147159134404e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>2.734156281480627e-07</v>
+        <v>3.17161968338111e-08</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.048614390954912e-08</v>
+        <v>3.081630341325447e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.001203138536644e-08</v>
+        <v>2.410683371109527e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.048614390954912e-08</v>
+        <v>3.081630341325447e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.013686987167397e-08</v>
+        <v>2.410683371109527e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.013686987167397e-08</v>
+        <v>2.410683371109527e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.043208629549209e-08</v>
+        <v>3.077954187679957e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.048614390954912e-08</v>
+        <v>3.081630341325447e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.021317715086936e-08</v>
+        <v>2.410683371109527e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.048614390954912e-08</v>
+        <v>3.081630341325447e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.048614390954912e-08</v>
+        <v>3.081630341325447e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.048614390954912e-08</v>
+        <v>3.081630341325447e-08</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.499673678565846e-08</v>
+        <v>3.067472168625146e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>2.467640523250271e-08</v>
+        <v>3.170870479399731e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>2.531097606128908e-08</v>
+        <v>4.588644812360019e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>2.357405212222759e-08</v>
+        <v>3.170870479399731e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>2.479589740876501e-08</v>
+        <v>3.170870479399731e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>4.023980937244281e-08</v>
+        <v>3.719392482129687e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>4.098367794987967e-08</v>
+        <v>8.351228759751877e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>2.472377002697872e-08</v>
+        <v>3.170870479399731e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>4.042225173434277e-08</v>
+        <v>2.570783313156016e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>2.48768401252407e-08</v>
+        <v>2.495593001563706e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>2.532053577537344e-08</v>
+        <v>2.734156281480632e-07</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.722460243562772e-08</v>
+        <v>1.04861439095491e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>4.695163567694785e-08</v>
+        <v>1.001203138536641e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>4.722221981113098e-08</v>
+        <v>1.04861439095491e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>4.695706305545498e-08</v>
+        <v>1.013686987167391e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>4.695706305545498e-08</v>
+        <v>1.013686987167391e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>4.717054482157066e-08</v>
+        <v>1.04320862954921e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>4.722460243562765e-08</v>
+        <v>1.04861439095491e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>4.695163567694785e-08</v>
+        <v>1.021317715086928e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>4.722460243562765e-08</v>
+        <v>1.04861439095491e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>4.722460243562765e-08</v>
+        <v>1.04861439095491e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>4.722460243562765e-08</v>
+        <v>1.04861439095491e-08</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.429873586583607e-07</v>
+        <v>2.499673678565851e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>2.292198429524629e-07</v>
+        <v>2.467640523250214e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>2.473998249239603e-07</v>
+        <v>2.531097606128911e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>2.055649452005497e-07</v>
+        <v>2.357405212222771e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.454603406215717e-07</v>
+        <v>2.479589740876503e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>2.294135287317145e-07</v>
+        <v>4.023980937244285e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.294675863457759e-07</v>
+        <v>4.098367794987955e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>2.291946195870917e-07</v>
+        <v>2.472377002697862e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>2.294845822006904e-07</v>
+        <v>4.04222517343428e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.413809440289256e-07</v>
+        <v>2.487684012524073e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>3.198034155358425e-07</v>
+        <v>2.532053577537349e-08</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.027989715912187e-07</v>
+        <v>4.722460243562781e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.290525234764255e-07</v>
+        <v>4.695163567694793e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.293254958587431e-07</v>
+        <v>4.722221981113104e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.596635351479055e-07</v>
+        <v>4.6957063055455e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.290524966970894e-07</v>
+        <v>4.6957063055455e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.292714326210479e-07</v>
+        <v>4.717054482157076e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.293254902351051e-07</v>
+        <v>4.72246024356278e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.290525234764255e-07</v>
+        <v>4.695163567694793e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.293254902351051e-07</v>
+        <v>4.72246024356278e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.139559235204418e-07</v>
+        <v>4.72246024356278e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.293254902351051e-07</v>
+        <v>4.72246024356278e-08</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.517954666095081e-08</v>
+        <v>1.429873586583611e-07</v>
       </c>
       <c r="C8" t="n">
-        <v>1.820283585250844e-08</v>
+        <v>2.292198429524627e-07</v>
       </c>
       <c r="D8" t="n">
-        <v>2.122413629126479e-08</v>
+        <v>2.473998249239605e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>1.820283585250844e-08</v>
+        <v>2.055649452005497e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>1.820283585250844e-08</v>
+        <v>1.454603406215718e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>2.36942420558074e-08</v>
+        <v>2.294135287317145e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>1.39213723466695e-08</v>
+        <v>2.29467586345776e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>1.820283585250844e-08</v>
+        <v>2.291946195870917e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>2.684632627417932e-08</v>
+        <v>2.294845822006905e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>2.650400361204832e-08</v>
+        <v>1.413809440289256e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>6.457609960761096e-09</v>
+        <v>3.19803415535843e-07</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.027989715912189e-07</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1.290525234764254e-07</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.29325495858743e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.596635351479053e-07</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.290524966970891e-07</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.292714326210482e-07</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.293254902351052e-07</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.290525234764254e-07</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.293254902351052e-07</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.13955923520442e-07</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.293254902351052e-07</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.517954666095077e-08</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.820283585250844e-08</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.122413629126479e-08</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.820283585250844e-08</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.820283585250844e-08</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.369424205580736e-08</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.392137234666946e-08</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.820283585250844e-08</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.684632627417932e-08</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.650400361204834e-08</v>
+      </c>
+      <c r="L10" t="n">
+        <v>6.457609960761087e-09</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>2.823968238971356e-08</v>
-      </c>
-      <c r="C9" t="n">
+      <c r="B11" t="n">
+        <v>2.82396823897136e-08</v>
+      </c>
+      <c r="C11" t="n">
         <v>2.152458857106485e-08</v>
       </c>
-      <c r="D9" t="n">
-        <v>2.662892773504509e-08</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="D11" t="n">
+        <v>2.66289277350451e-08</v>
+      </c>
+      <c r="E11" t="n">
         <v>2.152458857106485e-08</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F11" t="n">
         <v>2.152458857106485e-08</v>
       </c>
-      <c r="G9" t="n">
-        <v>2.761464540439524e-08</v>
-      </c>
-      <c r="H9" t="n">
-        <v>2.367016295746041e-08</v>
-      </c>
-      <c r="I9" t="n">
+      <c r="G11" t="n">
+        <v>2.761464540439518e-08</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.367016295746043e-08</v>
+      </c>
+      <c r="I11" t="n">
         <v>2.152458857106485e-08</v>
       </c>
-      <c r="J9" t="n">
-        <v>2.892012029571954e-08</v>
-      </c>
-      <c r="K9" t="n">
-        <v>2.877936143931114e-08</v>
-      </c>
-      <c r="L9" t="n">
-        <v>2.063291368637646e-08</v>
+      <c r="J11" t="n">
+        <v>2.892012029571959e-08</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.877936143931118e-08</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.063291368637652e-08</v>
       </c>
     </row>
   </sheetData>
@@ -5987,7 +7107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6055,321 +7175,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.62230943300037e-07</v>
+        <v>2.937906709153979e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.536353610965956e-07</v>
+        <v>2.248653488601046e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>2.514686582432598e-07</v>
+        <v>2.948026741184092e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.536353610965956e-07</v>
+        <v>2.248653488601046e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.536353610965956e-07</v>
+        <v>2.248653488601046e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>2.159674091740477e-07</v>
+        <v>2.939667685278737e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>4.497776642160711e-07</v>
+        <v>2.967604865010862e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.536353610965956e-07</v>
+        <v>2.248653488601046e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>2.486190790463592e-07</v>
+        <v>2.946536202213086e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.827648360721792e-07</v>
+        <v>2.940245722855477e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>4.517454878828088e-07</v>
+        <v>2.938261023843164e-08</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.323466214755608e-09</v>
+        <v>2.956904617594411e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>8.788476675583829e-09</v>
+        <v>2.258540696399947e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>9.323466214755608e-09</v>
+        <v>2.956904617594411e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>8.917732938237266e-09</v>
+        <v>2.258540696399947e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>8.917732938237291e-09</v>
+        <v>2.258540696399947e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>9.269001194073432e-09</v>
+        <v>2.953001218387458e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>9.323466214755608e-09</v>
+        <v>2.956904617594411e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>9.047780680622214e-09</v>
+        <v>2.258540696399947e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>9.323466214755608e-09</v>
+        <v>2.956904617594411e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>9.323466214755608e-09</v>
+        <v>2.956904617594411e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>9.323466214755608e-09</v>
+        <v>2.956904617594411e-08</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.924548920171611e-08</v>
+        <v>1.622309433000338e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>2.394313086241289e-08</v>
+        <v>1.536353610965953e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>3.951818021103788e-08</v>
+        <v>2.514686582432595e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>2.280141012952255e-08</v>
+        <v>1.536353610965953e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>2.410114409701222e-08</v>
+        <v>1.536353610965953e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>3.919102418103405e-08</v>
+        <v>2.159674091740483e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>2.446830635570314e-08</v>
+        <v>4.497776642160703e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>3.896980366758265e-08</v>
+        <v>1.536353610965953e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>3.936821151556471e-08</v>
+        <v>2.486190790463606e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>2.436028705801508e-08</v>
+        <v>1.827648360721785e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>2.445902709854768e-08</v>
+        <v>4.51745487882808e-07</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.716406049616563e-08</v>
+        <v>9.323466214755415e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>4.688837496203223e-08</v>
+        <v>8.788476675583852e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>4.716153262893039e-08</v>
+        <v>9.323466214755415e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>4.688660348781485e-08</v>
+        <v>8.917732938237329e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>4.688660348781485e-08</v>
+        <v>8.917732938237329e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>4.71095954754836e-08</v>
+        <v>9.269001194073395e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>4.716406049616563e-08</v>
+        <v>9.323466214755446e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>4.688837496203223e-08</v>
+        <v>9.047780680622041e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>4.716406049616563e-08</v>
+        <v>9.323466214755416e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>4.716406049616563e-08</v>
+        <v>9.323466214755415e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>4.716406049616563e-08</v>
+        <v>9.323466214755415e-09</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.490579415195519e-07</v>
+        <v>3.924548920171602e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>2.396942334202543e-07</v>
+        <v>2.394313086241261e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>2.587976907017574e-07</v>
+        <v>3.951818021103773e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>2.148331702972683e-07</v>
+        <v>2.280141012952253e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.516638616568856e-07</v>
+        <v>2.410114409701223e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>2.398960570025334e-07</v>
+        <v>3.919102418103396e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.39950522023216e-07</v>
+        <v>2.446830635570313e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>2.396748364890823e-07</v>
+        <v>3.896980366758259e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>2.399683850332959e-07</v>
+        <v>3.936821151556454e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.473695651711225e-07</v>
+        <v>2.436028705801505e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>3.34895422686107e-07</v>
+        <v>2.445902709854768e-08</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.138017051867591e-07</v>
+        <v>4.716406049616563e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.433370398923319e-07</v>
+        <v>4.688837496203222e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.436127330383928e-07</v>
+        <v>4.716153262893039e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.777383027674695e-07</v>
+        <v>4.68866034878148e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.433370164789113e-07</v>
+        <v>4.688660348781481e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.435582604057833e-07</v>
+        <v>4.710959547548362e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.436127254264655e-07</v>
+        <v>4.716406049616563e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.433370398923319e-07</v>
+        <v>4.688837496203222e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.436127254264655e-07</v>
+        <v>4.716406049616563e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.263401064242175e-07</v>
+        <v>4.716406049616563e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.436127254264655e-07</v>
+        <v>4.716406049616563e-08</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.793271916698292e-08</v>
+        <v>1.490579415195518e-07</v>
       </c>
       <c r="C8" t="n">
-        <v>2.128326367153278e-08</v>
+        <v>2.396942334202538e-07</v>
       </c>
       <c r="D8" t="n">
-        <v>2.581372232632235e-08</v>
+        <v>2.587976907017571e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>2.128326367153278e-08</v>
+        <v>2.14833170297268e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>2.128326367153278e-08</v>
+        <v>1.516638616568855e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>2.672106451209047e-08</v>
+        <v>2.398960570025333e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>2.186115018664582e-08</v>
+        <v>2.39950522023216e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>2.128326367153278e-08</v>
+        <v>2.396748364890819e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>2.615242397762133e-08</v>
+        <v>2.399683850332962e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>2.744498047267633e-08</v>
+        <v>1.473695651711226e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>2.240083565929803e-08</v>
+        <v>3.348954226861064e-07</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.13801705186759e-07</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1.433370398923318e-07</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.436127330383927e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.777383027674696e-07</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.433370164789112e-07</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.435582604057832e-07</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.436127254264652e-07</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.433370398923318e-07</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.436127254264652e-07</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.263401064242175e-07</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.436127254264652e-07</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.7932719166983e-08</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2.128326367153292e-08</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.581372232632241e-08</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.128326367153292e-08</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2.128326367153292e-08</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.672106451209055e-08</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.186115018664588e-08</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.128326367153292e-08</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.615242397762134e-08</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.744498047267645e-08</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.240083565929809e-08</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>2.863453308779764e-08</v>
-      </c>
-      <c r="C9" t="n">
-        <v>2.18940555382536e-08</v>
-      </c>
-      <c r="D9" t="n">
-        <v>2.777158309275593e-08</v>
-      </c>
-      <c r="E9" t="n">
-        <v>2.18940555382536e-08</v>
-      </c>
-      <c r="F9" t="n">
-        <v>2.18940555382536e-08</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2.811859671054048e-08</v>
-      </c>
-      <c r="H9" t="n">
-        <v>2.616893141137078e-08</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2.18940555382536e-08</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2.7910788033765e-08</v>
-      </c>
-      <c r="K9" t="n">
-        <v>2.843600056457212e-08</v>
-      </c>
-      <c r="L9" t="n">
-        <v>2.638696711453947e-08</v>
+      <c r="B11" t="n">
+        <v>2.86345330877977e-08</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2.189405553825372e-08</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.777158309275603e-08</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2.189405553825372e-08</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.189405553825372e-08</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.811859671054055e-08</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.616893141137086e-08</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.189405553825372e-08</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.791078803376508e-08</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.843600056457221e-08</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.638696711453957e-08</v>
       </c>
     </row>
   </sheetData>
@@ -6383,7 +7583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6451,321 +7651,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.451768665279844e-07</v>
+        <v>2.939068342096746e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.632680223391608e-07</v>
+        <v>2.263588520267493e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.695313867632641e-07</v>
+        <v>2.941116362024014e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.632680223391608e-07</v>
+        <v>2.263588520267493e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.632680223391608e-07</v>
+        <v>2.263588520267493e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.696305220799491e-07</v>
+        <v>2.938466220227896e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.723853286358808e-07</v>
+        <v>2.93952199871977e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.632680223391608e-07</v>
+        <v>2.263588520267493e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>2.061874046739627e-07</v>
+        <v>2.945414937981611e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.688227760595999e-07</v>
+        <v>2.941887463288782e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.553872987118484e-07</v>
+        <v>2.93861075124181e-08</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.225216720982303e-09</v>
+        <v>2.958799053159599e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>8.773509890047522e-09</v>
+        <v>2.271292707991411e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>9.225216720982303e-09</v>
+        <v>2.958799053159599e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>8.887109126597247e-09</v>
+        <v>2.271292707991411e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>8.887109126597278e-09</v>
+        <v>2.271292707991411e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>9.173037567394755e-09</v>
+        <v>2.955899841791899e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>9.225216720982303e-09</v>
+        <v>2.958799053159599e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>8.964141970570617e-09</v>
+        <v>2.271292707991411e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>9.225216720982303e-09</v>
+        <v>2.958799053159599e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>9.225216720982303e-09</v>
+        <v>2.958799053159599e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>9.225216720982303e-09</v>
+        <v>2.958799053159599e-08</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.682892452236311e-08</v>
+        <v>1.451768665279845e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>2.280615241584701e-08</v>
+        <v>1.632680223391606e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>2.312855967920788e-08</v>
+        <v>1.695313867632639e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>2.173947619704521e-08</v>
+        <v>1.632680223391606e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>2.287835388178926e-08</v>
+        <v>1.632680223391606e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>3.677674536877546e-08</v>
+        <v>1.696305220799485e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>3.73465316727773e-08</v>
+        <v>1.72385328635881e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>3.656784977195141e-08</v>
+        <v>1.632680223391606e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>2.394252215001484e-08</v>
+        <v>2.061874046739622e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>2.314503623688299e-08</v>
+        <v>1.688227760595999e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>2.311639964309359e-08</v>
+        <v>1.553872987118482e-07</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.46621845931504e-08</v>
+        <v>9.225216720982327e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>4.440110984273873e-08</v>
+        <v>8.773509890047509e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>4.465982485520352e-08</v>
+        <v>9.225216720982327e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>4.440122865233695e-08</v>
+        <v>8.887109126597237e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>4.440122865233695e-08</v>
+        <v>8.887109126597254e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>4.461000543956286e-08</v>
+        <v>9.173037567394748e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>4.46621845931504e-08</v>
+        <v>9.225216720982327e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>4.440110984273873e-08</v>
+        <v>8.96414197057058e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>4.46621845931504e-08</v>
+        <v>9.225216720982327e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>4.46621845931504e-08</v>
+        <v>9.225216720982327e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>4.46621845931504e-08</v>
+        <v>9.225216720982327e-09</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.394663485900728e-07</v>
+        <v>3.682892452236282e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>2.239980722806688e-07</v>
+        <v>2.280615241584681e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>2.418175992341245e-07</v>
+        <v>2.312855967920786e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>2.008106634668359e-07</v>
+        <v>2.173947619704519e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.418939260500837e-07</v>
+        <v>2.287835388178922e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>2.24187183391248e-07</v>
+        <v>3.677674536877534e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.24239362544835e-07</v>
+        <v>3.734653167277726e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>2.239782877944236e-07</v>
+        <v>3.656784977195123e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>2.24256022883831e-07</v>
+        <v>2.394252215001476e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.378916463321633e-07</v>
+        <v>2.314503623688297e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>3.127918642367058e-07</v>
+        <v>2.311639964309356e-08</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.006039159879083e-07</v>
+        <v>4.466218459315045e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.264929844524365e-07</v>
+        <v>4.440110984273872e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.26754068844109e-07</v>
+        <v>4.465982485520355e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.566696817155677e-07</v>
+        <v>4.440122865233687e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.264929666525901e-07</v>
+        <v>4.440122865233687e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.267018800492606e-07</v>
+        <v>4.461000543956282e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.267540592028481e-07</v>
+        <v>4.466218459315045e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.264929844524365e-07</v>
+        <v>4.440110984273872e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.267540592028481e-07</v>
+        <v>4.466218459315045e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.116025675796533e-07</v>
+        <v>4.466218459315045e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.267540592028481e-07</v>
+        <v>4.466218459315045e-08</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.809460113790822e-08</v>
+        <v>1.394663485900729e-07</v>
       </c>
       <c r="C8" t="n">
-        <v>2.091779426882776e-08</v>
+        <v>2.239980722806691e-07</v>
       </c>
       <c r="D8" t="n">
-        <v>2.76664915618546e-08</v>
+        <v>2.418175992341248e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>2.091779426882776e-08</v>
+        <v>2.008106634668359e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>2.091779426882776e-08</v>
+        <v>1.418939260500836e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>2.759458176301112e-08</v>
+        <v>2.241871833912481e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>2.803266448881333e-08</v>
+        <v>2.242393625448346e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>2.091779426882776e-08</v>
+        <v>2.239782877944233e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>2.678787404314349e-08</v>
+        <v>2.242560228838309e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>2.750618412753005e-08</v>
+        <v>1.378916463321634e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>2.821425105990332e-08</v>
+        <v>3.12791864236706e-07</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.006039159879081e-07</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1.264929844524361e-07</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.267540688441088e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.566696817155674e-07</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.264929666525898e-07</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.267018800492603e-07</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.267540592028479e-07</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.264929844524361e-07</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.267540592028479e-07</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.116025675796529e-07</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.267540592028479e-07</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.809460113790822e-08</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2.091779426882775e-08</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.766649156185463e-08</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.091779426882775e-08</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2.091779426882775e-08</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.759458176301111e-08</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.803266448881336e-08</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.091779426882775e-08</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.678787404314352e-08</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.750618412753004e-08</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.821425105990334e-08</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>2.871118648768985e-08</v>
-      </c>
-      <c r="C9" t="n">
-        <v>2.181909405288182e-08</v>
-      </c>
-      <c r="D9" t="n">
+      <c r="B11" t="n">
+        <v>2.871118648768983e-08</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2.18190940528818e-08</v>
+      </c>
+      <c r="D11" t="n">
         <v>2.853687546555394e-08</v>
       </c>
-      <c r="E9" t="n">
-        <v>2.181909405288182e-08</v>
-      </c>
-      <c r="F9" t="n">
-        <v>2.181909405288182e-08</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2.849084636407148e-08</v>
-      </c>
-      <c r="H9" t="n">
-        <v>2.868754168120157e-08</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2.181909405288182e-08</v>
-      </c>
-      <c r="J9" t="n">
+      <c r="E11" t="n">
+        <v>2.18190940528818e-08</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.18190940528818e-08</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.849084636407145e-08</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.868754168120161e-08</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.18190940528818e-08</v>
+      </c>
+      <c r="J11" t="n">
         <v>2.818008745412844e-08</v>
       </c>
-      <c r="K9" t="n">
-        <v>2.847164608471442e-08</v>
-      </c>
-      <c r="L9" t="n">
-        <v>2.876105167495004e-08</v>
+      <c r="K11" t="n">
+        <v>2.847164608471441e-08</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.876105167495002e-08</v>
       </c>
     </row>
   </sheetData>
@@ -6779,7 +8059,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6847,321 +8127,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.661080341049475e-07</v>
+        <v>2.953946726291902e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.721513655523539e-07</v>
+        <v>2.282306934519872e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.799343874583643e-07</v>
+        <v>2.955196641753323e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.721513655523539e-07</v>
+        <v>2.282306934519872e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.721513655523539e-07</v>
+        <v>2.282306934519872e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.704175192728261e-07</v>
+        <v>2.951219203708487e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.708281996530257e-07</v>
+        <v>2.952353718288435e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.721513655523539e-07</v>
+        <v>2.282306934519872e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>2.450915095471895e-07</v>
+        <v>2.962362582149135e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.632110427063899e-07</v>
+        <v>2.953519627212419e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.688262467705722e-07</v>
+        <v>2.952694495510579e-08</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.370549655624819e-09</v>
+        <v>2.97130122118064e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>8.927365236068731e-09</v>
+        <v>2.288912558942577e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>9.370549655624819e-09</v>
+        <v>2.97130122118064e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>9.04086351072701e-09</v>
+        <v>2.288912558942577e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>9.04086351072701e-09</v>
+        <v>2.288912558942577e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>9.318756114705864e-09</v>
+        <v>2.968565797958063e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>9.370549655624819e-09</v>
+        <v>2.97130122118064e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>9.111961199233526e-09</v>
+        <v>2.288912558942577e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>9.370549655624819e-09</v>
+        <v>2.97130122118064e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>9.370549655624819e-09</v>
+        <v>2.97130122118064e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>9.370549655624819e-09</v>
+        <v>2.97130122118064e-08</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.324892606079373e-08</v>
+        <v>1.661080341049475e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>2.294730376010109e-08</v>
+        <v>1.721513655523545e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>2.327255510491888e-08</v>
+        <v>1.799343874583644e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>2.187612291120382e-08</v>
+        <v>1.721513655523545e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>2.300792372562053e-08</v>
+        <v>1.721513655523545e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>2.319713251987482e-08</v>
+        <v>1.704175192728294e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>3.755467668863534e-08</v>
+        <v>1.708281996530261e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>2.299033760440246e-08</v>
+        <v>1.721513655523545e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>2.408156828630144e-08</v>
+        <v>2.450915095471906e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>2.324735807793402e-08</v>
+        <v>1.632110427063905e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>2.324325985813565e-08</v>
+        <v>1.688262467705726e-07</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.504199039687533e-08</v>
+        <v>9.370549655624788e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>4.4783401940484e-08</v>
+        <v>8.927365236068733e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>4.50396298858215e-08</v>
+        <v>9.370549655624786e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>4.478336093143799e-08</v>
+        <v>9.040863510727023e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>4.478336093143799e-08</v>
+        <v>9.04086351072702e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>4.499019685595636e-08</v>
+        <v>9.318756114705804e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>4.504199039687533e-08</v>
+        <v>9.370549655624786e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>4.4783401940484e-08</v>
+        <v>9.111961199233467e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>4.504199039687533e-08</v>
+        <v>9.370549655624786e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>4.504199039687533e-08</v>
+        <v>9.370549655624786e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>4.504199039687533e-08</v>
+        <v>9.370549655624786e-09</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.398895138556114e-07</v>
+        <v>2.324892606079379e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>2.246627513475058e-07</v>
+        <v>2.294730376010124e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>2.425294830390749e-07</v>
+        <v>2.327255510491893e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>2.01409953275578e-07</v>
+        <v>2.187612291120417e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.423270628716635e-07</v>
+        <v>2.300792372562051e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>2.248498670657514e-07</v>
+        <v>2.31971325198748e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.249016606066712e-07</v>
+        <v>3.755467668863537e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>2.24643072150279e-07</v>
+        <v>2.299033760440246e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>2.249183679420942e-07</v>
+        <v>2.408156828630136e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.383103695832389e-07</v>
+        <v>2.324735807793395e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>3.137039565002187e-07</v>
+        <v>2.324325985813572e-08</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.674012751397879e-08</v>
+        <v>4.504199039687539e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.215501869516084e-07</v>
+        <v>4.478340194048422e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.218087849501095e-07</v>
+        <v>4.503962988582157e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.504788614722841e-07</v>
+        <v>4.478336093143809e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.215501691646499e-07</v>
+        <v>4.478336093143809e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.217569818670807e-07</v>
+        <v>4.499019685595652e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.218087754079997e-07</v>
+        <v>4.504199039687539e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.215501869516084e-07</v>
+        <v>4.478340194048422e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.218087754079997e-07</v>
+        <v>4.504199039687539e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.066946137081193e-07</v>
+        <v>4.504199039687539e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.218087754079997e-07</v>
+        <v>4.504199039687539e-08</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.769091839605848e-08</v>
+        <v>1.398895138556116e-07</v>
       </c>
       <c r="C8" t="n">
-        <v>2.081836521563718e-08</v>
+        <v>2.246627513475064e-07</v>
       </c>
       <c r="D8" t="n">
-        <v>2.743029377927281e-08</v>
+        <v>2.425294830390751e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>2.081836521563718e-08</v>
+        <v>2.014099532755786e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>2.081836521563718e-08</v>
+        <v>1.423270628716638e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>2.767259232396176e-08</v>
+        <v>2.248498670657514e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>2.805987506279543e-08</v>
+        <v>2.249016606066708e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>2.081836521563718e-08</v>
+        <v>2.246430721502797e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>2.595810651561821e-08</v>
+        <v>2.249183679420948e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>2.778274657544672e-08</v>
+        <v>1.383103695832393e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>2.811943493714169e-08</v>
+        <v>3.137039565002184e-07</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>9.674012751397908e-08</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1.215501869516087e-07</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.218087849501097e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.504788614722845e-07</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.215501691646504e-07</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.217569818670811e-07</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.218087754079999e-07</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.215501869516087e-07</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.218087754079998e-07</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.066946137081196e-07</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.218087754079998e-07</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.769091839605854e-08</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2.081836521563727e-08</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.743029377927288e-08</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.081836521563727e-08</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2.081836521563727e-08</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.767259232396179e-08</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.805987506279548e-08</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.081836521563727e-08</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.595810651561827e-08</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.778274657544679e-08</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.811943493714174e-08</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>2.861940813272306e-08</v>
-      </c>
-      <c r="C9" t="n">
-        <v>2.188086677600312e-08</v>
-      </c>
-      <c r="D9" t="n">
-        <v>2.851332225613846e-08</v>
-      </c>
-      <c r="E9" t="n">
-        <v>2.188086677600312e-08</v>
-      </c>
-      <c r="F9" t="n">
-        <v>2.188086677600312e-08</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2.859624074851867e-08</v>
-      </c>
-      <c r="H9" t="n">
-        <v>2.87713545118488e-08</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2.188086677600312e-08</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2.791513176355127e-08</v>
-      </c>
-      <c r="K9" t="n">
-        <v>2.865691925618898e-08</v>
-      </c>
-      <c r="L9" t="n">
-        <v>2.879525237965146e-08</v>
+      <c r="B11" t="n">
+        <v>2.861940813272309e-08</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2.188086677600321e-08</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.851332225613848e-08</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2.188086677600321e-08</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.188086677600321e-08</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.859624074851871e-08</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.877135451184885e-08</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.188086677600321e-08</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.791513176355126e-08</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.865691925618899e-08</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.879525237965147e-08</v>
       </c>
     </row>
   </sheetData>
@@ -7175,7 +8535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7243,321 +8603,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.925793104167714e-07</v>
+        <v>3.019912754437194e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.913822852518365e-07</v>
+        <v>2.305865128543504e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>5.526981784457444e-07</v>
+        <v>3.04993972802822e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.913822852518365e-07</v>
+        <v>2.305865128543504e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.913822852518365e-07</v>
+        <v>2.305865128543504e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>3.874859559975121e-07</v>
+        <v>3.023620016442633e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.102833075315938e-06</v>
+        <v>3.105073404156549e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.913822852518365e-07</v>
+        <v>2.305865128543504e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>2.844679119625272e-07</v>
+        <v>3.017365389975069e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>2.48960255396068e-07</v>
+        <v>3.014832021058845e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>2.180124508544153e-07</v>
+        <v>3.118423764213199e-08</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.843922277642169e-09</v>
+        <v>3.024686329996441e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>9.166946966084005e-09</v>
+        <v>2.311958671377658e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>9.843922277642167e-09</v>
+        <v>3.024686329996441e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>9.307668937558371e-09</v>
+        <v>2.311958671377658e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>9.307668937558261e-09</v>
+        <v>2.311958671377658e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>9.78434191355954e-09</v>
+        <v>3.018478766847748e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>9.843922277642169e-09</v>
+        <v>3.024686329996441e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>9.535612156948994e-09</v>
+        <v>2.311958671377658e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>9.843922277642167e-09</v>
+        <v>3.024686329996441e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>9.843922277642167e-09</v>
+        <v>3.024686329996441e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>9.843922277642167e-09</v>
+        <v>3.024686329996441e-08</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.528489768948395e-08</v>
+        <v>2.925793104167715e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>2.463159399406866e-08</v>
+        <v>1.913822852518307e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>2.581035567898797e-08</v>
+        <v>5.526981784457458e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>2.347533704083006e-08</v>
+        <v>1.913822852518307e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>2.496917154593751e-08</v>
+        <v>1.913822852518307e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>4.129394631337658e-08</v>
+        <v>3.874859559975182e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>4.219511099407022e-08</v>
+        <v>1.102833075315942e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>4.104521655676591e-08</v>
+        <v>1.913822852518307e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>4.152358268786039e-08</v>
+        <v>2.844679119625266e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>2.516500727929416e-08</v>
+        <v>2.48960255396068e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>2.563854479494772e-08</v>
+        <v>2.180124508544208e-07</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.844218985095678e-08</v>
+        <v>9.843922277641876e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>4.813387973026363e-08</v>
+        <v>9.166946966083851e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>4.843965863551424e-08</v>
+        <v>9.843922277641876e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>4.812693906233254e-08</v>
+        <v>9.307668937558257e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>4.812693906233254e-08</v>
+        <v>9.307668937558285e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>4.838260948687414e-08</v>
+        <v>9.784341913559586e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>4.844218985095678e-08</v>
+        <v>9.843922277641876e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>4.813387973026363e-08</v>
+        <v>9.535612156948659e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>4.844218985095678e-08</v>
+        <v>9.843922277641876e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>4.844218985095678e-08</v>
+        <v>9.843922277641876e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>4.844218985095678e-08</v>
+        <v>9.843922277641876e-09</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.51013848211744e-07</v>
+        <v>2.528489768948391e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>2.426758072430583e-07</v>
+        <v>2.463159399406846e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>2.620370454823864e-07</v>
+        <v>2.581035567898797e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>2.175245197588756e-07</v>
+        <v>2.347533704082976e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.53617758281808e-07</v>
+        <v>2.496917154593734e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>2.429098716366156e-07</v>
+        <v>4.129394631337644e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.42969452000701e-07</v>
+        <v>4.219511099407013e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>2.426611418800044e-07</v>
+        <v>4.104521655676585e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>2.429875239250626e-07</v>
+        <v>4.152358268786028e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.49305725660058e-07</v>
+        <v>2.516500727929403e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>3.390247693734035e-07</v>
+        <v>2.56385447949477e-08</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.187695344895031e-07</v>
+        <v>4.844218985095672e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.495678961202439e-07</v>
+        <v>4.81338797302635e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.498762094961384e-07</v>
+        <v>4.843965863551429e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.854642972956568e-07</v>
+        <v>4.812693906233269e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.495678629999259e-07</v>
+        <v>4.812693906233269e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.498166258768541e-07</v>
+        <v>4.838260948687422e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.498762062409372e-07</v>
+        <v>4.844218985095672e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.495678961202439e-07</v>
+        <v>4.81338797302635e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.498762062409372e-07</v>
+        <v>4.844218985095672e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.318528798319564e-07</v>
+        <v>4.844218985095672e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.498762062409372e-07</v>
+        <v>4.844218985095672e-08</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.549601646926123e-08</v>
+        <v>1.51013848211744e-07</v>
       </c>
       <c r="C8" t="n">
-        <v>2.091468731113117e-08</v>
+        <v>2.426758072430581e-07</v>
       </c>
       <c r="D8" t="n">
-        <v>1.920854230753752e-08</v>
+        <v>2.620370454823861e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>2.091468731113117e-08</v>
+        <v>2.175245197588754e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>2.091468731113117e-08</v>
+        <v>1.536177582818079e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>2.33901650561558e-08</v>
+        <v>2.429098716366152e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>8.081547347135788e-09</v>
+        <v>2.429694520007006e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>2.091468731113117e-08</v>
+        <v>2.426611418800044e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>2.606453604971945e-08</v>
+        <v>2.429875239250619e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>2.65651970525564e-08</v>
+        <v>1.49305725660058e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>5.247082348969759e-09</v>
+        <v>3.390247693734035e-07</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.187695344895033e-07</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1.49567896120244e-07</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.498762094961385e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.854642972956564e-07</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.49567862999926e-07</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.498166258768543e-07</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.49876206240937e-07</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.49567896120244e-07</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.49876206240937e-07</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.318528798319565e-07</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.49876206240937e-07</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.549601646926094e-08</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2.091468731113103e-08</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.920854230753726e-08</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.091468731113103e-08</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2.091468731113103e-08</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.339016505615559e-08</v>
+      </c>
+      <c r="H10" t="n">
+        <v>8.081547347135635e-09</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.091468731113103e-08</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.606453604971947e-08</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.656519705255629e-08</v>
+      </c>
+      <c r="L10" t="n">
+        <v>5.247082348969586e-09</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>2.803747709635165e-08</v>
-      </c>
-      <c r="C9" t="n">
-        <v>2.205541503063398e-08</v>
-      </c>
-      <c r="D9" t="n">
-        <v>2.547692605168619e-08</v>
-      </c>
-      <c r="E9" t="n">
-        <v>2.205541503063398e-08</v>
-      </c>
-      <c r="F9" t="n">
-        <v>2.205541503063398e-08</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2.714462522264232e-08</v>
-      </c>
-      <c r="H9" t="n">
-        <v>2.096544464635757e-08</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2.205541503063398e-08</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2.827068167260312e-08</v>
-      </c>
-      <c r="K9" t="n">
-        <v>2.847315033524352e-08</v>
-      </c>
-      <c r="L9" t="n">
-        <v>2.893278927622775e-08</v>
+      <c r="B11" t="n">
+        <v>2.803747709635148e-08</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2.205541503063375e-08</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.547692605168618e-08</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2.205541503063375e-08</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.205541503063375e-08</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.714462522264225e-08</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.096544464635762e-08</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.205541503063375e-08</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.827068167260302e-08</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.847315033524338e-08</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.893278927622763e-08</v>
       </c>
     </row>
   </sheetData>
@@ -7571,7 +9011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7639,321 +9079,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.313624465274688e-07</v>
+        <v>2.96887144881741e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.536176713893511e-07</v>
+        <v>2.283169095118957e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>4.242143478057783e-07</v>
+        <v>3.006079765214029e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.536176713893511e-07</v>
+        <v>2.283169095118957e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.536176713893511e-07</v>
+        <v>2.283169095118957e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>2.586671471842148e-07</v>
+        <v>2.979174351763469e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>2.388729184164359e-07</v>
+        <v>2.979366616122816e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.536176713893511e-07</v>
+        <v>2.283169095118957e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>2.098113904826159e-07</v>
+        <v>2.977379876131036e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.476347299631442e-07</v>
+        <v>2.970611171398174e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>7.787875983176572e-07</v>
+        <v>2.971798243607657e-08</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.414372404060693e-09</v>
+        <v>2.990577362576984e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>8.851012288358445e-09</v>
+        <v>2.292298964025552e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>9.414372404060693e-09</v>
+        <v>2.990577362576984e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>8.973103828538976e-09</v>
+        <v>2.292298964025552e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>8.973103828538974e-09</v>
+        <v>2.292298964025552e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>9.35810130634156e-09</v>
+        <v>2.985758853855708e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>9.414372404060693e-09</v>
+        <v>2.990577362576984e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>9.127205101549672e-09</v>
+        <v>2.292298964025552e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>9.414372404060693e-09</v>
+        <v>2.990577362576984e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>9.414372404060693e-09</v>
+        <v>2.990577362576984e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>9.414372404060693e-09</v>
+        <v>2.990577362576984e-08</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.781975965663932e-08</v>
+        <v>1.313624465274688e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>2.293735403605072e-08</v>
+        <v>1.536176713893512e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>2.390063964562044e-08</v>
+        <v>4.242143478057775e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>2.186835276665713e-08</v>
+        <v>1.536176713893512e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>2.31429292429791e-08</v>
+        <v>1.536176713893512e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>3.776348855892024e-08</v>
+        <v>2.586671471842158e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>3.838126160890482e-08</v>
+        <v>2.388729184164361e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>3.753259235412833e-08</v>
+        <v>1.536176713893512e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>2.426750140125051e-08</v>
+        <v>2.098113904826153e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>2.329474028362921e-08</v>
+        <v>1.476347299631438e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>2.361981188961915e-08</v>
+        <v>7.787875983176557e-07</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.524844454104994e-08</v>
+        <v>9.414372404060759e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>4.496127723853892e-08</v>
+        <v>8.851012288358536e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>4.524608559033421e-08</v>
+        <v>9.414372404060759e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>4.495786977523919e-08</v>
+        <v>8.973103828538972e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>4.495786977523919e-08</v>
+        <v>8.973103828539e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>4.51921734433308e-08</v>
+        <v>9.35810130634171e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>4.524844454104994e-08</v>
+        <v>9.414372404060759e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>4.496127723853892e-08</v>
+        <v>9.127205101549912e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>4.524844454104994e-08</v>
+        <v>9.414372404060759e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>4.524844454104994e-08</v>
+        <v>9.414372404060759e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>4.524844454104994e-08</v>
+        <v>9.414372404060759e-09</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.404741569466056e-07</v>
+        <v>3.781975965663933e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>2.255818945799383e-07</v>
+        <v>2.293735403605049e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>2.435562942480371e-07</v>
+        <v>2.390063964562044e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>2.022292712049722e-07</v>
+        <v>2.186835276665715e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.428927268038852e-07</v>
+        <v>2.314292924297914e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>2.257962608951471e-07</v>
+        <v>3.776348855892022e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.25852531992865e-07</v>
+        <v>3.838126160890507e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>2.255653646903552e-07</v>
+        <v>3.75325923541284e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>2.25869311302542e-07</v>
+        <v>2.426750140125052e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.388882097956413e-07</v>
+        <v>2.329474028362925e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>3.150373839641726e-07</v>
+        <v>2.361981188961916e-08</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.028594432737327e-07</v>
+        <v>4.524844454104991e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.293309660129232e-07</v>
+        <v>4.496127723853892e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.296181447026466e-07</v>
+        <v>4.524608559033424e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.602099130166555e-07</v>
+        <v>4.495786977523933e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.293309466350701e-07</v>
+        <v>4.495786977523933e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.29561862217715e-07</v>
+        <v>4.519217344333085e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.296181333154341e-07</v>
+        <v>4.524844454104991e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.293309660129232e-07</v>
+        <v>4.496127723853892e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.296181333154341e-07</v>
+        <v>4.524844454104991e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.141140480052057e-07</v>
+        <v>4.524844454104991e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.296181333154341e-07</v>
+        <v>4.524844454104991e-08</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.877052095719006e-08</v>
+        <v>1.404741569466062e-07</v>
       </c>
       <c r="C8" t="n">
-        <v>2.138645003649592e-08</v>
+        <v>2.255818945799399e-07</v>
       </c>
       <c r="D8" t="n">
-        <v>2.097665194914612e-08</v>
+        <v>2.435562942480383e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>2.138645003649592e-08</v>
+        <v>2.022292712049738e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>2.138645003649592e-08</v>
+        <v>1.428927268038862e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>2.557481305691726e-08</v>
+        <v>2.257962608951479e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>2.663730203589171e-08</v>
+        <v>2.258525319928666e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>2.138645003649592e-08</v>
+        <v>2.255653646903559e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>2.701142585176457e-08</v>
+        <v>2.258693113025432e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>2.840770065003011e-08</v>
+        <v>1.38888209795642e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>1.506481516017915e-08</v>
+        <v>3.150373839641742e-07</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.028594432737324e-07</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1.29330966012923e-07</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.296181447026463e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.602099130166552e-07</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.293309466350698e-07</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.29561862217715e-07</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.296181333154339e-07</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.29330966012923e-07</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.296181333154339e-07</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.141140480052058e-07</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.296181333154339e-07</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.877052095719009e-08</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2.138645003649594e-08</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.097665194914615e-08</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.138645003649594e-08</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2.138645003649594e-08</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.557481305691741e-08</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.663730203589175e-08</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.138645003649594e-08</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.701142585176459e-08</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.840770065003017e-08</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.50648151601792e-08</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>2.917217090613468e-08</v>
-      </c>
-      <c r="C9" t="n">
-        <v>2.213256053481773e-08</v>
-      </c>
-      <c r="D9" t="n">
-        <v>2.599801883385403e-08</v>
-      </c>
-      <c r="E9" t="n">
-        <v>2.213256053481773e-08</v>
-      </c>
-      <c r="F9" t="n">
-        <v>2.213256053481773e-08</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2.784306702509293e-08</v>
-      </c>
-      <c r="H9" t="n">
-        <v>2.830650117183268e-08</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2.213256053481773e-08</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2.845686130039885e-08</v>
-      </c>
-      <c r="K9" t="n">
-        <v>2.902448373594487e-08</v>
-      </c>
-      <c r="L9" t="n">
-        <v>2.360127126400122e-08</v>
+      <c r="B11" t="n">
+        <v>2.917217090613472e-08</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2.213256053481776e-08</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.59980188338541e-08</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2.213256053481776e-08</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.213256053481776e-08</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.784306702509296e-08</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.830650117183271e-08</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.213256053481776e-08</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.845686130039888e-08</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.902448373594488e-08</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.360127126400124e-08</v>
       </c>
     </row>
   </sheetData>
